--- a/docs/DiagrammeGantt.xlsx
+++ b/docs/DiagrammeGantt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabinb/IUT/S5/SAE/Application IA/11_Doc2Quiz/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A24615-5B49-4D48-AF38-694F8D9E961A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{493F1EA0-F742-1F44-93CB-94964DC96E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17460" xr2:uid="{33E6F111-0219-404F-8A7B-D068A4E95F65}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="100">
   <si>
     <t>PROJET SAE : DOC2QUIZ - PLANNING DE GANTT</t>
   </si>
@@ -518,7 +518,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -552,22 +552,31 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -580,12 +589,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -615,111 +618,11 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="24">
     <dxf>
       <fill>
         <patternFill>
@@ -817,7 +720,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -831,7 +734,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -862,7 +765,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -883,7 +786,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor theme="6" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1247,14 +1150,14 @@
       <c r="Q1"/>
     </row>
     <row r="2" spans="1:133" ht="31" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
       <c r="P2"/>
       <c r="Q2"/>
     </row>
@@ -1263,808 +1166,808 @@
       <c r="Q3"/>
     </row>
     <row r="4" spans="1:133" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="33" t="s">
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33" t="s">
+      <c r="F4" s="34"/>
+      <c r="G4" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33" t="s">
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33" t="s">
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="25" t="s">
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="Q4" s="25"/>
-      <c r="S4" s="25" t="s">
+      <c r="Q4" s="26"/>
+      <c r="S4" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="T4" s="25"/>
-      <c r="U4" s="25"/>
-      <c r="V4" s="25"/>
-      <c r="W4" s="25"/>
-      <c r="X4" s="25"/>
-      <c r="Y4" s="25"/>
-      <c r="Z4" s="25"/>
-      <c r="AA4" s="25"/>
-      <c r="AB4" s="25"/>
-      <c r="AC4" s="32" t="s">
+      <c r="T4" s="26"/>
+      <c r="U4" s="26"/>
+      <c r="V4" s="26"/>
+      <c r="W4" s="26"/>
+      <c r="X4" s="26"/>
+      <c r="Y4" s="26"/>
+      <c r="Z4" s="26"/>
+      <c r="AA4" s="26"/>
+      <c r="AB4" s="26"/>
+      <c r="AC4" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="AD4" s="25"/>
-      <c r="AE4" s="25"/>
-      <c r="AF4" s="25"/>
-      <c r="AG4" s="25"/>
-      <c r="AH4" s="25"/>
-      <c r="AI4" s="25"/>
-      <c r="AJ4" s="25"/>
-      <c r="AK4" s="25"/>
-      <c r="AL4" s="25"/>
-      <c r="AM4" s="25" t="s">
+      <c r="AD4" s="26"/>
+      <c r="AE4" s="26"/>
+      <c r="AF4" s="26"/>
+      <c r="AG4" s="26"/>
+      <c r="AH4" s="26"/>
+      <c r="AI4" s="26"/>
+      <c r="AJ4" s="26"/>
+      <c r="AK4" s="26"/>
+      <c r="AL4" s="26"/>
+      <c r="AM4" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="AN4" s="25"/>
-      <c r="AO4" s="25"/>
-      <c r="AP4" s="25"/>
-      <c r="AQ4" s="25"/>
-      <c r="AR4" s="25"/>
-      <c r="AS4" s="25"/>
-      <c r="AT4" s="25"/>
-      <c r="AU4" s="25"/>
-      <c r="AV4" s="25"/>
-      <c r="AW4" s="25" t="s">
+      <c r="AN4" s="26"/>
+      <c r="AO4" s="26"/>
+      <c r="AP4" s="26"/>
+      <c r="AQ4" s="26"/>
+      <c r="AR4" s="26"/>
+      <c r="AS4" s="26"/>
+      <c r="AT4" s="26"/>
+      <c r="AU4" s="26"/>
+      <c r="AV4" s="26"/>
+      <c r="AW4" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="AX4" s="25"/>
-      <c r="AY4" s="25"/>
-      <c r="AZ4" s="25"/>
-      <c r="BA4" s="25"/>
-      <c r="BB4" s="25"/>
-      <c r="BC4" s="25"/>
-      <c r="BD4" s="25"/>
-      <c r="BE4" s="25"/>
-      <c r="BF4" s="25"/>
-      <c r="BG4" s="25" t="s">
+      <c r="AX4" s="26"/>
+      <c r="AY4" s="26"/>
+      <c r="AZ4" s="26"/>
+      <c r="BA4" s="26"/>
+      <c r="BB4" s="26"/>
+      <c r="BC4" s="26"/>
+      <c r="BD4" s="26"/>
+      <c r="BE4" s="26"/>
+      <c r="BF4" s="26"/>
+      <c r="BG4" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="BH4" s="25"/>
-      <c r="BI4" s="25"/>
-      <c r="BJ4" s="25"/>
-      <c r="BK4" s="25"/>
-      <c r="BL4" s="25"/>
-      <c r="BM4" s="25"/>
-      <c r="BN4" s="25"/>
-      <c r="BO4" s="25"/>
-      <c r="BP4" s="25"/>
-      <c r="BQ4" s="25" t="s">
+      <c r="BH4" s="26"/>
+      <c r="BI4" s="26"/>
+      <c r="BJ4" s="26"/>
+      <c r="BK4" s="26"/>
+      <c r="BL4" s="26"/>
+      <c r="BM4" s="26"/>
+      <c r="BN4" s="26"/>
+      <c r="BO4" s="26"/>
+      <c r="BP4" s="26"/>
+      <c r="BQ4" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="BR4" s="25"/>
-      <c r="BS4" s="25"/>
-      <c r="BT4" s="25"/>
-      <c r="BU4" s="25"/>
-      <c r="BV4" s="25"/>
-      <c r="BW4" s="25"/>
-      <c r="BX4" s="25"/>
-      <c r="BY4" s="25"/>
-      <c r="BZ4" s="25"/>
-      <c r="CA4" s="25" t="s">
+      <c r="BR4" s="26"/>
+      <c r="BS4" s="26"/>
+      <c r="BT4" s="26"/>
+      <c r="BU4" s="26"/>
+      <c r="BV4" s="26"/>
+      <c r="BW4" s="26"/>
+      <c r="BX4" s="26"/>
+      <c r="BY4" s="26"/>
+      <c r="BZ4" s="26"/>
+      <c r="CA4" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="CB4" s="25"/>
-      <c r="CC4" s="25"/>
-      <c r="CD4" s="25"/>
-      <c r="CE4" s="25"/>
-      <c r="CF4" s="25"/>
-      <c r="CG4" s="25"/>
-      <c r="CH4" s="25"/>
-      <c r="CI4" s="25"/>
-      <c r="CJ4" s="25"/>
-      <c r="CK4" s="25" t="s">
+      <c r="CB4" s="26"/>
+      <c r="CC4" s="26"/>
+      <c r="CD4" s="26"/>
+      <c r="CE4" s="26"/>
+      <c r="CF4" s="26"/>
+      <c r="CG4" s="26"/>
+      <c r="CH4" s="26"/>
+      <c r="CI4" s="26"/>
+      <c r="CJ4" s="26"/>
+      <c r="CK4" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="CL4" s="25"/>
-      <c r="CM4" s="25"/>
-      <c r="CN4" s="25"/>
-      <c r="CO4" s="25"/>
-      <c r="CP4" s="25"/>
-      <c r="CQ4" s="25"/>
-      <c r="CR4" s="25"/>
-      <c r="CS4" s="25"/>
-      <c r="CT4" s="25"/>
-      <c r="CU4" s="25" t="s">
+      <c r="CL4" s="26"/>
+      <c r="CM4" s="26"/>
+      <c r="CN4" s="26"/>
+      <c r="CO4" s="26"/>
+      <c r="CP4" s="26"/>
+      <c r="CQ4" s="26"/>
+      <c r="CR4" s="26"/>
+      <c r="CS4" s="26"/>
+      <c r="CT4" s="26"/>
+      <c r="CU4" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="CV4" s="25"/>
-      <c r="CW4" s="25"/>
-      <c r="CX4" s="25"/>
-      <c r="CY4" s="25"/>
-      <c r="CZ4" s="25"/>
-      <c r="DA4" s="25"/>
-      <c r="DB4" s="25"/>
-      <c r="DC4" s="25"/>
-      <c r="DD4" s="25"/>
-      <c r="DE4" s="25" t="s">
+      <c r="CV4" s="26"/>
+      <c r="CW4" s="26"/>
+      <c r="CX4" s="26"/>
+      <c r="CY4" s="26"/>
+      <c r="CZ4" s="26"/>
+      <c r="DA4" s="26"/>
+      <c r="DB4" s="26"/>
+      <c r="DC4" s="26"/>
+      <c r="DD4" s="26"/>
+      <c r="DE4" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="DF4" s="25"/>
-      <c r="DG4" s="25"/>
-      <c r="DH4" s="25"/>
-      <c r="DI4" s="25"/>
-      <c r="DJ4" s="25"/>
-      <c r="DK4" s="25"/>
-      <c r="DL4" s="25"/>
-      <c r="DM4" s="25"/>
-      <c r="DN4" s="25"/>
-      <c r="DO4" s="25" t="s">
+      <c r="DF4" s="26"/>
+      <c r="DG4" s="26"/>
+      <c r="DH4" s="26"/>
+      <c r="DI4" s="26"/>
+      <c r="DJ4" s="26"/>
+      <c r="DK4" s="26"/>
+      <c r="DL4" s="26"/>
+      <c r="DM4" s="26"/>
+      <c r="DN4" s="26"/>
+      <c r="DO4" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="DP4" s="25"/>
-      <c r="DQ4" s="25"/>
-      <c r="DR4" s="25"/>
-      <c r="DS4" s="25"/>
-      <c r="DT4" s="25"/>
-      <c r="DU4" s="25"/>
-      <c r="DV4" s="25"/>
-      <c r="DW4" s="25"/>
-      <c r="DX4" s="25"/>
-      <c r="DY4" s="25" t="s">
+      <c r="DP4" s="26"/>
+      <c r="DQ4" s="26"/>
+      <c r="DR4" s="26"/>
+      <c r="DS4" s="26"/>
+      <c r="DT4" s="26"/>
+      <c r="DU4" s="26"/>
+      <c r="DV4" s="26"/>
+      <c r="DW4" s="26"/>
+      <c r="DX4" s="26"/>
+      <c r="DY4" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="DZ4" s="25"/>
-      <c r="EA4" s="25"/>
-      <c r="EB4" s="25"/>
-      <c r="EC4" s="25"/>
+      <c r="DZ4" s="26"/>
+      <c r="EA4" s="26"/>
+      <c r="EB4" s="26"/>
+      <c r="EC4" s="26"/>
     </row>
     <row r="5" spans="1:133" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="25"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="25"/>
-      <c r="S5" s="25"/>
-      <c r="T5" s="25"/>
-      <c r="U5" s="25"/>
-      <c r="V5" s="25"/>
-      <c r="W5" s="25"/>
-      <c r="X5" s="25"/>
-      <c r="Y5" s="25"/>
-      <c r="Z5" s="25"/>
-      <c r="AA5" s="25"/>
-      <c r="AB5" s="25"/>
-      <c r="AC5" s="32"/>
-      <c r="AD5" s="25"/>
-      <c r="AE5" s="25"/>
-      <c r="AF5" s="25"/>
-      <c r="AG5" s="25"/>
-      <c r="AH5" s="25"/>
-      <c r="AI5" s="25"/>
-      <c r="AJ5" s="25"/>
-      <c r="AK5" s="25"/>
-      <c r="AL5" s="25"/>
-      <c r="AM5" s="25"/>
-      <c r="AN5" s="25"/>
-      <c r="AO5" s="25"/>
-      <c r="AP5" s="25"/>
-      <c r="AQ5" s="25"/>
-      <c r="AR5" s="25"/>
-      <c r="AS5" s="25"/>
-      <c r="AT5" s="25"/>
-      <c r="AU5" s="25"/>
-      <c r="AV5" s="25"/>
-      <c r="AW5" s="25"/>
-      <c r="AX5" s="25"/>
-      <c r="AY5" s="25"/>
-      <c r="AZ5" s="25"/>
-      <c r="BA5" s="25"/>
-      <c r="BB5" s="25"/>
-      <c r="BC5" s="25"/>
-      <c r="BD5" s="25"/>
-      <c r="BE5" s="25"/>
-      <c r="BF5" s="25"/>
-      <c r="BG5" s="25"/>
-      <c r="BH5" s="25"/>
-      <c r="BI5" s="25"/>
-      <c r="BJ5" s="25"/>
-      <c r="BK5" s="25"/>
-      <c r="BL5" s="25"/>
-      <c r="BM5" s="25"/>
-      <c r="BN5" s="25"/>
-      <c r="BO5" s="25"/>
-      <c r="BP5" s="25"/>
-      <c r="BQ5" s="25"/>
-      <c r="BR5" s="25"/>
-      <c r="BS5" s="25"/>
-      <c r="BT5" s="25"/>
-      <c r="BU5" s="25"/>
-      <c r="BV5" s="25"/>
-      <c r="BW5" s="25"/>
-      <c r="BX5" s="25"/>
-      <c r="BY5" s="25"/>
-      <c r="BZ5" s="25"/>
-      <c r="CA5" s="25"/>
-      <c r="CB5" s="25"/>
-      <c r="CC5" s="25"/>
-      <c r="CD5" s="25"/>
-      <c r="CE5" s="25"/>
-      <c r="CF5" s="25"/>
-      <c r="CG5" s="25"/>
-      <c r="CH5" s="25"/>
-      <c r="CI5" s="25"/>
-      <c r="CJ5" s="25"/>
-      <c r="CK5" s="25"/>
-      <c r="CL5" s="25"/>
-      <c r="CM5" s="25"/>
-      <c r="CN5" s="25"/>
-      <c r="CO5" s="25"/>
-      <c r="CP5" s="25"/>
-      <c r="CQ5" s="25"/>
-      <c r="CR5" s="25"/>
-      <c r="CS5" s="25"/>
-      <c r="CT5" s="25"/>
-      <c r="CU5" s="25"/>
-      <c r="CV5" s="25"/>
-      <c r="CW5" s="25"/>
-      <c r="CX5" s="25"/>
-      <c r="CY5" s="25"/>
-      <c r="CZ5" s="25"/>
-      <c r="DA5" s="25"/>
-      <c r="DB5" s="25"/>
-      <c r="DC5" s="25"/>
-      <c r="DD5" s="25"/>
-      <c r="DE5" s="25"/>
-      <c r="DF5" s="25"/>
-      <c r="DG5" s="25"/>
-      <c r="DH5" s="25"/>
-      <c r="DI5" s="25"/>
-      <c r="DJ5" s="25"/>
-      <c r="DK5" s="25"/>
-      <c r="DL5" s="25"/>
-      <c r="DM5" s="25"/>
-      <c r="DN5" s="25"/>
-      <c r="DO5" s="25"/>
-      <c r="DP5" s="25"/>
-      <c r="DQ5" s="25"/>
-      <c r="DR5" s="25"/>
-      <c r="DS5" s="25"/>
-      <c r="DT5" s="25"/>
-      <c r="DU5" s="25"/>
-      <c r="DV5" s="25"/>
-      <c r="DW5" s="25"/>
-      <c r="DX5" s="25"/>
-      <c r="DY5" s="25"/>
-      <c r="DZ5" s="25"/>
-      <c r="EA5" s="25"/>
-      <c r="EB5" s="25"/>
-      <c r="EC5" s="25"/>
+      <c r="A5" s="26"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="26"/>
+      <c r="Q5" s="26"/>
+      <c r="S5" s="26"/>
+      <c r="T5" s="26"/>
+      <c r="U5" s="26"/>
+      <c r="V5" s="26"/>
+      <c r="W5" s="26"/>
+      <c r="X5" s="26"/>
+      <c r="Y5" s="26"/>
+      <c r="Z5" s="26"/>
+      <c r="AA5" s="26"/>
+      <c r="AB5" s="26"/>
+      <c r="AC5" s="33"/>
+      <c r="AD5" s="26"/>
+      <c r="AE5" s="26"/>
+      <c r="AF5" s="26"/>
+      <c r="AG5" s="26"/>
+      <c r="AH5" s="26"/>
+      <c r="AI5" s="26"/>
+      <c r="AJ5" s="26"/>
+      <c r="AK5" s="26"/>
+      <c r="AL5" s="26"/>
+      <c r="AM5" s="26"/>
+      <c r="AN5" s="26"/>
+      <c r="AO5" s="26"/>
+      <c r="AP5" s="26"/>
+      <c r="AQ5" s="26"/>
+      <c r="AR5" s="26"/>
+      <c r="AS5" s="26"/>
+      <c r="AT5" s="26"/>
+      <c r="AU5" s="26"/>
+      <c r="AV5" s="26"/>
+      <c r="AW5" s="26"/>
+      <c r="AX5" s="26"/>
+      <c r="AY5" s="26"/>
+      <c r="AZ5" s="26"/>
+      <c r="BA5" s="26"/>
+      <c r="BB5" s="26"/>
+      <c r="BC5" s="26"/>
+      <c r="BD5" s="26"/>
+      <c r="BE5" s="26"/>
+      <c r="BF5" s="26"/>
+      <c r="BG5" s="26"/>
+      <c r="BH5" s="26"/>
+      <c r="BI5" s="26"/>
+      <c r="BJ5" s="26"/>
+      <c r="BK5" s="26"/>
+      <c r="BL5" s="26"/>
+      <c r="BM5" s="26"/>
+      <c r="BN5" s="26"/>
+      <c r="BO5" s="26"/>
+      <c r="BP5" s="26"/>
+      <c r="BQ5" s="26"/>
+      <c r="BR5" s="26"/>
+      <c r="BS5" s="26"/>
+      <c r="BT5" s="26"/>
+      <c r="BU5" s="26"/>
+      <c r="BV5" s="26"/>
+      <c r="BW5" s="26"/>
+      <c r="BX5" s="26"/>
+      <c r="BY5" s="26"/>
+      <c r="BZ5" s="26"/>
+      <c r="CA5" s="26"/>
+      <c r="CB5" s="26"/>
+      <c r="CC5" s="26"/>
+      <c r="CD5" s="26"/>
+      <c r="CE5" s="26"/>
+      <c r="CF5" s="26"/>
+      <c r="CG5" s="26"/>
+      <c r="CH5" s="26"/>
+      <c r="CI5" s="26"/>
+      <c r="CJ5" s="26"/>
+      <c r="CK5" s="26"/>
+      <c r="CL5" s="26"/>
+      <c r="CM5" s="26"/>
+      <c r="CN5" s="26"/>
+      <c r="CO5" s="26"/>
+      <c r="CP5" s="26"/>
+      <c r="CQ5" s="26"/>
+      <c r="CR5" s="26"/>
+      <c r="CS5" s="26"/>
+      <c r="CT5" s="26"/>
+      <c r="CU5" s="26"/>
+      <c r="CV5" s="26"/>
+      <c r="CW5" s="26"/>
+      <c r="CX5" s="26"/>
+      <c r="CY5" s="26"/>
+      <c r="CZ5" s="26"/>
+      <c r="DA5" s="26"/>
+      <c r="DB5" s="26"/>
+      <c r="DC5" s="26"/>
+      <c r="DD5" s="26"/>
+      <c r="DE5" s="26"/>
+      <c r="DF5" s="26"/>
+      <c r="DG5" s="26"/>
+      <c r="DH5" s="26"/>
+      <c r="DI5" s="26"/>
+      <c r="DJ5" s="26"/>
+      <c r="DK5" s="26"/>
+      <c r="DL5" s="26"/>
+      <c r="DM5" s="26"/>
+      <c r="DN5" s="26"/>
+      <c r="DO5" s="26"/>
+      <c r="DP5" s="26"/>
+      <c r="DQ5" s="26"/>
+      <c r="DR5" s="26"/>
+      <c r="DS5" s="26"/>
+      <c r="DT5" s="26"/>
+      <c r="DU5" s="26"/>
+      <c r="DV5" s="26"/>
+      <c r="DW5" s="26"/>
+      <c r="DX5" s="26"/>
+      <c r="DY5" s="26"/>
+      <c r="DZ5" s="26"/>
+      <c r="EA5" s="26"/>
+      <c r="EB5" s="26"/>
+      <c r="EC5" s="26"/>
     </row>
     <row r="6" spans="1:133" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="25"/>
-      <c r="Q6" s="25"/>
-      <c r="S6" s="28">
+      <c r="A6" s="26"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="34"/>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="26"/>
+      <c r="S6" s="29">
         <v>1</v>
       </c>
-      <c r="T6" s="28">
+      <c r="T6" s="29">
         <v>2</v>
       </c>
-      <c r="U6" s="28">
+      <c r="U6" s="29">
         <v>3</v>
       </c>
-      <c r="V6" s="28">
+      <c r="V6" s="29">
         <v>4</v>
       </c>
-      <c r="W6" s="28">
+      <c r="W6" s="29">
         <v>5</v>
       </c>
-      <c r="X6" s="28">
+      <c r="X6" s="29">
         <v>6</v>
       </c>
-      <c r="Y6" s="28">
+      <c r="Y6" s="29">
         <v>7</v>
       </c>
-      <c r="Z6" s="28">
+      <c r="Z6" s="29">
         <v>8</v>
       </c>
-      <c r="AA6" s="28">
+      <c r="AA6" s="29">
         <v>9</v>
       </c>
-      <c r="AB6" s="28">
+      <c r="AB6" s="29">
         <v>10</v>
       </c>
-      <c r="AC6" s="29">
+      <c r="AC6" s="30">
         <v>11</v>
       </c>
-      <c r="AD6" s="28">
+      <c r="AD6" s="29">
         <v>12</v>
       </c>
-      <c r="AE6" s="28">
+      <c r="AE6" s="29">
         <v>13</v>
       </c>
-      <c r="AF6" s="28">
+      <c r="AF6" s="29">
         <v>14</v>
       </c>
-      <c r="AG6" s="28">
+      <c r="AG6" s="29">
         <v>15</v>
       </c>
-      <c r="AH6" s="28">
+      <c r="AH6" s="29">
         <v>16</v>
       </c>
-      <c r="AI6" s="28">
+      <c r="AI6" s="29">
         <v>17</v>
       </c>
-      <c r="AJ6" s="28">
+      <c r="AJ6" s="29">
         <v>18</v>
       </c>
-      <c r="AK6" s="28">
+      <c r="AK6" s="29">
         <v>19</v>
       </c>
-      <c r="AL6" s="28">
+      <c r="AL6" s="29">
         <v>20</v>
       </c>
-      <c r="AM6" s="28">
+      <c r="AM6" s="29">
         <v>21</v>
       </c>
-      <c r="AN6" s="28">
+      <c r="AN6" s="29">
         <v>22</v>
       </c>
-      <c r="AO6" s="28">
+      <c r="AO6" s="29">
         <v>23</v>
       </c>
-      <c r="AP6" s="28">
+      <c r="AP6" s="29">
         <v>24</v>
       </c>
-      <c r="AQ6" s="28">
+      <c r="AQ6" s="29">
         <v>25</v>
       </c>
-      <c r="AR6" s="28">
+      <c r="AR6" s="29">
         <v>26</v>
       </c>
-      <c r="AS6" s="28">
+      <c r="AS6" s="29">
         <v>27</v>
       </c>
-      <c r="AT6" s="28">
+      <c r="AT6" s="29">
         <v>28</v>
       </c>
-      <c r="AU6" s="28">
+      <c r="AU6" s="29">
         <v>29</v>
       </c>
-      <c r="AV6" s="28">
+      <c r="AV6" s="29">
         <v>30</v>
       </c>
-      <c r="AW6" s="28">
+      <c r="AW6" s="29">
         <v>31</v>
       </c>
-      <c r="AX6" s="28">
+      <c r="AX6" s="29">
         <v>32</v>
       </c>
-      <c r="AY6" s="28">
+      <c r="AY6" s="29">
         <v>33</v>
       </c>
-      <c r="AZ6" s="28">
+      <c r="AZ6" s="29">
         <v>34</v>
       </c>
-      <c r="BA6" s="28">
+      <c r="BA6" s="29">
         <v>35</v>
       </c>
-      <c r="BB6" s="28">
+      <c r="BB6" s="29">
         <v>36</v>
       </c>
-      <c r="BC6" s="28">
+      <c r="BC6" s="29">
         <v>37</v>
       </c>
-      <c r="BD6" s="28">
+      <c r="BD6" s="29">
         <v>38</v>
       </c>
-      <c r="BE6" s="28">
+      <c r="BE6" s="29">
         <v>39</v>
       </c>
-      <c r="BF6" s="28">
+      <c r="BF6" s="29">
         <v>40</v>
       </c>
-      <c r="BG6" s="28">
+      <c r="BG6" s="29">
         <v>41</v>
       </c>
-      <c r="BH6" s="28">
+      <c r="BH6" s="29">
         <v>42</v>
       </c>
-      <c r="BI6" s="28">
+      <c r="BI6" s="29">
         <v>43</v>
       </c>
-      <c r="BJ6" s="28">
+      <c r="BJ6" s="29">
         <v>44</v>
       </c>
-      <c r="BK6" s="28">
+      <c r="BK6" s="29">
         <v>45</v>
       </c>
-      <c r="BL6" s="28">
+      <c r="BL6" s="29">
         <v>46</v>
       </c>
-      <c r="BM6" s="28">
+      <c r="BM6" s="29">
         <v>47</v>
       </c>
-      <c r="BN6" s="28">
+      <c r="BN6" s="29">
         <v>48</v>
       </c>
-      <c r="BO6" s="28">
+      <c r="BO6" s="29">
         <v>49</v>
       </c>
-      <c r="BP6" s="28">
+      <c r="BP6" s="29">
         <v>50</v>
       </c>
-      <c r="BQ6" s="28">
+      <c r="BQ6" s="29">
         <v>51</v>
       </c>
-      <c r="BR6" s="28">
+      <c r="BR6" s="29">
         <v>52</v>
       </c>
-      <c r="BS6" s="28">
+      <c r="BS6" s="29">
         <v>53</v>
       </c>
-      <c r="BT6" s="28">
+      <c r="BT6" s="29">
         <v>54</v>
       </c>
-      <c r="BU6" s="28">
+      <c r="BU6" s="29">
         <v>55</v>
       </c>
-      <c r="BV6" s="28">
+      <c r="BV6" s="29">
         <v>56</v>
       </c>
-      <c r="BW6" s="28">
+      <c r="BW6" s="29">
         <v>57</v>
       </c>
-      <c r="BX6" s="28">
+      <c r="BX6" s="29">
         <v>58</v>
       </c>
-      <c r="BY6" s="28">
+      <c r="BY6" s="29">
         <v>59</v>
       </c>
-      <c r="BZ6" s="28">
+      <c r="BZ6" s="29">
         <v>60</v>
       </c>
-      <c r="CA6" s="28">
+      <c r="CA6" s="29">
         <v>61</v>
       </c>
-      <c r="CB6" s="28">
+      <c r="CB6" s="29">
         <v>62</v>
       </c>
-      <c r="CC6" s="28">
+      <c r="CC6" s="29">
         <v>63</v>
       </c>
-      <c r="CD6" s="28">
+      <c r="CD6" s="29">
         <v>64</v>
       </c>
-      <c r="CE6" s="28">
+      <c r="CE6" s="29">
         <v>65</v>
       </c>
-      <c r="CF6" s="28">
+      <c r="CF6" s="29">
         <v>66</v>
       </c>
-      <c r="CG6" s="28">
+      <c r="CG6" s="29">
         <v>67</v>
       </c>
-      <c r="CH6" s="28">
+      <c r="CH6" s="29">
         <v>68</v>
       </c>
-      <c r="CI6" s="28">
+      <c r="CI6" s="29">
         <v>69</v>
       </c>
-      <c r="CJ6" s="28">
+      <c r="CJ6" s="29">
         <v>70</v>
       </c>
-      <c r="CK6" s="28">
+      <c r="CK6" s="29">
         <v>71</v>
       </c>
-      <c r="CL6" s="28">
+      <c r="CL6" s="29">
         <v>72</v>
       </c>
-      <c r="CM6" s="28">
+      <c r="CM6" s="29">
         <v>73</v>
       </c>
-      <c r="CN6" s="28">
+      <c r="CN6" s="29">
         <v>74</v>
       </c>
-      <c r="CO6" s="28">
+      <c r="CO6" s="29">
         <v>75</v>
       </c>
-      <c r="CP6" s="28">
+      <c r="CP6" s="29">
         <v>76</v>
       </c>
-      <c r="CQ6" s="28">
+      <c r="CQ6" s="29">
         <v>77</v>
       </c>
-      <c r="CR6" s="28">
+      <c r="CR6" s="29">
         <v>78</v>
       </c>
-      <c r="CS6" s="28">
+      <c r="CS6" s="29">
         <v>79</v>
       </c>
-      <c r="CT6" s="28">
+      <c r="CT6" s="29">
         <v>80</v>
       </c>
-      <c r="CU6" s="28">
+      <c r="CU6" s="29">
         <v>81</v>
       </c>
-      <c r="CV6" s="28">
+      <c r="CV6" s="29">
         <v>82</v>
       </c>
-      <c r="CW6" s="28">
+      <c r="CW6" s="29">
         <v>83</v>
       </c>
-      <c r="CX6" s="28">
+      <c r="CX6" s="29">
         <v>84</v>
       </c>
-      <c r="CY6" s="28">
+      <c r="CY6" s="29">
         <v>85</v>
       </c>
-      <c r="CZ6" s="28">
+      <c r="CZ6" s="29">
         <v>86</v>
       </c>
-      <c r="DA6" s="28">
+      <c r="DA6" s="29">
         <v>87</v>
       </c>
-      <c r="DB6" s="28">
+      <c r="DB6" s="29">
         <v>88</v>
       </c>
-      <c r="DC6" s="28">
+      <c r="DC6" s="29">
         <v>89</v>
       </c>
-      <c r="DD6" s="28">
+      <c r="DD6" s="29">
         <v>90</v>
       </c>
-      <c r="DE6" s="28">
+      <c r="DE6" s="29">
         <v>91</v>
       </c>
-      <c r="DF6" s="28">
+      <c r="DF6" s="29">
         <v>92</v>
       </c>
-      <c r="DG6" s="28">
+      <c r="DG6" s="29">
         <v>93</v>
       </c>
-      <c r="DH6" s="28">
+      <c r="DH6" s="29">
         <v>94</v>
       </c>
-      <c r="DI6" s="28">
+      <c r="DI6" s="29">
         <v>95</v>
       </c>
-      <c r="DJ6" s="28">
+      <c r="DJ6" s="29">
         <v>96</v>
       </c>
-      <c r="DK6" s="28">
+      <c r="DK6" s="29">
         <v>97</v>
       </c>
-      <c r="DL6" s="28">
+      <c r="DL6" s="29">
         <v>98</v>
       </c>
-      <c r="DM6" s="28">
+      <c r="DM6" s="29">
         <v>99</v>
       </c>
-      <c r="DN6" s="28">
+      <c r="DN6" s="29">
         <v>100</v>
       </c>
-      <c r="DO6" s="28">
+      <c r="DO6" s="29">
         <v>101</v>
       </c>
-      <c r="DP6" s="28">
+      <c r="DP6" s="29">
         <v>102</v>
       </c>
-      <c r="DQ6" s="28">
+      <c r="DQ6" s="29">
         <v>103</v>
       </c>
-      <c r="DR6" s="28">
+      <c r="DR6" s="29">
         <v>104</v>
       </c>
-      <c r="DS6" s="28">
+      <c r="DS6" s="29">
         <v>105</v>
       </c>
-      <c r="DT6" s="28">
+      <c r="DT6" s="29">
         <v>106</v>
       </c>
-      <c r="DU6" s="28">
+      <c r="DU6" s="29">
         <v>107</v>
       </c>
-      <c r="DV6" s="28">
+      <c r="DV6" s="29">
         <v>108</v>
       </c>
-      <c r="DW6" s="28">
+      <c r="DW6" s="29">
         <v>109</v>
       </c>
-      <c r="DX6" s="28">
+      <c r="DX6" s="29">
         <v>110</v>
       </c>
-      <c r="DY6" s="28">
+      <c r="DY6" s="29">
         <v>111</v>
       </c>
-      <c r="DZ6" s="28">
+      <c r="DZ6" s="29">
         <v>112</v>
       </c>
-      <c r="EA6" s="28">
+      <c r="EA6" s="29">
         <v>113</v>
       </c>
-      <c r="EB6" s="28">
+      <c r="EB6" s="29">
         <v>114</v>
       </c>
-      <c r="EC6" s="28">
+      <c r="EC6" s="29">
         <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:133" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="33"/>
-      <c r="M7" s="33"/>
-      <c r="N7" s="33"/>
-      <c r="O7" s="33"/>
-      <c r="P7" s="25"/>
-      <c r="Q7" s="25"/>
-      <c r="S7" s="28"/>
-      <c r="T7" s="28"/>
-      <c r="U7" s="28"/>
-      <c r="V7" s="28"/>
-      <c r="W7" s="28"/>
-      <c r="X7" s="28"/>
-      <c r="Y7" s="28"/>
-      <c r="Z7" s="28"/>
-      <c r="AA7" s="28"/>
-      <c r="AB7" s="28"/>
-      <c r="AC7" s="29"/>
-      <c r="AD7" s="28"/>
-      <c r="AE7" s="28"/>
-      <c r="AF7" s="28"/>
-      <c r="AG7" s="28"/>
-      <c r="AH7" s="28"/>
-      <c r="AI7" s="28"/>
-      <c r="AJ7" s="28"/>
-      <c r="AK7" s="28"/>
-      <c r="AL7" s="28"/>
-      <c r="AM7" s="28"/>
-      <c r="AN7" s="28"/>
-      <c r="AO7" s="28"/>
-      <c r="AP7" s="28"/>
-      <c r="AQ7" s="28"/>
-      <c r="AR7" s="28"/>
-      <c r="AS7" s="28"/>
-      <c r="AT7" s="28"/>
-      <c r="AU7" s="28"/>
-      <c r="AV7" s="28"/>
-      <c r="AW7" s="28"/>
-      <c r="AX7" s="28"/>
-      <c r="AY7" s="28"/>
-      <c r="AZ7" s="28"/>
-      <c r="BA7" s="28"/>
-      <c r="BB7" s="28"/>
-      <c r="BC7" s="28"/>
-      <c r="BD7" s="28"/>
-      <c r="BE7" s="28"/>
-      <c r="BF7" s="28"/>
-      <c r="BG7" s="28"/>
-      <c r="BH7" s="28"/>
-      <c r="BI7" s="28"/>
-      <c r="BJ7" s="28"/>
-      <c r="BK7" s="28"/>
-      <c r="BL7" s="28"/>
-      <c r="BM7" s="28"/>
-      <c r="BN7" s="28"/>
-      <c r="BO7" s="28"/>
-      <c r="BP7" s="28"/>
-      <c r="BQ7" s="28"/>
-      <c r="BR7" s="28"/>
-      <c r="BS7" s="28"/>
-      <c r="BT7" s="28"/>
-      <c r="BU7" s="28"/>
-      <c r="BV7" s="28"/>
-      <c r="BW7" s="28"/>
-      <c r="BX7" s="28"/>
-      <c r="BY7" s="28"/>
-      <c r="BZ7" s="28"/>
-      <c r="CA7" s="28"/>
-      <c r="CB7" s="28"/>
-      <c r="CC7" s="28"/>
-      <c r="CD7" s="28"/>
-      <c r="CE7" s="28"/>
-      <c r="CF7" s="28"/>
-      <c r="CG7" s="28"/>
-      <c r="CH7" s="28"/>
-      <c r="CI7" s="28"/>
-      <c r="CJ7" s="28"/>
-      <c r="CK7" s="28"/>
-      <c r="CL7" s="28"/>
-      <c r="CM7" s="28"/>
-      <c r="CN7" s="28"/>
-      <c r="CO7" s="28"/>
-      <c r="CP7" s="28"/>
-      <c r="CQ7" s="28"/>
-      <c r="CR7" s="28"/>
-      <c r="CS7" s="28"/>
-      <c r="CT7" s="28"/>
-      <c r="CU7" s="28"/>
-      <c r="CV7" s="28"/>
-      <c r="CW7" s="28"/>
-      <c r="CX7" s="28"/>
-      <c r="CY7" s="28"/>
-      <c r="CZ7" s="28"/>
-      <c r="DA7" s="28"/>
-      <c r="DB7" s="28"/>
-      <c r="DC7" s="28"/>
-      <c r="DD7" s="28"/>
-      <c r="DE7" s="28"/>
-      <c r="DF7" s="28"/>
-      <c r="DG7" s="28"/>
-      <c r="DH7" s="28"/>
-      <c r="DI7" s="28"/>
-      <c r="DJ7" s="28"/>
-      <c r="DK7" s="28"/>
-      <c r="DL7" s="28"/>
-      <c r="DM7" s="28"/>
-      <c r="DN7" s="28"/>
-      <c r="DO7" s="28"/>
-      <c r="DP7" s="28"/>
-      <c r="DQ7" s="28"/>
-      <c r="DR7" s="28"/>
-      <c r="DS7" s="28"/>
-      <c r="DT7" s="28"/>
-      <c r="DU7" s="28"/>
-      <c r="DV7" s="28"/>
-      <c r="DW7" s="28"/>
-      <c r="DX7" s="28"/>
-      <c r="DY7" s="28"/>
-      <c r="DZ7" s="28"/>
-      <c r="EA7" s="28"/>
-      <c r="EB7" s="28"/>
-      <c r="EC7" s="28"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="34"/>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="26"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="29"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="29"/>
+      <c r="W7" s="29"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="29"/>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="29"/>
+      <c r="AC7" s="30"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="29"/>
+      <c r="AF7" s="29"/>
+      <c r="AG7" s="29"/>
+      <c r="AH7" s="29"/>
+      <c r="AI7" s="29"/>
+      <c r="AJ7" s="29"/>
+      <c r="AK7" s="29"/>
+      <c r="AL7" s="29"/>
+      <c r="AM7" s="29"/>
+      <c r="AN7" s="29"/>
+      <c r="AO7" s="29"/>
+      <c r="AP7" s="29"/>
+      <c r="AQ7" s="29"/>
+      <c r="AR7" s="29"/>
+      <c r="AS7" s="29"/>
+      <c r="AT7" s="29"/>
+      <c r="AU7" s="29"/>
+      <c r="AV7" s="29"/>
+      <c r="AW7" s="29"/>
+      <c r="AX7" s="29"/>
+      <c r="AY7" s="29"/>
+      <c r="AZ7" s="29"/>
+      <c r="BA7" s="29"/>
+      <c r="BB7" s="29"/>
+      <c r="BC7" s="29"/>
+      <c r="BD7" s="29"/>
+      <c r="BE7" s="29"/>
+      <c r="BF7" s="29"/>
+      <c r="BG7" s="29"/>
+      <c r="BH7" s="29"/>
+      <c r="BI7" s="29"/>
+      <c r="BJ7" s="29"/>
+      <c r="BK7" s="29"/>
+      <c r="BL7" s="29"/>
+      <c r="BM7" s="29"/>
+      <c r="BN7" s="29"/>
+      <c r="BO7" s="29"/>
+      <c r="BP7" s="29"/>
+      <c r="BQ7" s="29"/>
+      <c r="BR7" s="29"/>
+      <c r="BS7" s="29"/>
+      <c r="BT7" s="29"/>
+      <c r="BU7" s="29"/>
+      <c r="BV7" s="29"/>
+      <c r="BW7" s="29"/>
+      <c r="BX7" s="29"/>
+      <c r="BY7" s="29"/>
+      <c r="BZ7" s="29"/>
+      <c r="CA7" s="29"/>
+      <c r="CB7" s="29"/>
+      <c r="CC7" s="29"/>
+      <c r="CD7" s="29"/>
+      <c r="CE7" s="29"/>
+      <c r="CF7" s="29"/>
+      <c r="CG7" s="29"/>
+      <c r="CH7" s="29"/>
+      <c r="CI7" s="29"/>
+      <c r="CJ7" s="29"/>
+      <c r="CK7" s="29"/>
+      <c r="CL7" s="29"/>
+      <c r="CM7" s="29"/>
+      <c r="CN7" s="29"/>
+      <c r="CO7" s="29"/>
+      <c r="CP7" s="29"/>
+      <c r="CQ7" s="29"/>
+      <c r="CR7" s="29"/>
+      <c r="CS7" s="29"/>
+      <c r="CT7" s="29"/>
+      <c r="CU7" s="29"/>
+      <c r="CV7" s="29"/>
+      <c r="CW7" s="29"/>
+      <c r="CX7" s="29"/>
+      <c r="CY7" s="29"/>
+      <c r="CZ7" s="29"/>
+      <c r="DA7" s="29"/>
+      <c r="DB7" s="29"/>
+      <c r="DC7" s="29"/>
+      <c r="DD7" s="29"/>
+      <c r="DE7" s="29"/>
+      <c r="DF7" s="29"/>
+      <c r="DG7" s="29"/>
+      <c r="DH7" s="29"/>
+      <c r="DI7" s="29"/>
+      <c r="DJ7" s="29"/>
+      <c r="DK7" s="29"/>
+      <c r="DL7" s="29"/>
+      <c r="DM7" s="29"/>
+      <c r="DN7" s="29"/>
+      <c r="DO7" s="29"/>
+      <c r="DP7" s="29"/>
+      <c r="DQ7" s="29"/>
+      <c r="DR7" s="29"/>
+      <c r="DS7" s="29"/>
+      <c r="DT7" s="29"/>
+      <c r="DU7" s="29"/>
+      <c r="DV7" s="29"/>
+      <c r="DW7" s="29"/>
+      <c r="DX7" s="29"/>
+      <c r="DY7" s="29"/>
+      <c r="DZ7" s="29"/>
+      <c r="EA7" s="29"/>
+      <c r="EB7" s="29"/>
+      <c r="EC7" s="29"/>
     </row>
     <row r="8" spans="1:133" ht="19" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
@@ -2218,12 +2121,12 @@
         <v>10</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="20">
+      <c r="G9" s="23">
         <v>46272</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
-      <c r="J9" s="20"/>
+      <c r="J9" s="23"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5">
@@ -2235,21 +2138,21 @@
         <v>15</v>
       </c>
       <c r="Q9" s="8"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="13"/>
-      <c r="U9" s="17"/>
-      <c r="V9" s="17"/>
-      <c r="W9" s="17"/>
-      <c r="X9" s="17"/>
-      <c r="Y9" s="17"/>
-      <c r="Z9" s="13"/>
-      <c r="AA9" s="13"/>
-      <c r="AB9" s="13"/>
-      <c r="AC9" s="13"/>
-      <c r="AD9" s="13"/>
-      <c r="AE9" s="13"/>
-      <c r="AF9" s="13"/>
-      <c r="AG9" s="13"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="15"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="19"/>
+      <c r="Y9" s="19"/>
+      <c r="Z9" s="15"/>
+      <c r="AA9" s="15"/>
+      <c r="AB9" s="15"/>
+      <c r="AC9" s="15"/>
+      <c r="AD9" s="15"/>
+      <c r="AE9" s="15"/>
+      <c r="AF9" s="15"/>
+      <c r="AG9" s="15"/>
       <c r="AH9" s="11"/>
       <c r="AI9" s="11"/>
       <c r="AJ9" s="11"/>
@@ -2371,11 +2274,11 @@
       <c r="Q10" s="8"/>
       <c r="S10" s="16"/>
       <c r="T10" s="16"/>
-      <c r="U10" s="18"/>
-      <c r="V10" s="18"/>
-      <c r="W10" s="18"/>
-      <c r="X10" s="18"/>
-      <c r="Y10" s="18"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="20"/>
       <c r="Z10" s="16"/>
       <c r="AA10" s="16"/>
       <c r="AB10" s="16"/>
@@ -2498,12 +2401,12 @@
         <v>12</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="G11" s="20">
+      <c r="G11" s="23">
         <v>46272</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
-      <c r="J11" s="20">
+      <c r="J11" s="23">
         <v>46272</v>
       </c>
       <c r="K11" s="5"/>
@@ -2517,13 +2420,13 @@
         <v>16</v>
       </c>
       <c r="Q11" s="8"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="13"/>
-      <c r="U11" s="23"/>
-      <c r="V11" s="23"/>
-      <c r="W11" s="23"/>
-      <c r="X11" s="23"/>
-      <c r="Y11" s="26"/>
+      <c r="S11" s="15"/>
+      <c r="T11" s="15"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="17"/>
+      <c r="W11" s="17"/>
+      <c r="X11" s="17"/>
+      <c r="Y11" s="27"/>
       <c r="Z11" s="11"/>
       <c r="AA11" s="11"/>
       <c r="AB11" s="11"/>
@@ -2653,11 +2556,11 @@
       <c r="Q12" s="8"/>
       <c r="S12" s="16"/>
       <c r="T12" s="16"/>
-      <c r="U12" s="24"/>
-      <c r="V12" s="24"/>
-      <c r="W12" s="24"/>
-      <c r="X12" s="24"/>
-      <c r="Y12" s="27"/>
+      <c r="U12" s="18"/>
+      <c r="V12" s="18"/>
+      <c r="W12" s="18"/>
+      <c r="X12" s="18"/>
+      <c r="Y12" s="28"/>
       <c r="Z12" s="12"/>
       <c r="AA12" s="12"/>
       <c r="AB12" s="12"/>
@@ -2780,12 +2683,12 @@
         <v>14</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="20">
+      <c r="G13" s="23">
         <v>46272</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
-      <c r="J13" s="20">
+      <c r="J13" s="23">
         <v>46272</v>
       </c>
       <c r="K13" s="5"/>
@@ -2799,16 +2702,16 @@
         <v>16</v>
       </c>
       <c r="Q13" s="8"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="23"/>
+      <c r="S13" s="24"/>
+      <c r="T13" s="24"/>
+      <c r="U13" s="17"/>
+      <c r="V13" s="17"/>
       <c r="W13" s="11"/>
       <c r="X13" s="11"/>
       <c r="Y13" s="11"/>
       <c r="Z13" s="11"/>
       <c r="AA13" s="11"/>
-      <c r="AB13" s="23"/>
+      <c r="AB13" s="17"/>
       <c r="AC13" s="11"/>
       <c r="AD13" s="11"/>
       <c r="AE13" s="11"/>
@@ -2933,16 +2836,16 @@
       <c r="O14" s="5"/>
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
-      <c r="S14" s="22"/>
-      <c r="T14" s="22"/>
-      <c r="U14" s="24"/>
-      <c r="V14" s="24"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="18"/>
+      <c r="V14" s="18"/>
       <c r="W14" s="12"/>
       <c r="X14" s="12"/>
       <c r="Y14" s="12"/>
       <c r="Z14" s="12"/>
       <c r="AA14" s="12"/>
-      <c r="AB14" s="24"/>
+      <c r="AB14" s="18"/>
       <c r="AC14" s="12"/>
       <c r="AD14" s="12"/>
       <c r="AE14" s="12"/>
@@ -3062,12 +2965,12 @@
         <v>14</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="20">
+      <c r="G15" s="23">
         <v>46272</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="31"/>
+      <c r="J15" s="32"/>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
       <c r="M15" s="5">
@@ -3079,13 +2982,13 @@
         <v>16</v>
       </c>
       <c r="Q15" s="8"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13"/>
+      <c r="S15" s="15"/>
+      <c r="T15" s="15"/>
       <c r="U15" s="11"/>
       <c r="V15" s="11"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="23"/>
-      <c r="Y15" s="23"/>
+      <c r="W15" s="17"/>
+      <c r="X15" s="17"/>
+      <c r="Y15" s="17"/>
       <c r="Z15" s="11"/>
       <c r="AA15" s="11"/>
       <c r="AB15" s="11"/>
@@ -3217,9 +3120,9 @@
       <c r="T16" s="16"/>
       <c r="U16" s="12"/>
       <c r="V16" s="12"/>
-      <c r="W16" s="24"/>
-      <c r="X16" s="24"/>
-      <c r="Y16" s="24"/>
+      <c r="W16" s="18"/>
+      <c r="X16" s="18"/>
+      <c r="Y16" s="18"/>
       <c r="Z16" s="12"/>
       <c r="AA16" s="12"/>
       <c r="AB16" s="12"/>
@@ -3366,7 +3269,7 @@
         <v>10</v>
       </c>
       <c r="F18" s="5"/>
-      <c r="G18" s="20"/>
+      <c r="G18" s="23"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
@@ -3379,21 +3282,21 @@
         <v>15</v>
       </c>
       <c r="Q18" s="8"/>
-      <c r="S18" s="13"/>
-      <c r="T18" s="13"/>
-      <c r="U18" s="13"/>
-      <c r="V18" s="13"/>
-      <c r="W18" s="13"/>
-      <c r="X18" s="13"/>
-      <c r="Y18" s="13"/>
-      <c r="Z18" s="17"/>
-      <c r="AA18" s="17"/>
-      <c r="AB18" s="17"/>
-      <c r="AC18" s="17"/>
-      <c r="AD18" s="17"/>
-      <c r="AE18" s="34"/>
-      <c r="AF18" s="34"/>
-      <c r="AG18" s="34"/>
+      <c r="S18" s="15"/>
+      <c r="T18" s="15"/>
+      <c r="U18" s="15"/>
+      <c r="V18" s="15"/>
+      <c r="W18" s="15"/>
+      <c r="X18" s="15"/>
+      <c r="Y18" s="15"/>
+      <c r="Z18" s="19"/>
+      <c r="AA18" s="19"/>
+      <c r="AB18" s="19"/>
+      <c r="AC18" s="19"/>
+      <c r="AD18" s="19"/>
+      <c r="AE18" s="21"/>
+      <c r="AF18" s="21"/>
+      <c r="AG18" s="21"/>
       <c r="AH18" s="11"/>
       <c r="AI18" s="11"/>
       <c r="AJ18" s="11"/>
@@ -3520,14 +3423,14 @@
       <c r="W19" s="16"/>
       <c r="X19" s="16"/>
       <c r="Y19" s="16"/>
-      <c r="Z19" s="18"/>
-      <c r="AA19" s="18"/>
-      <c r="AB19" s="18"/>
-      <c r="AC19" s="18"/>
-      <c r="AD19" s="18"/>
-      <c r="AE19" s="35"/>
-      <c r="AF19" s="35"/>
-      <c r="AG19" s="35"/>
+      <c r="Z19" s="20"/>
+      <c r="AA19" s="20"/>
+      <c r="AB19" s="20"/>
+      <c r="AC19" s="20"/>
+      <c r="AD19" s="20"/>
+      <c r="AE19" s="12"/>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
       <c r="AH19" s="12"/>
       <c r="AI19" s="12"/>
       <c r="AJ19" s="12"/>
@@ -3642,7 +3545,7 @@
         <v>54</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="20"/>
+      <c r="G20" s="23"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
@@ -3652,21 +3555,21 @@
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
       <c r="P20" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q20" s="8"/>
-      <c r="S20" s="13"/>
-      <c r="T20" s="13"/>
+      <c r="S20" s="15"/>
+      <c r="T20" s="15"/>
       <c r="U20" s="11"/>
       <c r="V20" s="11"/>
       <c r="W20" s="11"/>
       <c r="X20" s="11"/>
       <c r="Y20" s="11"/>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="14"/>
+      <c r="Z20" s="17"/>
+      <c r="AA20" s="17"/>
       <c r="AB20" s="11"/>
-      <c r="AC20" s="11"/>
-      <c r="AD20" s="11"/>
+      <c r="AC20" s="17"/>
+      <c r="AD20" s="17"/>
       <c r="AE20" s="11"/>
       <c r="AF20" s="11"/>
       <c r="AG20" s="11"/>
@@ -3796,11 +3699,11 @@
       <c r="W21" s="12"/>
       <c r="X21" s="12"/>
       <c r="Y21" s="12"/>
-      <c r="Z21" s="15"/>
-      <c r="AA21" s="15"/>
+      <c r="Z21" s="18"/>
+      <c r="AA21" s="18"/>
       <c r="AB21" s="12"/>
-      <c r="AC21" s="12"/>
-      <c r="AD21" s="12"/>
+      <c r="AC21" s="18"/>
+      <c r="AD21" s="18"/>
       <c r="AE21" s="12"/>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -3914,23 +3817,25 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
+      <c r="E22" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" s="5"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
       <c r="P22" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q22" s="8"/>
-      <c r="S22" s="13"/>
-      <c r="T22" s="13"/>
+      <c r="S22" s="15"/>
+      <c r="T22" s="15"/>
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
       <c r="W22" s="11"/>
@@ -3941,7 +3846,7 @@
       <c r="AB22" s="11"/>
       <c r="AC22" s="11"/>
       <c r="AD22" s="11"/>
-      <c r="AE22" s="11"/>
+      <c r="AE22" s="13"/>
       <c r="AF22" s="11"/>
       <c r="AG22" s="11"/>
       <c r="AH22" s="11"/>
@@ -4050,17 +3955,17 @@
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
       <c r="S23" s="16"/>
@@ -4075,7 +3980,7 @@
       <c r="AB23" s="12"/>
       <c r="AC23" s="12"/>
       <c r="AD23" s="12"/>
-      <c r="AE23" s="12"/>
+      <c r="AE23" s="14"/>
       <c r="AF23" s="12"/>
       <c r="AG23" s="12"/>
       <c r="AH23" s="12"/>
@@ -4188,23 +4093,23 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
       <c r="P24" s="8" t="s">
         <v>17</v>
       </c>
       <c r="Q24" s="8"/>
-      <c r="S24" s="13"/>
-      <c r="T24" s="13"/>
+      <c r="S24" s="15"/>
+      <c r="T24" s="15"/>
       <c r="U24" s="11"/>
       <c r="V24" s="11"/>
       <c r="W24" s="11"/>
@@ -4324,17 +4229,17 @@
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
       <c r="P25" s="8"/>
       <c r="Q25" s="8"/>
       <c r="S25" s="16"/>
@@ -4462,36 +4367,36 @@
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19"/>
-      <c r="O26" s="19"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
       <c r="P26" s="8" t="s">
         <v>17</v>
       </c>
       <c r="Q26" s="8"/>
-      <c r="S26" s="13"/>
-      <c r="T26" s="13"/>
-      <c r="U26" s="13"/>
-      <c r="V26" s="13"/>
-      <c r="W26" s="13"/>
-      <c r="X26" s="13"/>
-      <c r="Y26" s="13"/>
-      <c r="Z26" s="13"/>
-      <c r="AA26" s="13"/>
-      <c r="AB26" s="13"/>
-      <c r="AC26" s="13"/>
-      <c r="AD26" s="13"/>
-      <c r="AE26" s="13"/>
-      <c r="AF26" s="13"/>
-      <c r="AG26" s="13"/>
+      <c r="S26" s="15"/>
+      <c r="T26" s="15"/>
+      <c r="U26" s="15"/>
+      <c r="V26" s="15"/>
+      <c r="W26" s="15"/>
+      <c r="X26" s="15"/>
+      <c r="Y26" s="15"/>
+      <c r="Z26" s="15"/>
+      <c r="AA26" s="15"/>
+      <c r="AB26" s="15"/>
+      <c r="AC26" s="15"/>
+      <c r="AD26" s="15"/>
+      <c r="AE26" s="15"/>
+      <c r="AF26" s="15"/>
+      <c r="AG26" s="15"/>
       <c r="AH26" s="11"/>
       <c r="AI26" s="11"/>
       <c r="AJ26" s="11"/>
@@ -4598,17 +4503,17 @@
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
       <c r="P27" s="8"/>
       <c r="Q27" s="8"/>
       <c r="S27" s="16"/>
@@ -4740,34 +4645,34 @@
         <v>12</v>
       </c>
       <c r="F28" s="5"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
       <c r="P28" s="8" t="s">
         <v>15</v>
       </c>
       <c r="Q28" s="8"/>
-      <c r="S28" s="13"/>
-      <c r="T28" s="13"/>
+      <c r="S28" s="15"/>
+      <c r="T28" s="15"/>
       <c r="U28" s="11"/>
       <c r="V28" s="11"/>
       <c r="W28" s="11"/>
       <c r="X28" s="11"/>
       <c r="Y28" s="11"/>
-      <c r="Z28" s="14"/>
-      <c r="AA28" s="14"/>
-      <c r="AB28" s="14"/>
-      <c r="AC28" s="14"/>
-      <c r="AD28" s="14"/>
-      <c r="AE28" s="14"/>
-      <c r="AF28" s="14"/>
-      <c r="AG28" s="14"/>
+      <c r="Z28" s="13"/>
+      <c r="AA28" s="13"/>
+      <c r="AB28" s="13"/>
+      <c r="AC28" s="13"/>
+      <c r="AD28" s="13"/>
+      <c r="AE28" s="11"/>
+      <c r="AF28" s="11"/>
+      <c r="AG28" s="11"/>
       <c r="AH28" s="11"/>
       <c r="AI28" s="11"/>
       <c r="AJ28" s="11"/>
@@ -4876,15 +4781,15 @@
       <c r="D29" s="6"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19"/>
-      <c r="O29" s="19"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
       <c r="P29" s="8"/>
       <c r="Q29" s="8"/>
       <c r="S29" s="16"/>
@@ -4894,14 +4799,14 @@
       <c r="W29" s="12"/>
       <c r="X29" s="12"/>
       <c r="Y29" s="12"/>
-      <c r="Z29" s="15"/>
-      <c r="AA29" s="15"/>
-      <c r="AB29" s="15"/>
-      <c r="AC29" s="15"/>
-      <c r="AD29" s="15"/>
-      <c r="AE29" s="15"/>
-      <c r="AF29" s="15"/>
-      <c r="AG29" s="15"/>
+      <c r="Z29" s="14"/>
+      <c r="AA29" s="14"/>
+      <c r="AB29" s="14"/>
+      <c r="AC29" s="14"/>
+      <c r="AD29" s="14"/>
+      <c r="AE29" s="12"/>
+      <c r="AF29" s="12"/>
+      <c r="AG29" s="12"/>
       <c r="AH29" s="12"/>
       <c r="AI29" s="12"/>
       <c r="AJ29" s="12"/>
@@ -5016,34 +4921,34 @@
         <v>8</v>
       </c>
       <c r="F30" s="5"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
       <c r="P30" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q30" s="8"/>
-      <c r="S30" s="36"/>
-      <c r="T30" s="13"/>
-      <c r="U30" s="13"/>
-      <c r="V30" s="13"/>
-      <c r="W30" s="13"/>
-      <c r="X30" s="13"/>
-      <c r="Y30" s="13"/>
-      <c r="Z30" s="14"/>
-      <c r="AA30" s="14"/>
-      <c r="AB30" s="14"/>
-      <c r="AC30" s="14"/>
-      <c r="AD30" s="14"/>
-      <c r="AE30" s="14"/>
-      <c r="AF30" s="14"/>
-      <c r="AG30" s="14"/>
+      <c r="S30" s="15"/>
+      <c r="T30" s="15"/>
+      <c r="U30" s="15"/>
+      <c r="V30" s="15"/>
+      <c r="W30" s="15"/>
+      <c r="X30" s="15"/>
+      <c r="Y30" s="15"/>
+      <c r="Z30" s="17"/>
+      <c r="AA30" s="17"/>
+      <c r="AB30" s="17"/>
+      <c r="AC30" s="17"/>
+      <c r="AD30" s="17"/>
+      <c r="AE30" s="17"/>
+      <c r="AF30" s="11"/>
+      <c r="AG30" s="11"/>
       <c r="AH30" s="11"/>
       <c r="AI30" s="11"/>
       <c r="AJ30" s="11"/>
@@ -5152,32 +5057,32 @@
       <c r="D31" s="6"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19"/>
-      <c r="O31" s="19"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
       <c r="P31" s="8"/>
       <c r="Q31" s="8"/>
-      <c r="S31" s="37"/>
+      <c r="S31" s="16"/>
       <c r="T31" s="16"/>
       <c r="U31" s="16"/>
       <c r="V31" s="16"/>
       <c r="W31" s="16"/>
       <c r="X31" s="16"/>
       <c r="Y31" s="16"/>
-      <c r="Z31" s="15"/>
-      <c r="AA31" s="15"/>
-      <c r="AB31" s="15"/>
-      <c r="AC31" s="15"/>
-      <c r="AD31" s="15"/>
-      <c r="AE31" s="15"/>
-      <c r="AF31" s="15"/>
-      <c r="AG31" s="15"/>
+      <c r="Z31" s="18"/>
+      <c r="AA31" s="18"/>
+      <c r="AB31" s="18"/>
+      <c r="AC31" s="18"/>
+      <c r="AD31" s="18"/>
+      <c r="AE31" s="18"/>
+      <c r="AF31" s="12"/>
+      <c r="AG31" s="12"/>
       <c r="AH31" s="12"/>
       <c r="AI31" s="12"/>
       <c r="AJ31" s="12"/>
@@ -5329,35 +5234,35 @@
         <v>17</v>
       </c>
       <c r="Q33" s="8"/>
-      <c r="S33" s="36"/>
-      <c r="T33" s="36"/>
-      <c r="U33" s="36"/>
-      <c r="V33" s="36"/>
-      <c r="W33" s="36"/>
-      <c r="X33" s="36"/>
-      <c r="Y33" s="36"/>
-      <c r="Z33" s="36"/>
-      <c r="AA33" s="36"/>
-      <c r="AB33" s="36"/>
-      <c r="AC33" s="36"/>
-      <c r="AD33" s="36"/>
-      <c r="AE33" s="34"/>
-      <c r="AF33" s="34"/>
-      <c r="AG33" s="34"/>
-      <c r="AH33" s="38"/>
-      <c r="AI33" s="38"/>
-      <c r="AJ33" s="38"/>
-      <c r="AK33" s="38"/>
-      <c r="AL33" s="38"/>
-      <c r="AM33" s="38"/>
-      <c r="AN33" s="38"/>
-      <c r="AO33" s="38"/>
-      <c r="AP33" s="38"/>
-      <c r="AQ33" s="38"/>
-      <c r="AR33" s="38"/>
-      <c r="AS33" s="38"/>
-      <c r="AT33" s="38"/>
-      <c r="AU33" s="38"/>
+      <c r="S33" s="15"/>
+      <c r="T33" s="15"/>
+      <c r="U33" s="15"/>
+      <c r="V33" s="15"/>
+      <c r="W33" s="15"/>
+      <c r="X33" s="15"/>
+      <c r="Y33" s="15"/>
+      <c r="Z33" s="15"/>
+      <c r="AA33" s="15"/>
+      <c r="AB33" s="15"/>
+      <c r="AC33" s="15"/>
+      <c r="AD33" s="15"/>
+      <c r="AE33" s="21"/>
+      <c r="AF33" s="21"/>
+      <c r="AG33" s="21"/>
+      <c r="AH33" s="11"/>
+      <c r="AI33" s="11"/>
+      <c r="AJ33" s="11"/>
+      <c r="AK33" s="11"/>
+      <c r="AL33" s="11"/>
+      <c r="AM33" s="11"/>
+      <c r="AN33" s="11"/>
+      <c r="AO33" s="11"/>
+      <c r="AP33" s="11"/>
+      <c r="AQ33" s="11"/>
+      <c r="AR33" s="11"/>
+      <c r="AS33" s="11"/>
+      <c r="AT33" s="11"/>
+      <c r="AU33" s="11"/>
       <c r="AV33" s="11"/>
       <c r="AW33" s="11"/>
       <c r="AX33" s="11"/>
@@ -5463,35 +5368,35 @@
       <c r="O34" s="7"/>
       <c r="P34" s="8"/>
       <c r="Q34" s="8"/>
-      <c r="S34" s="37"/>
-      <c r="T34" s="37"/>
-      <c r="U34" s="37"/>
-      <c r="V34" s="37"/>
-      <c r="W34" s="37"/>
-      <c r="X34" s="37"/>
-      <c r="Y34" s="37"/>
-      <c r="Z34" s="37"/>
-      <c r="AA34" s="37"/>
-      <c r="AB34" s="37"/>
-      <c r="AC34" s="37"/>
-      <c r="AD34" s="37"/>
-      <c r="AE34" s="35"/>
-      <c r="AF34" s="35"/>
-      <c r="AG34" s="35"/>
-      <c r="AH34" s="35"/>
-      <c r="AI34" s="35"/>
-      <c r="AJ34" s="35"/>
-      <c r="AK34" s="35"/>
-      <c r="AL34" s="35"/>
-      <c r="AM34" s="35"/>
-      <c r="AN34" s="35"/>
-      <c r="AO34" s="35"/>
-      <c r="AP34" s="35"/>
-      <c r="AQ34" s="35"/>
-      <c r="AR34" s="35"/>
-      <c r="AS34" s="35"/>
-      <c r="AT34" s="35"/>
-      <c r="AU34" s="35"/>
+      <c r="S34" s="16"/>
+      <c r="T34" s="16"/>
+      <c r="U34" s="16"/>
+      <c r="V34" s="16"/>
+      <c r="W34" s="16"/>
+      <c r="X34" s="16"/>
+      <c r="Y34" s="16"/>
+      <c r="Z34" s="16"/>
+      <c r="AA34" s="16"/>
+      <c r="AB34" s="16"/>
+      <c r="AC34" s="16"/>
+      <c r="AD34" s="16"/>
+      <c r="AE34" s="12"/>
+      <c r="AF34" s="12"/>
+      <c r="AG34" s="12"/>
+      <c r="AH34" s="12"/>
+      <c r="AI34" s="12"/>
+      <c r="AJ34" s="12"/>
+      <c r="AK34" s="12"/>
+      <c r="AL34" s="12"/>
+      <c r="AM34" s="12"/>
+      <c r="AN34" s="12"/>
+      <c r="AO34" s="12"/>
+      <c r="AP34" s="12"/>
+      <c r="AQ34" s="12"/>
+      <c r="AR34" s="12"/>
+      <c r="AS34" s="12"/>
+      <c r="AT34" s="12"/>
+      <c r="AU34" s="12"/>
       <c r="AV34" s="12"/>
       <c r="AW34" s="12"/>
       <c r="AX34" s="12"/>
@@ -5603,35 +5508,35 @@
         <v>17</v>
       </c>
       <c r="Q35" s="8"/>
-      <c r="S35" s="36"/>
-      <c r="T35" s="36"/>
-      <c r="U35" s="38"/>
-      <c r="V35" s="38"/>
-      <c r="W35" s="38"/>
-      <c r="X35" s="38"/>
-      <c r="Y35" s="38"/>
-      <c r="Z35" s="38"/>
-      <c r="AA35" s="38"/>
-      <c r="AB35" s="38"/>
-      <c r="AC35" s="38"/>
-      <c r="AD35" s="38"/>
-      <c r="AE35" s="38"/>
-      <c r="AF35" s="38"/>
-      <c r="AG35" s="38"/>
-      <c r="AH35" s="38"/>
-      <c r="AI35" s="38"/>
-      <c r="AJ35" s="38"/>
-      <c r="AK35" s="38"/>
-      <c r="AL35" s="38"/>
-      <c r="AM35" s="38"/>
-      <c r="AN35" s="38"/>
-      <c r="AO35" s="38"/>
-      <c r="AP35" s="38"/>
-      <c r="AQ35" s="38"/>
-      <c r="AR35" s="38"/>
-      <c r="AS35" s="38"/>
-      <c r="AT35" s="38"/>
-      <c r="AU35" s="38"/>
+      <c r="S35" s="15"/>
+      <c r="T35" s="15"/>
+      <c r="U35" s="11"/>
+      <c r="V35" s="11"/>
+      <c r="W35" s="11"/>
+      <c r="X35" s="11"/>
+      <c r="Y35" s="11"/>
+      <c r="Z35" s="11"/>
+      <c r="AA35" s="11"/>
+      <c r="AB35" s="11"/>
+      <c r="AC35" s="11"/>
+      <c r="AD35" s="11"/>
+      <c r="AE35" s="11"/>
+      <c r="AF35" s="11"/>
+      <c r="AG35" s="11"/>
+      <c r="AH35" s="11"/>
+      <c r="AI35" s="11"/>
+      <c r="AJ35" s="11"/>
+      <c r="AK35" s="11"/>
+      <c r="AL35" s="11"/>
+      <c r="AM35" s="11"/>
+      <c r="AN35" s="11"/>
+      <c r="AO35" s="11"/>
+      <c r="AP35" s="11"/>
+      <c r="AQ35" s="11"/>
+      <c r="AR35" s="11"/>
+      <c r="AS35" s="11"/>
+      <c r="AT35" s="11"/>
+      <c r="AU35" s="11"/>
       <c r="AV35" s="11"/>
       <c r="AW35" s="11"/>
       <c r="AX35" s="11"/>
@@ -5737,35 +5642,35 @@
       <c r="O36" s="7"/>
       <c r="P36" s="8"/>
       <c r="Q36" s="8"/>
-      <c r="S36" s="37"/>
-      <c r="T36" s="37"/>
-      <c r="U36" s="35"/>
-      <c r="V36" s="35"/>
-      <c r="W36" s="35"/>
-      <c r="X36" s="35"/>
-      <c r="Y36" s="35"/>
-      <c r="Z36" s="35"/>
-      <c r="AA36" s="35"/>
-      <c r="AB36" s="35"/>
-      <c r="AC36" s="35"/>
-      <c r="AD36" s="35"/>
-      <c r="AE36" s="35"/>
-      <c r="AF36" s="35"/>
-      <c r="AG36" s="35"/>
-      <c r="AH36" s="35"/>
-      <c r="AI36" s="35"/>
-      <c r="AJ36" s="35"/>
-      <c r="AK36" s="35"/>
-      <c r="AL36" s="35"/>
-      <c r="AM36" s="35"/>
-      <c r="AN36" s="35"/>
-      <c r="AO36" s="35"/>
-      <c r="AP36" s="35"/>
-      <c r="AQ36" s="35"/>
-      <c r="AR36" s="35"/>
-      <c r="AS36" s="35"/>
-      <c r="AT36" s="35"/>
-      <c r="AU36" s="35"/>
+      <c r="S36" s="16"/>
+      <c r="T36" s="16"/>
+      <c r="U36" s="12"/>
+      <c r="V36" s="12"/>
+      <c r="W36" s="12"/>
+      <c r="X36" s="12"/>
+      <c r="Y36" s="12"/>
+      <c r="Z36" s="12"/>
+      <c r="AA36" s="12"/>
+      <c r="AB36" s="12"/>
+      <c r="AC36" s="12"/>
+      <c r="AD36" s="12"/>
+      <c r="AE36" s="12"/>
+      <c r="AF36" s="12"/>
+      <c r="AG36" s="12"/>
+      <c r="AH36" s="12"/>
+      <c r="AI36" s="12"/>
+      <c r="AJ36" s="12"/>
+      <c r="AK36" s="12"/>
+      <c r="AL36" s="12"/>
+      <c r="AM36" s="12"/>
+      <c r="AN36" s="12"/>
+      <c r="AO36" s="12"/>
+      <c r="AP36" s="12"/>
+      <c r="AQ36" s="12"/>
+      <c r="AR36" s="12"/>
+      <c r="AS36" s="12"/>
+      <c r="AT36" s="12"/>
+      <c r="AU36" s="12"/>
       <c r="AV36" s="12"/>
       <c r="AW36" s="12"/>
       <c r="AX36" s="12"/>
@@ -5877,35 +5782,35 @@
         <v>17</v>
       </c>
       <c r="Q37" s="8"/>
-      <c r="S37" s="36"/>
-      <c r="T37" s="36"/>
-      <c r="U37" s="38"/>
-      <c r="V37" s="38"/>
-      <c r="W37" s="38"/>
-      <c r="X37" s="38"/>
-      <c r="Y37" s="38"/>
-      <c r="Z37" s="38"/>
-      <c r="AA37" s="38"/>
-      <c r="AB37" s="38"/>
-      <c r="AC37" s="38"/>
-      <c r="AD37" s="38"/>
-      <c r="AE37" s="38"/>
-      <c r="AF37" s="38"/>
-      <c r="AG37" s="38"/>
-      <c r="AH37" s="38"/>
-      <c r="AI37" s="38"/>
-      <c r="AJ37" s="38"/>
-      <c r="AK37" s="38"/>
-      <c r="AL37" s="38"/>
-      <c r="AM37" s="38"/>
-      <c r="AN37" s="38"/>
-      <c r="AO37" s="38"/>
-      <c r="AP37" s="38"/>
-      <c r="AQ37" s="38"/>
-      <c r="AR37" s="38"/>
-      <c r="AS37" s="38"/>
-      <c r="AT37" s="38"/>
-      <c r="AU37" s="38"/>
+      <c r="S37" s="15"/>
+      <c r="T37" s="15"/>
+      <c r="U37" s="11"/>
+      <c r="V37" s="11"/>
+      <c r="W37" s="11"/>
+      <c r="X37" s="11"/>
+      <c r="Y37" s="11"/>
+      <c r="Z37" s="11"/>
+      <c r="AA37" s="11"/>
+      <c r="AB37" s="11"/>
+      <c r="AC37" s="11"/>
+      <c r="AD37" s="11"/>
+      <c r="AE37" s="11"/>
+      <c r="AF37" s="11"/>
+      <c r="AG37" s="11"/>
+      <c r="AH37" s="11"/>
+      <c r="AI37" s="11"/>
+      <c r="AJ37" s="11"/>
+      <c r="AK37" s="11"/>
+      <c r="AL37" s="11"/>
+      <c r="AM37" s="11"/>
+      <c r="AN37" s="11"/>
+      <c r="AO37" s="11"/>
+      <c r="AP37" s="11"/>
+      <c r="AQ37" s="11"/>
+      <c r="AR37" s="11"/>
+      <c r="AS37" s="11"/>
+      <c r="AT37" s="11"/>
+      <c r="AU37" s="11"/>
       <c r="AV37" s="11"/>
       <c r="AW37" s="11"/>
       <c r="AX37" s="11"/>
@@ -6011,35 +5916,35 @@
       <c r="O38" s="7"/>
       <c r="P38" s="8"/>
       <c r="Q38" s="8"/>
-      <c r="S38" s="37"/>
-      <c r="T38" s="37"/>
-      <c r="U38" s="35"/>
-      <c r="V38" s="35"/>
-      <c r="W38" s="35"/>
-      <c r="X38" s="35"/>
-      <c r="Y38" s="35"/>
-      <c r="Z38" s="35"/>
-      <c r="AA38" s="35"/>
-      <c r="AB38" s="35"/>
-      <c r="AC38" s="35"/>
-      <c r="AD38" s="35"/>
-      <c r="AE38" s="35"/>
-      <c r="AF38" s="35"/>
-      <c r="AG38" s="35"/>
-      <c r="AH38" s="35"/>
-      <c r="AI38" s="35"/>
-      <c r="AJ38" s="35"/>
-      <c r="AK38" s="35"/>
-      <c r="AL38" s="35"/>
-      <c r="AM38" s="35"/>
-      <c r="AN38" s="35"/>
-      <c r="AO38" s="35"/>
-      <c r="AP38" s="35"/>
-      <c r="AQ38" s="35"/>
-      <c r="AR38" s="35"/>
-      <c r="AS38" s="35"/>
-      <c r="AT38" s="35"/>
-      <c r="AU38" s="35"/>
+      <c r="S38" s="16"/>
+      <c r="T38" s="16"/>
+      <c r="U38" s="12"/>
+      <c r="V38" s="12"/>
+      <c r="W38" s="12"/>
+      <c r="X38" s="12"/>
+      <c r="Y38" s="12"/>
+      <c r="Z38" s="12"/>
+      <c r="AA38" s="12"/>
+      <c r="AB38" s="12"/>
+      <c r="AC38" s="12"/>
+      <c r="AD38" s="12"/>
+      <c r="AE38" s="12"/>
+      <c r="AF38" s="12"/>
+      <c r="AG38" s="12"/>
+      <c r="AH38" s="12"/>
+      <c r="AI38" s="12"/>
+      <c r="AJ38" s="12"/>
+      <c r="AK38" s="12"/>
+      <c r="AL38" s="12"/>
+      <c r="AM38" s="12"/>
+      <c r="AN38" s="12"/>
+      <c r="AO38" s="12"/>
+      <c r="AP38" s="12"/>
+      <c r="AQ38" s="12"/>
+      <c r="AR38" s="12"/>
+      <c r="AS38" s="12"/>
+      <c r="AT38" s="12"/>
+      <c r="AU38" s="12"/>
       <c r="AV38" s="12"/>
       <c r="AW38" s="12"/>
       <c r="AX38" s="12"/>
@@ -6151,35 +6056,35 @@
         <v>17</v>
       </c>
       <c r="Q39" s="8"/>
-      <c r="S39" s="36"/>
-      <c r="T39" s="36"/>
-      <c r="U39" s="38"/>
-      <c r="V39" s="38"/>
-      <c r="W39" s="38"/>
-      <c r="X39" s="38"/>
-      <c r="Y39" s="38"/>
-      <c r="Z39" s="38"/>
-      <c r="AA39" s="38"/>
-      <c r="AB39" s="38"/>
-      <c r="AC39" s="38"/>
-      <c r="AD39" s="38"/>
-      <c r="AE39" s="38"/>
-      <c r="AF39" s="38"/>
-      <c r="AG39" s="38"/>
-      <c r="AH39" s="38"/>
-      <c r="AI39" s="38"/>
-      <c r="AJ39" s="38"/>
-      <c r="AK39" s="38"/>
-      <c r="AL39" s="38"/>
-      <c r="AM39" s="38"/>
-      <c r="AN39" s="38"/>
-      <c r="AO39" s="38"/>
-      <c r="AP39" s="38"/>
-      <c r="AQ39" s="38"/>
-      <c r="AR39" s="38"/>
-      <c r="AS39" s="38"/>
-      <c r="AT39" s="38"/>
-      <c r="AU39" s="38"/>
+      <c r="S39" s="15"/>
+      <c r="T39" s="15"/>
+      <c r="U39" s="11"/>
+      <c r="V39" s="11"/>
+      <c r="W39" s="11"/>
+      <c r="X39" s="11"/>
+      <c r="Y39" s="11"/>
+      <c r="Z39" s="11"/>
+      <c r="AA39" s="11"/>
+      <c r="AB39" s="11"/>
+      <c r="AC39" s="11"/>
+      <c r="AD39" s="11"/>
+      <c r="AE39" s="11"/>
+      <c r="AF39" s="11"/>
+      <c r="AG39" s="11"/>
+      <c r="AH39" s="11"/>
+      <c r="AI39" s="11"/>
+      <c r="AJ39" s="11"/>
+      <c r="AK39" s="11"/>
+      <c r="AL39" s="11"/>
+      <c r="AM39" s="11"/>
+      <c r="AN39" s="11"/>
+      <c r="AO39" s="11"/>
+      <c r="AP39" s="11"/>
+      <c r="AQ39" s="11"/>
+      <c r="AR39" s="11"/>
+      <c r="AS39" s="11"/>
+      <c r="AT39" s="11"/>
+      <c r="AU39" s="11"/>
       <c r="AV39" s="11"/>
       <c r="AW39" s="11"/>
       <c r="AX39" s="11"/>
@@ -6285,35 +6190,35 @@
       <c r="O40" s="7"/>
       <c r="P40" s="8"/>
       <c r="Q40" s="8"/>
-      <c r="S40" s="37"/>
-      <c r="T40" s="37"/>
-      <c r="U40" s="35"/>
-      <c r="V40" s="35"/>
-      <c r="W40" s="35"/>
-      <c r="X40" s="35"/>
-      <c r="Y40" s="35"/>
-      <c r="Z40" s="35"/>
-      <c r="AA40" s="35"/>
-      <c r="AB40" s="35"/>
-      <c r="AC40" s="35"/>
-      <c r="AD40" s="35"/>
-      <c r="AE40" s="35"/>
-      <c r="AF40" s="35"/>
-      <c r="AG40" s="35"/>
-      <c r="AH40" s="35"/>
-      <c r="AI40" s="35"/>
-      <c r="AJ40" s="35"/>
-      <c r="AK40" s="35"/>
-      <c r="AL40" s="35"/>
-      <c r="AM40" s="35"/>
-      <c r="AN40" s="35"/>
-      <c r="AO40" s="35"/>
-      <c r="AP40" s="35"/>
-      <c r="AQ40" s="35"/>
-      <c r="AR40" s="35"/>
-      <c r="AS40" s="35"/>
-      <c r="AT40" s="35"/>
-      <c r="AU40" s="35"/>
+      <c r="S40" s="16"/>
+      <c r="T40" s="16"/>
+      <c r="U40" s="12"/>
+      <c r="V40" s="12"/>
+      <c r="W40" s="12"/>
+      <c r="X40" s="12"/>
+      <c r="Y40" s="12"/>
+      <c r="Z40" s="12"/>
+      <c r="AA40" s="12"/>
+      <c r="AB40" s="12"/>
+      <c r="AC40" s="12"/>
+      <c r="AD40" s="12"/>
+      <c r="AE40" s="12"/>
+      <c r="AF40" s="12"/>
+      <c r="AG40" s="12"/>
+      <c r="AH40" s="12"/>
+      <c r="AI40" s="12"/>
+      <c r="AJ40" s="12"/>
+      <c r="AK40" s="12"/>
+      <c r="AL40" s="12"/>
+      <c r="AM40" s="12"/>
+      <c r="AN40" s="12"/>
+      <c r="AO40" s="12"/>
+      <c r="AP40" s="12"/>
+      <c r="AQ40" s="12"/>
+      <c r="AR40" s="12"/>
+      <c r="AS40" s="12"/>
+      <c r="AT40" s="12"/>
+      <c r="AU40" s="12"/>
       <c r="AV40" s="12"/>
       <c r="AW40" s="12"/>
       <c r="AX40" s="12"/>
@@ -6425,35 +6330,35 @@
         <v>17</v>
       </c>
       <c r="Q41" s="8"/>
-      <c r="S41" s="36"/>
-      <c r="T41" s="36"/>
-      <c r="U41" s="36"/>
-      <c r="V41" s="36"/>
-      <c r="W41" s="36"/>
-      <c r="X41" s="36"/>
-      <c r="Y41" s="36"/>
-      <c r="Z41" s="36"/>
-      <c r="AA41" s="36"/>
-      <c r="AB41" s="36"/>
-      <c r="AC41" s="36"/>
-      <c r="AD41" s="36"/>
-      <c r="AE41" s="36"/>
-      <c r="AF41" s="36"/>
-      <c r="AG41" s="36"/>
-      <c r="AH41" s="38"/>
-      <c r="AI41" s="38"/>
-      <c r="AJ41" s="38"/>
-      <c r="AK41" s="38"/>
-      <c r="AL41" s="38"/>
-      <c r="AM41" s="38"/>
-      <c r="AN41" s="38"/>
-      <c r="AO41" s="38"/>
-      <c r="AP41" s="38"/>
-      <c r="AQ41" s="38"/>
-      <c r="AR41" s="38"/>
-      <c r="AS41" s="38"/>
-      <c r="AT41" s="38"/>
-      <c r="AU41" s="38"/>
+      <c r="S41" s="15"/>
+      <c r="T41" s="15"/>
+      <c r="U41" s="15"/>
+      <c r="V41" s="15"/>
+      <c r="W41" s="15"/>
+      <c r="X41" s="15"/>
+      <c r="Y41" s="15"/>
+      <c r="Z41" s="15"/>
+      <c r="AA41" s="15"/>
+      <c r="AB41" s="15"/>
+      <c r="AC41" s="15"/>
+      <c r="AD41" s="15"/>
+      <c r="AE41" s="15"/>
+      <c r="AF41" s="15"/>
+      <c r="AG41" s="15"/>
+      <c r="AH41" s="11"/>
+      <c r="AI41" s="11"/>
+      <c r="AJ41" s="11"/>
+      <c r="AK41" s="11"/>
+      <c r="AL41" s="11"/>
+      <c r="AM41" s="11"/>
+      <c r="AN41" s="11"/>
+      <c r="AO41" s="11"/>
+      <c r="AP41" s="11"/>
+      <c r="AQ41" s="11"/>
+      <c r="AR41" s="11"/>
+      <c r="AS41" s="11"/>
+      <c r="AT41" s="11"/>
+      <c r="AU41" s="11"/>
       <c r="AV41" s="11"/>
       <c r="AW41" s="11"/>
       <c r="AX41" s="11"/>
@@ -6559,35 +6464,35 @@
       <c r="O42" s="7"/>
       <c r="P42" s="8"/>
       <c r="Q42" s="8"/>
-      <c r="S42" s="37"/>
-      <c r="T42" s="37"/>
-      <c r="U42" s="37"/>
-      <c r="V42" s="37"/>
-      <c r="W42" s="37"/>
-      <c r="X42" s="37"/>
-      <c r="Y42" s="37"/>
-      <c r="Z42" s="37"/>
-      <c r="AA42" s="37"/>
-      <c r="AB42" s="37"/>
-      <c r="AC42" s="37"/>
-      <c r="AD42" s="37"/>
-      <c r="AE42" s="37"/>
-      <c r="AF42" s="37"/>
-      <c r="AG42" s="37"/>
-      <c r="AH42" s="35"/>
-      <c r="AI42" s="35"/>
-      <c r="AJ42" s="35"/>
-      <c r="AK42" s="35"/>
-      <c r="AL42" s="35"/>
-      <c r="AM42" s="35"/>
-      <c r="AN42" s="35"/>
-      <c r="AO42" s="35"/>
-      <c r="AP42" s="35"/>
-      <c r="AQ42" s="35"/>
-      <c r="AR42" s="35"/>
-      <c r="AS42" s="35"/>
-      <c r="AT42" s="35"/>
-      <c r="AU42" s="35"/>
+      <c r="S42" s="16"/>
+      <c r="T42" s="16"/>
+      <c r="U42" s="16"/>
+      <c r="V42" s="16"/>
+      <c r="W42" s="16"/>
+      <c r="X42" s="16"/>
+      <c r="Y42" s="16"/>
+      <c r="Z42" s="16"/>
+      <c r="AA42" s="16"/>
+      <c r="AB42" s="16"/>
+      <c r="AC42" s="16"/>
+      <c r="AD42" s="16"/>
+      <c r="AE42" s="16"/>
+      <c r="AF42" s="16"/>
+      <c r="AG42" s="16"/>
+      <c r="AH42" s="12"/>
+      <c r="AI42" s="12"/>
+      <c r="AJ42" s="12"/>
+      <c r="AK42" s="12"/>
+      <c r="AL42" s="12"/>
+      <c r="AM42" s="12"/>
+      <c r="AN42" s="12"/>
+      <c r="AO42" s="12"/>
+      <c r="AP42" s="12"/>
+      <c r="AQ42" s="12"/>
+      <c r="AR42" s="12"/>
+      <c r="AS42" s="12"/>
+      <c r="AT42" s="12"/>
+      <c r="AU42" s="12"/>
       <c r="AV42" s="12"/>
       <c r="AW42" s="12"/>
       <c r="AX42" s="12"/>
@@ -6698,35 +6603,6 @@
       <c r="O43" s="9"/>
       <c r="P43" s="9"/>
       <c r="Q43" s="9"/>
-      <c r="S43" s="39"/>
-      <c r="T43" s="39"/>
-      <c r="U43" s="39"/>
-      <c r="V43" s="39"/>
-      <c r="W43" s="39"/>
-      <c r="X43" s="39"/>
-      <c r="Y43" s="39"/>
-      <c r="Z43" s="39"/>
-      <c r="AA43" s="39"/>
-      <c r="AB43" s="39"/>
-      <c r="AC43" s="39"/>
-      <c r="AD43" s="39"/>
-      <c r="AE43" s="39"/>
-      <c r="AF43" s="39"/>
-      <c r="AG43" s="39"/>
-      <c r="AH43" s="39"/>
-      <c r="AI43" s="39"/>
-      <c r="AJ43" s="39"/>
-      <c r="AK43" s="39"/>
-      <c r="AL43" s="39"/>
-      <c r="AM43" s="39"/>
-      <c r="AN43" s="39"/>
-      <c r="AO43" s="39"/>
-      <c r="AP43" s="39"/>
-      <c r="AQ43" s="39"/>
-      <c r="AR43" s="39"/>
-      <c r="AS43" s="39"/>
-      <c r="AT43" s="39"/>
-      <c r="AU43" s="39"/>
     </row>
     <row r="44" spans="1:133" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
@@ -6752,35 +6628,35 @@
         <v>17</v>
       </c>
       <c r="Q44" s="8"/>
-      <c r="S44" s="36"/>
-      <c r="T44" s="36"/>
-      <c r="U44" s="36"/>
-      <c r="V44" s="36"/>
-      <c r="W44" s="36"/>
-      <c r="X44" s="36"/>
-      <c r="Y44" s="36"/>
-      <c r="Z44" s="36"/>
-      <c r="AA44" s="36"/>
-      <c r="AB44" s="36"/>
-      <c r="AC44" s="36"/>
-      <c r="AD44" s="36"/>
-      <c r="AE44" s="34"/>
-      <c r="AF44" s="34"/>
-      <c r="AG44" s="34"/>
-      <c r="AH44" s="38"/>
-      <c r="AI44" s="38"/>
-      <c r="AJ44" s="38"/>
-      <c r="AK44" s="38"/>
-      <c r="AL44" s="38"/>
-      <c r="AM44" s="38"/>
-      <c r="AN44" s="38"/>
-      <c r="AO44" s="38"/>
-      <c r="AP44" s="38"/>
-      <c r="AQ44" s="38"/>
-      <c r="AR44" s="38"/>
-      <c r="AS44" s="38"/>
-      <c r="AT44" s="38"/>
-      <c r="AU44" s="38"/>
+      <c r="S44" s="15"/>
+      <c r="T44" s="15"/>
+      <c r="U44" s="15"/>
+      <c r="V44" s="15"/>
+      <c r="W44" s="15"/>
+      <c r="X44" s="15"/>
+      <c r="Y44" s="15"/>
+      <c r="Z44" s="15"/>
+      <c r="AA44" s="15"/>
+      <c r="AB44" s="15"/>
+      <c r="AC44" s="15"/>
+      <c r="AD44" s="15"/>
+      <c r="AE44" s="21"/>
+      <c r="AF44" s="21"/>
+      <c r="AG44" s="21"/>
+      <c r="AH44" s="11"/>
+      <c r="AI44" s="11"/>
+      <c r="AJ44" s="11"/>
+      <c r="AK44" s="11"/>
+      <c r="AL44" s="11"/>
+      <c r="AM44" s="11"/>
+      <c r="AN44" s="11"/>
+      <c r="AO44" s="11"/>
+      <c r="AP44" s="11"/>
+      <c r="AQ44" s="11"/>
+      <c r="AR44" s="11"/>
+      <c r="AS44" s="11"/>
+      <c r="AT44" s="11"/>
+      <c r="AU44" s="11"/>
       <c r="AV44" s="11"/>
       <c r="AW44" s="11"/>
       <c r="AX44" s="11"/>
@@ -6886,35 +6762,35 @@
       <c r="O45" s="7"/>
       <c r="P45" s="8"/>
       <c r="Q45" s="8"/>
-      <c r="S45" s="37"/>
-      <c r="T45" s="37"/>
-      <c r="U45" s="37"/>
-      <c r="V45" s="37"/>
-      <c r="W45" s="37"/>
-      <c r="X45" s="37"/>
-      <c r="Y45" s="37"/>
-      <c r="Z45" s="37"/>
-      <c r="AA45" s="37"/>
-      <c r="AB45" s="37"/>
-      <c r="AC45" s="37"/>
-      <c r="AD45" s="37"/>
-      <c r="AE45" s="35"/>
-      <c r="AF45" s="35"/>
-      <c r="AG45" s="35"/>
-      <c r="AH45" s="35"/>
-      <c r="AI45" s="35"/>
-      <c r="AJ45" s="35"/>
-      <c r="AK45" s="35"/>
-      <c r="AL45" s="35"/>
-      <c r="AM45" s="35"/>
-      <c r="AN45" s="35"/>
-      <c r="AO45" s="35"/>
-      <c r="AP45" s="35"/>
-      <c r="AQ45" s="35"/>
-      <c r="AR45" s="35"/>
-      <c r="AS45" s="35"/>
-      <c r="AT45" s="35"/>
-      <c r="AU45" s="35"/>
+      <c r="S45" s="16"/>
+      <c r="T45" s="16"/>
+      <c r="U45" s="16"/>
+      <c r="V45" s="16"/>
+      <c r="W45" s="16"/>
+      <c r="X45" s="16"/>
+      <c r="Y45" s="16"/>
+      <c r="Z45" s="16"/>
+      <c r="AA45" s="16"/>
+      <c r="AB45" s="16"/>
+      <c r="AC45" s="16"/>
+      <c r="AD45" s="16"/>
+      <c r="AE45" s="12"/>
+      <c r="AF45" s="12"/>
+      <c r="AG45" s="12"/>
+      <c r="AH45" s="12"/>
+      <c r="AI45" s="12"/>
+      <c r="AJ45" s="12"/>
+      <c r="AK45" s="12"/>
+      <c r="AL45" s="12"/>
+      <c r="AM45" s="12"/>
+      <c r="AN45" s="12"/>
+      <c r="AO45" s="12"/>
+      <c r="AP45" s="12"/>
+      <c r="AQ45" s="12"/>
+      <c r="AR45" s="12"/>
+      <c r="AS45" s="12"/>
+      <c r="AT45" s="12"/>
+      <c r="AU45" s="12"/>
       <c r="AV45" s="12"/>
       <c r="AW45" s="12"/>
       <c r="AX45" s="12"/>
@@ -7026,35 +6902,35 @@
         <v>17</v>
       </c>
       <c r="Q46" s="8"/>
-      <c r="S46" s="36"/>
-      <c r="T46" s="36"/>
-      <c r="U46" s="38"/>
-      <c r="V46" s="38"/>
-      <c r="W46" s="38"/>
-      <c r="X46" s="38"/>
-      <c r="Y46" s="38"/>
-      <c r="Z46" s="38"/>
-      <c r="AA46" s="38"/>
-      <c r="AB46" s="38"/>
-      <c r="AC46" s="38"/>
-      <c r="AD46" s="38"/>
-      <c r="AE46" s="38"/>
-      <c r="AF46" s="38"/>
-      <c r="AG46" s="38"/>
-      <c r="AH46" s="38"/>
-      <c r="AI46" s="38"/>
-      <c r="AJ46" s="38"/>
-      <c r="AK46" s="38"/>
-      <c r="AL46" s="38"/>
-      <c r="AM46" s="38"/>
-      <c r="AN46" s="38"/>
-      <c r="AO46" s="38"/>
-      <c r="AP46" s="38"/>
-      <c r="AQ46" s="38"/>
-      <c r="AR46" s="38"/>
-      <c r="AS46" s="38"/>
-      <c r="AT46" s="38"/>
-      <c r="AU46" s="38"/>
+      <c r="S46" s="15"/>
+      <c r="T46" s="15"/>
+      <c r="U46" s="11"/>
+      <c r="V46" s="11"/>
+      <c r="W46" s="11"/>
+      <c r="X46" s="11"/>
+      <c r="Y46" s="11"/>
+      <c r="Z46" s="11"/>
+      <c r="AA46" s="11"/>
+      <c r="AB46" s="11"/>
+      <c r="AC46" s="11"/>
+      <c r="AD46" s="11"/>
+      <c r="AE46" s="11"/>
+      <c r="AF46" s="11"/>
+      <c r="AG46" s="11"/>
+      <c r="AH46" s="11"/>
+      <c r="AI46" s="11"/>
+      <c r="AJ46" s="11"/>
+      <c r="AK46" s="11"/>
+      <c r="AL46" s="11"/>
+      <c r="AM46" s="11"/>
+      <c r="AN46" s="11"/>
+      <c r="AO46" s="11"/>
+      <c r="AP46" s="11"/>
+      <c r="AQ46" s="11"/>
+      <c r="AR46" s="11"/>
+      <c r="AS46" s="11"/>
+      <c r="AT46" s="11"/>
+      <c r="AU46" s="11"/>
       <c r="AV46" s="11"/>
       <c r="AW46" s="11"/>
       <c r="AX46" s="11"/>
@@ -7160,35 +7036,35 @@
       <c r="O47" s="7"/>
       <c r="P47" s="8"/>
       <c r="Q47" s="8"/>
-      <c r="S47" s="37"/>
-      <c r="T47" s="37"/>
-      <c r="U47" s="35"/>
-      <c r="V47" s="35"/>
-      <c r="W47" s="35"/>
-      <c r="X47" s="35"/>
-      <c r="Y47" s="35"/>
-      <c r="Z47" s="35"/>
-      <c r="AA47" s="35"/>
-      <c r="AB47" s="35"/>
-      <c r="AC47" s="35"/>
-      <c r="AD47" s="35"/>
-      <c r="AE47" s="35"/>
-      <c r="AF47" s="35"/>
-      <c r="AG47" s="35"/>
-      <c r="AH47" s="35"/>
-      <c r="AI47" s="35"/>
-      <c r="AJ47" s="35"/>
-      <c r="AK47" s="35"/>
-      <c r="AL47" s="35"/>
-      <c r="AM47" s="35"/>
-      <c r="AN47" s="35"/>
-      <c r="AO47" s="35"/>
-      <c r="AP47" s="35"/>
-      <c r="AQ47" s="35"/>
-      <c r="AR47" s="35"/>
-      <c r="AS47" s="35"/>
-      <c r="AT47" s="35"/>
-      <c r="AU47" s="35"/>
+      <c r="S47" s="16"/>
+      <c r="T47" s="16"/>
+      <c r="U47" s="12"/>
+      <c r="V47" s="12"/>
+      <c r="W47" s="12"/>
+      <c r="X47" s="12"/>
+      <c r="Y47" s="12"/>
+      <c r="Z47" s="12"/>
+      <c r="AA47" s="12"/>
+      <c r="AB47" s="12"/>
+      <c r="AC47" s="12"/>
+      <c r="AD47" s="12"/>
+      <c r="AE47" s="12"/>
+      <c r="AF47" s="12"/>
+      <c r="AG47" s="12"/>
+      <c r="AH47" s="12"/>
+      <c r="AI47" s="12"/>
+      <c r="AJ47" s="12"/>
+      <c r="AK47" s="12"/>
+      <c r="AL47" s="12"/>
+      <c r="AM47" s="12"/>
+      <c r="AN47" s="12"/>
+      <c r="AO47" s="12"/>
+      <c r="AP47" s="12"/>
+      <c r="AQ47" s="12"/>
+      <c r="AR47" s="12"/>
+      <c r="AS47" s="12"/>
+      <c r="AT47" s="12"/>
+      <c r="AU47" s="12"/>
       <c r="AV47" s="12"/>
       <c r="AW47" s="12"/>
       <c r="AX47" s="12"/>
@@ -7300,35 +7176,35 @@
         <v>17</v>
       </c>
       <c r="Q48" s="8"/>
-      <c r="S48" s="36"/>
-      <c r="T48" s="36"/>
-      <c r="U48" s="38"/>
-      <c r="V48" s="38"/>
-      <c r="W48" s="38"/>
-      <c r="X48" s="38"/>
-      <c r="Y48" s="38"/>
-      <c r="Z48" s="38"/>
-      <c r="AA48" s="38"/>
-      <c r="AB48" s="38"/>
-      <c r="AC48" s="38"/>
-      <c r="AD48" s="38"/>
-      <c r="AE48" s="38"/>
-      <c r="AF48" s="38"/>
-      <c r="AG48" s="38"/>
-      <c r="AH48" s="38"/>
-      <c r="AI48" s="38"/>
-      <c r="AJ48" s="38"/>
-      <c r="AK48" s="38"/>
-      <c r="AL48" s="38"/>
-      <c r="AM48" s="38"/>
-      <c r="AN48" s="38"/>
-      <c r="AO48" s="38"/>
-      <c r="AP48" s="38"/>
-      <c r="AQ48" s="38"/>
-      <c r="AR48" s="38"/>
-      <c r="AS48" s="38"/>
-      <c r="AT48" s="38"/>
-      <c r="AU48" s="38"/>
+      <c r="S48" s="15"/>
+      <c r="T48" s="15"/>
+      <c r="U48" s="11"/>
+      <c r="V48" s="11"/>
+      <c r="W48" s="11"/>
+      <c r="X48" s="11"/>
+      <c r="Y48" s="11"/>
+      <c r="Z48" s="11"/>
+      <c r="AA48" s="11"/>
+      <c r="AB48" s="11"/>
+      <c r="AC48" s="11"/>
+      <c r="AD48" s="11"/>
+      <c r="AE48" s="11"/>
+      <c r="AF48" s="11"/>
+      <c r="AG48" s="11"/>
+      <c r="AH48" s="11"/>
+      <c r="AI48" s="11"/>
+      <c r="AJ48" s="11"/>
+      <c r="AK48" s="11"/>
+      <c r="AL48" s="11"/>
+      <c r="AM48" s="11"/>
+      <c r="AN48" s="11"/>
+      <c r="AO48" s="11"/>
+      <c r="AP48" s="11"/>
+      <c r="AQ48" s="11"/>
+      <c r="AR48" s="11"/>
+      <c r="AS48" s="11"/>
+      <c r="AT48" s="11"/>
+      <c r="AU48" s="11"/>
       <c r="AV48" s="11"/>
       <c r="AW48" s="11"/>
       <c r="AX48" s="11"/>
@@ -7434,35 +7310,35 @@
       <c r="O49" s="7"/>
       <c r="P49" s="8"/>
       <c r="Q49" s="8"/>
-      <c r="S49" s="37"/>
-      <c r="T49" s="37"/>
-      <c r="U49" s="35"/>
-      <c r="V49" s="35"/>
-      <c r="W49" s="35"/>
-      <c r="X49" s="35"/>
-      <c r="Y49" s="35"/>
-      <c r="Z49" s="35"/>
-      <c r="AA49" s="35"/>
-      <c r="AB49" s="35"/>
-      <c r="AC49" s="35"/>
-      <c r="AD49" s="35"/>
-      <c r="AE49" s="35"/>
-      <c r="AF49" s="35"/>
-      <c r="AG49" s="35"/>
-      <c r="AH49" s="35"/>
-      <c r="AI49" s="35"/>
-      <c r="AJ49" s="35"/>
-      <c r="AK49" s="35"/>
-      <c r="AL49" s="35"/>
-      <c r="AM49" s="35"/>
-      <c r="AN49" s="35"/>
-      <c r="AO49" s="35"/>
-      <c r="AP49" s="35"/>
-      <c r="AQ49" s="35"/>
-      <c r="AR49" s="35"/>
-      <c r="AS49" s="35"/>
-      <c r="AT49" s="35"/>
-      <c r="AU49" s="35"/>
+      <c r="S49" s="16"/>
+      <c r="T49" s="16"/>
+      <c r="U49" s="12"/>
+      <c r="V49" s="12"/>
+      <c r="W49" s="12"/>
+      <c r="X49" s="12"/>
+      <c r="Y49" s="12"/>
+      <c r="Z49" s="12"/>
+      <c r="AA49" s="12"/>
+      <c r="AB49" s="12"/>
+      <c r="AC49" s="12"/>
+      <c r="AD49" s="12"/>
+      <c r="AE49" s="12"/>
+      <c r="AF49" s="12"/>
+      <c r="AG49" s="12"/>
+      <c r="AH49" s="12"/>
+      <c r="AI49" s="12"/>
+      <c r="AJ49" s="12"/>
+      <c r="AK49" s="12"/>
+      <c r="AL49" s="12"/>
+      <c r="AM49" s="12"/>
+      <c r="AN49" s="12"/>
+      <c r="AO49" s="12"/>
+      <c r="AP49" s="12"/>
+      <c r="AQ49" s="12"/>
+      <c r="AR49" s="12"/>
+      <c r="AS49" s="12"/>
+      <c r="AT49" s="12"/>
+      <c r="AU49" s="12"/>
       <c r="AV49" s="12"/>
       <c r="AW49" s="12"/>
       <c r="AX49" s="12"/>
@@ -7574,35 +7450,35 @@
         <v>17</v>
       </c>
       <c r="Q50" s="8"/>
-      <c r="S50" s="36"/>
-      <c r="T50" s="36"/>
-      <c r="U50" s="38"/>
-      <c r="V50" s="38"/>
-      <c r="W50" s="38"/>
-      <c r="X50" s="38"/>
-      <c r="Y50" s="38"/>
-      <c r="Z50" s="38"/>
-      <c r="AA50" s="38"/>
-      <c r="AB50" s="38"/>
-      <c r="AC50" s="38"/>
-      <c r="AD50" s="38"/>
-      <c r="AE50" s="38"/>
-      <c r="AF50" s="38"/>
-      <c r="AG50" s="38"/>
-      <c r="AH50" s="38"/>
-      <c r="AI50" s="38"/>
-      <c r="AJ50" s="38"/>
-      <c r="AK50" s="38"/>
-      <c r="AL50" s="38"/>
-      <c r="AM50" s="38"/>
-      <c r="AN50" s="38"/>
-      <c r="AO50" s="38"/>
-      <c r="AP50" s="38"/>
-      <c r="AQ50" s="38"/>
-      <c r="AR50" s="38"/>
-      <c r="AS50" s="38"/>
-      <c r="AT50" s="38"/>
-      <c r="AU50" s="38"/>
+      <c r="S50" s="15"/>
+      <c r="T50" s="15"/>
+      <c r="U50" s="11"/>
+      <c r="V50" s="11"/>
+      <c r="W50" s="11"/>
+      <c r="X50" s="11"/>
+      <c r="Y50" s="11"/>
+      <c r="Z50" s="11"/>
+      <c r="AA50" s="11"/>
+      <c r="AB50" s="11"/>
+      <c r="AC50" s="11"/>
+      <c r="AD50" s="11"/>
+      <c r="AE50" s="11"/>
+      <c r="AF50" s="11"/>
+      <c r="AG50" s="11"/>
+      <c r="AH50" s="11"/>
+      <c r="AI50" s="11"/>
+      <c r="AJ50" s="11"/>
+      <c r="AK50" s="11"/>
+      <c r="AL50" s="11"/>
+      <c r="AM50" s="11"/>
+      <c r="AN50" s="11"/>
+      <c r="AO50" s="11"/>
+      <c r="AP50" s="11"/>
+      <c r="AQ50" s="11"/>
+      <c r="AR50" s="11"/>
+      <c r="AS50" s="11"/>
+      <c r="AT50" s="11"/>
+      <c r="AU50" s="11"/>
       <c r="AV50" s="11"/>
       <c r="AW50" s="11"/>
       <c r="AX50" s="11"/>
@@ -7708,35 +7584,35 @@
       <c r="O51" s="7"/>
       <c r="P51" s="8"/>
       <c r="Q51" s="8"/>
-      <c r="S51" s="37"/>
-      <c r="T51" s="37"/>
-      <c r="U51" s="35"/>
-      <c r="V51" s="35"/>
-      <c r="W51" s="35"/>
-      <c r="X51" s="35"/>
-      <c r="Y51" s="35"/>
-      <c r="Z51" s="35"/>
-      <c r="AA51" s="35"/>
-      <c r="AB51" s="35"/>
-      <c r="AC51" s="35"/>
-      <c r="AD51" s="35"/>
-      <c r="AE51" s="35"/>
-      <c r="AF51" s="35"/>
-      <c r="AG51" s="35"/>
-      <c r="AH51" s="35"/>
-      <c r="AI51" s="35"/>
-      <c r="AJ51" s="35"/>
-      <c r="AK51" s="35"/>
-      <c r="AL51" s="35"/>
-      <c r="AM51" s="35"/>
-      <c r="AN51" s="35"/>
-      <c r="AO51" s="35"/>
-      <c r="AP51" s="35"/>
-      <c r="AQ51" s="35"/>
-      <c r="AR51" s="35"/>
-      <c r="AS51" s="35"/>
-      <c r="AT51" s="35"/>
-      <c r="AU51" s="35"/>
+      <c r="S51" s="16"/>
+      <c r="T51" s="16"/>
+      <c r="U51" s="12"/>
+      <c r="V51" s="12"/>
+      <c r="W51" s="12"/>
+      <c r="X51" s="12"/>
+      <c r="Y51" s="12"/>
+      <c r="Z51" s="12"/>
+      <c r="AA51" s="12"/>
+      <c r="AB51" s="12"/>
+      <c r="AC51" s="12"/>
+      <c r="AD51" s="12"/>
+      <c r="AE51" s="12"/>
+      <c r="AF51" s="12"/>
+      <c r="AG51" s="12"/>
+      <c r="AH51" s="12"/>
+      <c r="AI51" s="12"/>
+      <c r="AJ51" s="12"/>
+      <c r="AK51" s="12"/>
+      <c r="AL51" s="12"/>
+      <c r="AM51" s="12"/>
+      <c r="AN51" s="12"/>
+      <c r="AO51" s="12"/>
+      <c r="AP51" s="12"/>
+      <c r="AQ51" s="12"/>
+      <c r="AR51" s="12"/>
+      <c r="AS51" s="12"/>
+      <c r="AT51" s="12"/>
+      <c r="AU51" s="12"/>
       <c r="AV51" s="12"/>
       <c r="AW51" s="12"/>
       <c r="AX51" s="12"/>
@@ -7848,35 +7724,35 @@
         <v>17</v>
       </c>
       <c r="Q52" s="8"/>
-      <c r="S52" s="36"/>
-      <c r="T52" s="36"/>
-      <c r="U52" s="36"/>
-      <c r="V52" s="36"/>
-      <c r="W52" s="36"/>
-      <c r="X52" s="36"/>
-      <c r="Y52" s="36"/>
-      <c r="Z52" s="36"/>
-      <c r="AA52" s="36"/>
-      <c r="AB52" s="36"/>
-      <c r="AC52" s="36"/>
-      <c r="AD52" s="36"/>
-      <c r="AE52" s="36"/>
-      <c r="AF52" s="36"/>
-      <c r="AG52" s="36"/>
-      <c r="AH52" s="38"/>
-      <c r="AI52" s="38"/>
-      <c r="AJ52" s="38"/>
-      <c r="AK52" s="38"/>
-      <c r="AL52" s="38"/>
-      <c r="AM52" s="38"/>
-      <c r="AN52" s="38"/>
-      <c r="AO52" s="38"/>
-      <c r="AP52" s="38"/>
-      <c r="AQ52" s="38"/>
-      <c r="AR52" s="38"/>
-      <c r="AS52" s="38"/>
-      <c r="AT52" s="38"/>
-      <c r="AU52" s="38"/>
+      <c r="S52" s="15"/>
+      <c r="T52" s="15"/>
+      <c r="U52" s="15"/>
+      <c r="V52" s="15"/>
+      <c r="W52" s="15"/>
+      <c r="X52" s="15"/>
+      <c r="Y52" s="15"/>
+      <c r="Z52" s="15"/>
+      <c r="AA52" s="15"/>
+      <c r="AB52" s="15"/>
+      <c r="AC52" s="15"/>
+      <c r="AD52" s="15"/>
+      <c r="AE52" s="15"/>
+      <c r="AF52" s="15"/>
+      <c r="AG52" s="15"/>
+      <c r="AH52" s="11"/>
+      <c r="AI52" s="11"/>
+      <c r="AJ52" s="11"/>
+      <c r="AK52" s="11"/>
+      <c r="AL52" s="11"/>
+      <c r="AM52" s="11"/>
+      <c r="AN52" s="11"/>
+      <c r="AO52" s="11"/>
+      <c r="AP52" s="11"/>
+      <c r="AQ52" s="11"/>
+      <c r="AR52" s="11"/>
+      <c r="AS52" s="11"/>
+      <c r="AT52" s="11"/>
+      <c r="AU52" s="11"/>
       <c r="AV52" s="11"/>
       <c r="AW52" s="11"/>
       <c r="AX52" s="11"/>
@@ -7982,35 +7858,35 @@
       <c r="O53" s="7"/>
       <c r="P53" s="8"/>
       <c r="Q53" s="8"/>
-      <c r="S53" s="37"/>
-      <c r="T53" s="37"/>
-      <c r="U53" s="37"/>
-      <c r="V53" s="37"/>
-      <c r="W53" s="37"/>
-      <c r="X53" s="37"/>
-      <c r="Y53" s="37"/>
-      <c r="Z53" s="37"/>
-      <c r="AA53" s="37"/>
-      <c r="AB53" s="37"/>
-      <c r="AC53" s="37"/>
-      <c r="AD53" s="37"/>
-      <c r="AE53" s="37"/>
-      <c r="AF53" s="37"/>
-      <c r="AG53" s="37"/>
-      <c r="AH53" s="35"/>
-      <c r="AI53" s="35"/>
-      <c r="AJ53" s="35"/>
-      <c r="AK53" s="35"/>
-      <c r="AL53" s="35"/>
-      <c r="AM53" s="35"/>
-      <c r="AN53" s="35"/>
-      <c r="AO53" s="35"/>
-      <c r="AP53" s="35"/>
-      <c r="AQ53" s="35"/>
-      <c r="AR53" s="35"/>
-      <c r="AS53" s="35"/>
-      <c r="AT53" s="35"/>
-      <c r="AU53" s="35"/>
+      <c r="S53" s="16"/>
+      <c r="T53" s="16"/>
+      <c r="U53" s="16"/>
+      <c r="V53" s="16"/>
+      <c r="W53" s="16"/>
+      <c r="X53" s="16"/>
+      <c r="Y53" s="16"/>
+      <c r="Z53" s="16"/>
+      <c r="AA53" s="16"/>
+      <c r="AB53" s="16"/>
+      <c r="AC53" s="16"/>
+      <c r="AD53" s="16"/>
+      <c r="AE53" s="16"/>
+      <c r="AF53" s="16"/>
+      <c r="AG53" s="16"/>
+      <c r="AH53" s="12"/>
+      <c r="AI53" s="12"/>
+      <c r="AJ53" s="12"/>
+      <c r="AK53" s="12"/>
+      <c r="AL53" s="12"/>
+      <c r="AM53" s="12"/>
+      <c r="AN53" s="12"/>
+      <c r="AO53" s="12"/>
+      <c r="AP53" s="12"/>
+      <c r="AQ53" s="12"/>
+      <c r="AR53" s="12"/>
+      <c r="AS53" s="12"/>
+      <c r="AT53" s="12"/>
+      <c r="AU53" s="12"/>
       <c r="AV53" s="12"/>
       <c r="AW53" s="12"/>
       <c r="AX53" s="12"/>
@@ -8121,35 +7997,6 @@
       <c r="O54" s="9"/>
       <c r="P54" s="9"/>
       <c r="Q54" s="9"/>
-      <c r="S54" s="39"/>
-      <c r="T54" s="39"/>
-      <c r="U54" s="39"/>
-      <c r="V54" s="39"/>
-      <c r="W54" s="39"/>
-      <c r="X54" s="39"/>
-      <c r="Y54" s="39"/>
-      <c r="Z54" s="39"/>
-      <c r="AA54" s="39"/>
-      <c r="AB54" s="39"/>
-      <c r="AC54" s="39"/>
-      <c r="AD54" s="39"/>
-      <c r="AE54" s="39"/>
-      <c r="AF54" s="39"/>
-      <c r="AG54" s="39"/>
-      <c r="AH54" s="39"/>
-      <c r="AI54" s="39"/>
-      <c r="AJ54" s="39"/>
-      <c r="AK54" s="39"/>
-      <c r="AL54" s="39"/>
-      <c r="AM54" s="39"/>
-      <c r="AN54" s="39"/>
-      <c r="AO54" s="39"/>
-      <c r="AP54" s="39"/>
-      <c r="AQ54" s="39"/>
-      <c r="AR54" s="39"/>
-      <c r="AS54" s="39"/>
-      <c r="AT54" s="39"/>
-      <c r="AU54" s="39"/>
     </row>
     <row r="55" spans="1:133" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
@@ -8175,35 +8022,35 @@
         <v>17</v>
       </c>
       <c r="Q55" s="8"/>
-      <c r="S55" s="36"/>
-      <c r="T55" s="36"/>
-      <c r="U55" s="36"/>
-      <c r="V55" s="36"/>
-      <c r="W55" s="36"/>
-      <c r="X55" s="36"/>
-      <c r="Y55" s="36"/>
-      <c r="Z55" s="36"/>
-      <c r="AA55" s="36"/>
-      <c r="AB55" s="36"/>
-      <c r="AC55" s="36"/>
-      <c r="AD55" s="36"/>
-      <c r="AE55" s="34"/>
-      <c r="AF55" s="34"/>
-      <c r="AG55" s="34"/>
-      <c r="AH55" s="38"/>
-      <c r="AI55" s="38"/>
-      <c r="AJ55" s="38"/>
-      <c r="AK55" s="38"/>
-      <c r="AL55" s="38"/>
-      <c r="AM55" s="38"/>
-      <c r="AN55" s="38"/>
-      <c r="AO55" s="38"/>
-      <c r="AP55" s="38"/>
-      <c r="AQ55" s="38"/>
-      <c r="AR55" s="38"/>
-      <c r="AS55" s="38"/>
-      <c r="AT55" s="38"/>
-      <c r="AU55" s="38"/>
+      <c r="S55" s="15"/>
+      <c r="T55" s="15"/>
+      <c r="U55" s="15"/>
+      <c r="V55" s="15"/>
+      <c r="W55" s="15"/>
+      <c r="X55" s="15"/>
+      <c r="Y55" s="15"/>
+      <c r="Z55" s="15"/>
+      <c r="AA55" s="15"/>
+      <c r="AB55" s="15"/>
+      <c r="AC55" s="15"/>
+      <c r="AD55" s="15"/>
+      <c r="AE55" s="21"/>
+      <c r="AF55" s="21"/>
+      <c r="AG55" s="21"/>
+      <c r="AH55" s="11"/>
+      <c r="AI55" s="11"/>
+      <c r="AJ55" s="11"/>
+      <c r="AK55" s="11"/>
+      <c r="AL55" s="11"/>
+      <c r="AM55" s="11"/>
+      <c r="AN55" s="11"/>
+      <c r="AO55" s="11"/>
+      <c r="AP55" s="11"/>
+      <c r="AQ55" s="11"/>
+      <c r="AR55" s="11"/>
+      <c r="AS55" s="11"/>
+      <c r="AT55" s="11"/>
+      <c r="AU55" s="11"/>
       <c r="AV55" s="11"/>
       <c r="AW55" s="11"/>
       <c r="AX55" s="11"/>
@@ -8309,35 +8156,35 @@
       <c r="O56" s="7"/>
       <c r="P56" s="8"/>
       <c r="Q56" s="8"/>
-      <c r="S56" s="37"/>
-      <c r="T56" s="37"/>
-      <c r="U56" s="37"/>
-      <c r="V56" s="37"/>
-      <c r="W56" s="37"/>
-      <c r="X56" s="37"/>
-      <c r="Y56" s="37"/>
-      <c r="Z56" s="37"/>
-      <c r="AA56" s="37"/>
-      <c r="AB56" s="37"/>
-      <c r="AC56" s="37"/>
-      <c r="AD56" s="37"/>
-      <c r="AE56" s="35"/>
-      <c r="AF56" s="35"/>
-      <c r="AG56" s="35"/>
-      <c r="AH56" s="35"/>
-      <c r="AI56" s="35"/>
-      <c r="AJ56" s="35"/>
-      <c r="AK56" s="35"/>
-      <c r="AL56" s="35"/>
-      <c r="AM56" s="35"/>
-      <c r="AN56" s="35"/>
-      <c r="AO56" s="35"/>
-      <c r="AP56" s="35"/>
-      <c r="AQ56" s="35"/>
-      <c r="AR56" s="35"/>
-      <c r="AS56" s="35"/>
-      <c r="AT56" s="35"/>
-      <c r="AU56" s="35"/>
+      <c r="S56" s="16"/>
+      <c r="T56" s="16"/>
+      <c r="U56" s="16"/>
+      <c r="V56" s="16"/>
+      <c r="W56" s="16"/>
+      <c r="X56" s="16"/>
+      <c r="Y56" s="16"/>
+      <c r="Z56" s="16"/>
+      <c r="AA56" s="16"/>
+      <c r="AB56" s="16"/>
+      <c r="AC56" s="16"/>
+      <c r="AD56" s="16"/>
+      <c r="AE56" s="12"/>
+      <c r="AF56" s="12"/>
+      <c r="AG56" s="12"/>
+      <c r="AH56" s="12"/>
+      <c r="AI56" s="12"/>
+      <c r="AJ56" s="12"/>
+      <c r="AK56" s="12"/>
+      <c r="AL56" s="12"/>
+      <c r="AM56" s="12"/>
+      <c r="AN56" s="12"/>
+      <c r="AO56" s="12"/>
+      <c r="AP56" s="12"/>
+      <c r="AQ56" s="12"/>
+      <c r="AR56" s="12"/>
+      <c r="AS56" s="12"/>
+      <c r="AT56" s="12"/>
+      <c r="AU56" s="12"/>
       <c r="AV56" s="12"/>
       <c r="AW56" s="12"/>
       <c r="AX56" s="12"/>
@@ -8449,35 +8296,35 @@
         <v>17</v>
       </c>
       <c r="Q57" s="8"/>
-      <c r="S57" s="36"/>
-      <c r="T57" s="36"/>
-      <c r="U57" s="38"/>
-      <c r="V57" s="38"/>
-      <c r="W57" s="38"/>
-      <c r="X57" s="38"/>
-      <c r="Y57" s="38"/>
-      <c r="Z57" s="38"/>
-      <c r="AA57" s="38"/>
-      <c r="AB57" s="38"/>
-      <c r="AC57" s="38"/>
-      <c r="AD57" s="38"/>
-      <c r="AE57" s="38"/>
-      <c r="AF57" s="38"/>
-      <c r="AG57" s="38"/>
-      <c r="AH57" s="38"/>
-      <c r="AI57" s="38"/>
-      <c r="AJ57" s="38"/>
-      <c r="AK57" s="38"/>
-      <c r="AL57" s="38"/>
-      <c r="AM57" s="38"/>
-      <c r="AN57" s="38"/>
-      <c r="AO57" s="38"/>
-      <c r="AP57" s="38"/>
-      <c r="AQ57" s="38"/>
-      <c r="AR57" s="38"/>
-      <c r="AS57" s="38"/>
-      <c r="AT57" s="38"/>
-      <c r="AU57" s="38"/>
+      <c r="S57" s="15"/>
+      <c r="T57" s="15"/>
+      <c r="U57" s="11"/>
+      <c r="V57" s="11"/>
+      <c r="W57" s="11"/>
+      <c r="X57" s="11"/>
+      <c r="Y57" s="11"/>
+      <c r="Z57" s="11"/>
+      <c r="AA57" s="11"/>
+      <c r="AB57" s="11"/>
+      <c r="AC57" s="11"/>
+      <c r="AD57" s="11"/>
+      <c r="AE57" s="11"/>
+      <c r="AF57" s="11"/>
+      <c r="AG57" s="11"/>
+      <c r="AH57" s="11"/>
+      <c r="AI57" s="11"/>
+      <c r="AJ57" s="11"/>
+      <c r="AK57" s="11"/>
+      <c r="AL57" s="11"/>
+      <c r="AM57" s="11"/>
+      <c r="AN57" s="11"/>
+      <c r="AO57" s="11"/>
+      <c r="AP57" s="11"/>
+      <c r="AQ57" s="11"/>
+      <c r="AR57" s="11"/>
+      <c r="AS57" s="11"/>
+      <c r="AT57" s="11"/>
+      <c r="AU57" s="11"/>
       <c r="AV57" s="11"/>
       <c r="AW57" s="11"/>
       <c r="AX57" s="11"/>
@@ -8583,35 +8430,35 @@
       <c r="O58" s="7"/>
       <c r="P58" s="8"/>
       <c r="Q58" s="8"/>
-      <c r="S58" s="37"/>
-      <c r="T58" s="37"/>
-      <c r="U58" s="35"/>
-      <c r="V58" s="35"/>
-      <c r="W58" s="35"/>
-      <c r="X58" s="35"/>
-      <c r="Y58" s="35"/>
-      <c r="Z58" s="35"/>
-      <c r="AA58" s="35"/>
-      <c r="AB58" s="35"/>
-      <c r="AC58" s="35"/>
-      <c r="AD58" s="35"/>
-      <c r="AE58" s="35"/>
-      <c r="AF58" s="35"/>
-      <c r="AG58" s="35"/>
-      <c r="AH58" s="35"/>
-      <c r="AI58" s="35"/>
-      <c r="AJ58" s="35"/>
-      <c r="AK58" s="35"/>
-      <c r="AL58" s="35"/>
-      <c r="AM58" s="35"/>
-      <c r="AN58" s="35"/>
-      <c r="AO58" s="35"/>
-      <c r="AP58" s="35"/>
-      <c r="AQ58" s="35"/>
-      <c r="AR58" s="35"/>
-      <c r="AS58" s="35"/>
-      <c r="AT58" s="35"/>
-      <c r="AU58" s="35"/>
+      <c r="S58" s="16"/>
+      <c r="T58" s="16"/>
+      <c r="U58" s="12"/>
+      <c r="V58" s="12"/>
+      <c r="W58" s="12"/>
+      <c r="X58" s="12"/>
+      <c r="Y58" s="12"/>
+      <c r="Z58" s="12"/>
+      <c r="AA58" s="12"/>
+      <c r="AB58" s="12"/>
+      <c r="AC58" s="12"/>
+      <c r="AD58" s="12"/>
+      <c r="AE58" s="12"/>
+      <c r="AF58" s="12"/>
+      <c r="AG58" s="12"/>
+      <c r="AH58" s="12"/>
+      <c r="AI58" s="12"/>
+      <c r="AJ58" s="12"/>
+      <c r="AK58" s="12"/>
+      <c r="AL58" s="12"/>
+      <c r="AM58" s="12"/>
+      <c r="AN58" s="12"/>
+      <c r="AO58" s="12"/>
+      <c r="AP58" s="12"/>
+      <c r="AQ58" s="12"/>
+      <c r="AR58" s="12"/>
+      <c r="AS58" s="12"/>
+      <c r="AT58" s="12"/>
+      <c r="AU58" s="12"/>
       <c r="AV58" s="12"/>
       <c r="AW58" s="12"/>
       <c r="AX58" s="12"/>
@@ -8723,35 +8570,35 @@
         <v>17</v>
       </c>
       <c r="Q59" s="8"/>
-      <c r="S59" s="36"/>
-      <c r="T59" s="36"/>
-      <c r="U59" s="38"/>
-      <c r="V59" s="38"/>
-      <c r="W59" s="38"/>
-      <c r="X59" s="38"/>
-      <c r="Y59" s="38"/>
-      <c r="Z59" s="38"/>
-      <c r="AA59" s="38"/>
-      <c r="AB59" s="38"/>
-      <c r="AC59" s="38"/>
-      <c r="AD59" s="38"/>
-      <c r="AE59" s="38"/>
-      <c r="AF59" s="38"/>
-      <c r="AG59" s="38"/>
-      <c r="AH59" s="38"/>
-      <c r="AI59" s="38"/>
-      <c r="AJ59" s="38"/>
-      <c r="AK59" s="38"/>
-      <c r="AL59" s="38"/>
-      <c r="AM59" s="38"/>
-      <c r="AN59" s="38"/>
-      <c r="AO59" s="38"/>
-      <c r="AP59" s="38"/>
-      <c r="AQ59" s="38"/>
-      <c r="AR59" s="38"/>
-      <c r="AS59" s="38"/>
-      <c r="AT59" s="38"/>
-      <c r="AU59" s="38"/>
+      <c r="S59" s="15"/>
+      <c r="T59" s="15"/>
+      <c r="U59" s="11"/>
+      <c r="V59" s="11"/>
+      <c r="W59" s="11"/>
+      <c r="X59" s="11"/>
+      <c r="Y59" s="11"/>
+      <c r="Z59" s="11"/>
+      <c r="AA59" s="11"/>
+      <c r="AB59" s="11"/>
+      <c r="AC59" s="11"/>
+      <c r="AD59" s="11"/>
+      <c r="AE59" s="11"/>
+      <c r="AF59" s="11"/>
+      <c r="AG59" s="11"/>
+      <c r="AH59" s="11"/>
+      <c r="AI59" s="11"/>
+      <c r="AJ59" s="11"/>
+      <c r="AK59" s="11"/>
+      <c r="AL59" s="11"/>
+      <c r="AM59" s="11"/>
+      <c r="AN59" s="11"/>
+      <c r="AO59" s="11"/>
+      <c r="AP59" s="11"/>
+      <c r="AQ59" s="11"/>
+      <c r="AR59" s="11"/>
+      <c r="AS59" s="11"/>
+      <c r="AT59" s="11"/>
+      <c r="AU59" s="11"/>
       <c r="AV59" s="11"/>
       <c r="AW59" s="11"/>
       <c r="AX59" s="11"/>
@@ -8857,35 +8704,35 @@
       <c r="O60" s="7"/>
       <c r="P60" s="8"/>
       <c r="Q60" s="8"/>
-      <c r="S60" s="37"/>
-      <c r="T60" s="37"/>
-      <c r="U60" s="35"/>
-      <c r="V60" s="35"/>
-      <c r="W60" s="35"/>
-      <c r="X60" s="35"/>
-      <c r="Y60" s="35"/>
-      <c r="Z60" s="35"/>
-      <c r="AA60" s="35"/>
-      <c r="AB60" s="35"/>
-      <c r="AC60" s="35"/>
-      <c r="AD60" s="35"/>
-      <c r="AE60" s="35"/>
-      <c r="AF60" s="35"/>
-      <c r="AG60" s="35"/>
-      <c r="AH60" s="35"/>
-      <c r="AI60" s="35"/>
-      <c r="AJ60" s="35"/>
-      <c r="AK60" s="35"/>
-      <c r="AL60" s="35"/>
-      <c r="AM60" s="35"/>
-      <c r="AN60" s="35"/>
-      <c r="AO60" s="35"/>
-      <c r="AP60" s="35"/>
-      <c r="AQ60" s="35"/>
-      <c r="AR60" s="35"/>
-      <c r="AS60" s="35"/>
-      <c r="AT60" s="35"/>
-      <c r="AU60" s="35"/>
+      <c r="S60" s="16"/>
+      <c r="T60" s="16"/>
+      <c r="U60" s="12"/>
+      <c r="V60" s="12"/>
+      <c r="W60" s="12"/>
+      <c r="X60" s="12"/>
+      <c r="Y60" s="12"/>
+      <c r="Z60" s="12"/>
+      <c r="AA60" s="12"/>
+      <c r="AB60" s="12"/>
+      <c r="AC60" s="12"/>
+      <c r="AD60" s="12"/>
+      <c r="AE60" s="12"/>
+      <c r="AF60" s="12"/>
+      <c r="AG60" s="12"/>
+      <c r="AH60" s="12"/>
+      <c r="AI60" s="12"/>
+      <c r="AJ60" s="12"/>
+      <c r="AK60" s="12"/>
+      <c r="AL60" s="12"/>
+      <c r="AM60" s="12"/>
+      <c r="AN60" s="12"/>
+      <c r="AO60" s="12"/>
+      <c r="AP60" s="12"/>
+      <c r="AQ60" s="12"/>
+      <c r="AR60" s="12"/>
+      <c r="AS60" s="12"/>
+      <c r="AT60" s="12"/>
+      <c r="AU60" s="12"/>
       <c r="AV60" s="12"/>
       <c r="AW60" s="12"/>
       <c r="AX60" s="12"/>
@@ -8997,35 +8844,35 @@
         <v>17</v>
       </c>
       <c r="Q61" s="8"/>
-      <c r="S61" s="36"/>
-      <c r="T61" s="36"/>
-      <c r="U61" s="38"/>
-      <c r="V61" s="38"/>
-      <c r="W61" s="38"/>
-      <c r="X61" s="38"/>
-      <c r="Y61" s="38"/>
-      <c r="Z61" s="38"/>
-      <c r="AA61" s="38"/>
-      <c r="AB61" s="38"/>
-      <c r="AC61" s="38"/>
-      <c r="AD61" s="38"/>
-      <c r="AE61" s="38"/>
-      <c r="AF61" s="38"/>
-      <c r="AG61" s="38"/>
-      <c r="AH61" s="38"/>
-      <c r="AI61" s="38"/>
-      <c r="AJ61" s="38"/>
-      <c r="AK61" s="38"/>
-      <c r="AL61" s="38"/>
-      <c r="AM61" s="38"/>
-      <c r="AN61" s="38"/>
-      <c r="AO61" s="38"/>
-      <c r="AP61" s="38"/>
-      <c r="AQ61" s="38"/>
-      <c r="AR61" s="38"/>
-      <c r="AS61" s="38"/>
-      <c r="AT61" s="38"/>
-      <c r="AU61" s="38"/>
+      <c r="S61" s="15"/>
+      <c r="T61" s="15"/>
+      <c r="U61" s="11"/>
+      <c r="V61" s="11"/>
+      <c r="W61" s="11"/>
+      <c r="X61" s="11"/>
+      <c r="Y61" s="11"/>
+      <c r="Z61" s="11"/>
+      <c r="AA61" s="11"/>
+      <c r="AB61" s="11"/>
+      <c r="AC61" s="11"/>
+      <c r="AD61" s="11"/>
+      <c r="AE61" s="11"/>
+      <c r="AF61" s="11"/>
+      <c r="AG61" s="11"/>
+      <c r="AH61" s="11"/>
+      <c r="AI61" s="11"/>
+      <c r="AJ61" s="11"/>
+      <c r="AK61" s="11"/>
+      <c r="AL61" s="11"/>
+      <c r="AM61" s="11"/>
+      <c r="AN61" s="11"/>
+      <c r="AO61" s="11"/>
+      <c r="AP61" s="11"/>
+      <c r="AQ61" s="11"/>
+      <c r="AR61" s="11"/>
+      <c r="AS61" s="11"/>
+      <c r="AT61" s="11"/>
+      <c r="AU61" s="11"/>
       <c r="AV61" s="11"/>
       <c r="AW61" s="11"/>
       <c r="AX61" s="11"/>
@@ -9131,35 +8978,35 @@
       <c r="O62" s="7"/>
       <c r="P62" s="8"/>
       <c r="Q62" s="8"/>
-      <c r="S62" s="37"/>
-      <c r="T62" s="37"/>
-      <c r="U62" s="35"/>
-      <c r="V62" s="35"/>
-      <c r="W62" s="35"/>
-      <c r="X62" s="35"/>
-      <c r="Y62" s="35"/>
-      <c r="Z62" s="35"/>
-      <c r="AA62" s="35"/>
-      <c r="AB62" s="35"/>
-      <c r="AC62" s="35"/>
-      <c r="AD62" s="35"/>
-      <c r="AE62" s="35"/>
-      <c r="AF62" s="35"/>
-      <c r="AG62" s="35"/>
-      <c r="AH62" s="35"/>
-      <c r="AI62" s="35"/>
-      <c r="AJ62" s="35"/>
-      <c r="AK62" s="35"/>
-      <c r="AL62" s="35"/>
-      <c r="AM62" s="35"/>
-      <c r="AN62" s="35"/>
-      <c r="AO62" s="35"/>
-      <c r="AP62" s="35"/>
-      <c r="AQ62" s="35"/>
-      <c r="AR62" s="35"/>
-      <c r="AS62" s="35"/>
-      <c r="AT62" s="35"/>
-      <c r="AU62" s="35"/>
+      <c r="S62" s="16"/>
+      <c r="T62" s="16"/>
+      <c r="U62" s="12"/>
+      <c r="V62" s="12"/>
+      <c r="W62" s="12"/>
+      <c r="X62" s="12"/>
+      <c r="Y62" s="12"/>
+      <c r="Z62" s="12"/>
+      <c r="AA62" s="12"/>
+      <c r="AB62" s="12"/>
+      <c r="AC62" s="12"/>
+      <c r="AD62" s="12"/>
+      <c r="AE62" s="12"/>
+      <c r="AF62" s="12"/>
+      <c r="AG62" s="12"/>
+      <c r="AH62" s="12"/>
+      <c r="AI62" s="12"/>
+      <c r="AJ62" s="12"/>
+      <c r="AK62" s="12"/>
+      <c r="AL62" s="12"/>
+      <c r="AM62" s="12"/>
+      <c r="AN62" s="12"/>
+      <c r="AO62" s="12"/>
+      <c r="AP62" s="12"/>
+      <c r="AQ62" s="12"/>
+      <c r="AR62" s="12"/>
+      <c r="AS62" s="12"/>
+      <c r="AT62" s="12"/>
+      <c r="AU62" s="12"/>
       <c r="AV62" s="12"/>
       <c r="AW62" s="12"/>
       <c r="AX62" s="12"/>
@@ -9271,35 +9118,35 @@
         <v>17</v>
       </c>
       <c r="Q63" s="8"/>
-      <c r="S63" s="36"/>
-      <c r="T63" s="36"/>
-      <c r="U63" s="36"/>
-      <c r="V63" s="36"/>
-      <c r="W63" s="36"/>
-      <c r="X63" s="36"/>
-      <c r="Y63" s="36"/>
-      <c r="Z63" s="36"/>
-      <c r="AA63" s="36"/>
-      <c r="AB63" s="36"/>
-      <c r="AC63" s="36"/>
-      <c r="AD63" s="36"/>
-      <c r="AE63" s="36"/>
-      <c r="AF63" s="36"/>
-      <c r="AG63" s="36"/>
-      <c r="AH63" s="38"/>
-      <c r="AI63" s="38"/>
-      <c r="AJ63" s="38"/>
-      <c r="AK63" s="38"/>
-      <c r="AL63" s="38"/>
-      <c r="AM63" s="38"/>
-      <c r="AN63" s="38"/>
-      <c r="AO63" s="38"/>
-      <c r="AP63" s="38"/>
-      <c r="AQ63" s="38"/>
-      <c r="AR63" s="38"/>
-      <c r="AS63" s="38"/>
-      <c r="AT63" s="38"/>
-      <c r="AU63" s="38"/>
+      <c r="S63" s="15"/>
+      <c r="T63" s="15"/>
+      <c r="U63" s="15"/>
+      <c r="V63" s="15"/>
+      <c r="W63" s="15"/>
+      <c r="X63" s="15"/>
+      <c r="Y63" s="15"/>
+      <c r="Z63" s="15"/>
+      <c r="AA63" s="15"/>
+      <c r="AB63" s="15"/>
+      <c r="AC63" s="15"/>
+      <c r="AD63" s="15"/>
+      <c r="AE63" s="15"/>
+      <c r="AF63" s="15"/>
+      <c r="AG63" s="15"/>
+      <c r="AH63" s="11"/>
+      <c r="AI63" s="11"/>
+      <c r="AJ63" s="11"/>
+      <c r="AK63" s="11"/>
+      <c r="AL63" s="11"/>
+      <c r="AM63" s="11"/>
+      <c r="AN63" s="11"/>
+      <c r="AO63" s="11"/>
+      <c r="AP63" s="11"/>
+      <c r="AQ63" s="11"/>
+      <c r="AR63" s="11"/>
+      <c r="AS63" s="11"/>
+      <c r="AT63" s="11"/>
+      <c r="AU63" s="11"/>
       <c r="AV63" s="11"/>
       <c r="AW63" s="11"/>
       <c r="AX63" s="11"/>
@@ -9405,35 +9252,35 @@
       <c r="O64" s="7"/>
       <c r="P64" s="8"/>
       <c r="Q64" s="8"/>
-      <c r="S64" s="37"/>
-      <c r="T64" s="37"/>
-      <c r="U64" s="37"/>
-      <c r="V64" s="37"/>
-      <c r="W64" s="37"/>
-      <c r="X64" s="37"/>
-      <c r="Y64" s="37"/>
-      <c r="Z64" s="37"/>
-      <c r="AA64" s="37"/>
-      <c r="AB64" s="37"/>
-      <c r="AC64" s="37"/>
-      <c r="AD64" s="37"/>
-      <c r="AE64" s="37"/>
-      <c r="AF64" s="37"/>
-      <c r="AG64" s="37"/>
-      <c r="AH64" s="35"/>
-      <c r="AI64" s="35"/>
-      <c r="AJ64" s="35"/>
-      <c r="AK64" s="35"/>
-      <c r="AL64" s="35"/>
-      <c r="AM64" s="35"/>
-      <c r="AN64" s="35"/>
-      <c r="AO64" s="35"/>
-      <c r="AP64" s="35"/>
-      <c r="AQ64" s="35"/>
-      <c r="AR64" s="35"/>
-      <c r="AS64" s="35"/>
-      <c r="AT64" s="35"/>
-      <c r="AU64" s="35"/>
+      <c r="S64" s="16"/>
+      <c r="T64" s="16"/>
+      <c r="U64" s="16"/>
+      <c r="V64" s="16"/>
+      <c r="W64" s="16"/>
+      <c r="X64" s="16"/>
+      <c r="Y64" s="16"/>
+      <c r="Z64" s="16"/>
+      <c r="AA64" s="16"/>
+      <c r="AB64" s="16"/>
+      <c r="AC64" s="16"/>
+      <c r="AD64" s="16"/>
+      <c r="AE64" s="16"/>
+      <c r="AF64" s="16"/>
+      <c r="AG64" s="16"/>
+      <c r="AH64" s="12"/>
+      <c r="AI64" s="12"/>
+      <c r="AJ64" s="12"/>
+      <c r="AK64" s="12"/>
+      <c r="AL64" s="12"/>
+      <c r="AM64" s="12"/>
+      <c r="AN64" s="12"/>
+      <c r="AO64" s="12"/>
+      <c r="AP64" s="12"/>
+      <c r="AQ64" s="12"/>
+      <c r="AR64" s="12"/>
+      <c r="AS64" s="12"/>
+      <c r="AT64" s="12"/>
+      <c r="AU64" s="12"/>
       <c r="AV64" s="12"/>
       <c r="AW64" s="12"/>
       <c r="AX64" s="12"/>
@@ -9545,35 +9392,35 @@
         <v>17</v>
       </c>
       <c r="Q65" s="8"/>
-      <c r="S65" s="36"/>
-      <c r="T65" s="36"/>
-      <c r="U65" s="38"/>
-      <c r="V65" s="38"/>
-      <c r="W65" s="38"/>
-      <c r="X65" s="38"/>
-      <c r="Y65" s="38"/>
-      <c r="Z65" s="38"/>
-      <c r="AA65" s="38"/>
-      <c r="AB65" s="38"/>
-      <c r="AC65" s="38"/>
-      <c r="AD65" s="38"/>
-      <c r="AE65" s="38"/>
-      <c r="AF65" s="38"/>
-      <c r="AG65" s="38"/>
-      <c r="AH65" s="38"/>
-      <c r="AI65" s="38"/>
-      <c r="AJ65" s="38"/>
-      <c r="AK65" s="38"/>
-      <c r="AL65" s="38"/>
-      <c r="AM65" s="38"/>
-      <c r="AN65" s="38"/>
-      <c r="AO65" s="38"/>
-      <c r="AP65" s="38"/>
-      <c r="AQ65" s="38"/>
-      <c r="AR65" s="38"/>
-      <c r="AS65" s="38"/>
-      <c r="AT65" s="38"/>
-      <c r="AU65" s="38"/>
+      <c r="S65" s="15"/>
+      <c r="T65" s="15"/>
+      <c r="U65" s="11"/>
+      <c r="V65" s="11"/>
+      <c r="W65" s="11"/>
+      <c r="X65" s="11"/>
+      <c r="Y65" s="11"/>
+      <c r="Z65" s="11"/>
+      <c r="AA65" s="11"/>
+      <c r="AB65" s="11"/>
+      <c r="AC65" s="11"/>
+      <c r="AD65" s="11"/>
+      <c r="AE65" s="11"/>
+      <c r="AF65" s="11"/>
+      <c r="AG65" s="11"/>
+      <c r="AH65" s="11"/>
+      <c r="AI65" s="11"/>
+      <c r="AJ65" s="11"/>
+      <c r="AK65" s="11"/>
+      <c r="AL65" s="11"/>
+      <c r="AM65" s="11"/>
+      <c r="AN65" s="11"/>
+      <c r="AO65" s="11"/>
+      <c r="AP65" s="11"/>
+      <c r="AQ65" s="11"/>
+      <c r="AR65" s="11"/>
+      <c r="AS65" s="11"/>
+      <c r="AT65" s="11"/>
+      <c r="AU65" s="11"/>
       <c r="AV65" s="11"/>
       <c r="AW65" s="11"/>
       <c r="AX65" s="11"/>
@@ -9679,35 +9526,35 @@
       <c r="O66" s="7"/>
       <c r="P66" s="8"/>
       <c r="Q66" s="8"/>
-      <c r="S66" s="37"/>
-      <c r="T66" s="37"/>
-      <c r="U66" s="35"/>
-      <c r="V66" s="35"/>
-      <c r="W66" s="35"/>
-      <c r="X66" s="35"/>
-      <c r="Y66" s="35"/>
-      <c r="Z66" s="35"/>
-      <c r="AA66" s="35"/>
-      <c r="AB66" s="35"/>
-      <c r="AC66" s="35"/>
-      <c r="AD66" s="35"/>
-      <c r="AE66" s="35"/>
-      <c r="AF66" s="35"/>
-      <c r="AG66" s="35"/>
-      <c r="AH66" s="35"/>
-      <c r="AI66" s="35"/>
-      <c r="AJ66" s="35"/>
-      <c r="AK66" s="35"/>
-      <c r="AL66" s="35"/>
-      <c r="AM66" s="35"/>
-      <c r="AN66" s="35"/>
-      <c r="AO66" s="35"/>
-      <c r="AP66" s="35"/>
-      <c r="AQ66" s="35"/>
-      <c r="AR66" s="35"/>
-      <c r="AS66" s="35"/>
-      <c r="AT66" s="35"/>
-      <c r="AU66" s="35"/>
+      <c r="S66" s="16"/>
+      <c r="T66" s="16"/>
+      <c r="U66" s="12"/>
+      <c r="V66" s="12"/>
+      <c r="W66" s="12"/>
+      <c r="X66" s="12"/>
+      <c r="Y66" s="12"/>
+      <c r="Z66" s="12"/>
+      <c r="AA66" s="12"/>
+      <c r="AB66" s="12"/>
+      <c r="AC66" s="12"/>
+      <c r="AD66" s="12"/>
+      <c r="AE66" s="12"/>
+      <c r="AF66" s="12"/>
+      <c r="AG66" s="12"/>
+      <c r="AH66" s="12"/>
+      <c r="AI66" s="12"/>
+      <c r="AJ66" s="12"/>
+      <c r="AK66" s="12"/>
+      <c r="AL66" s="12"/>
+      <c r="AM66" s="12"/>
+      <c r="AN66" s="12"/>
+      <c r="AO66" s="12"/>
+      <c r="AP66" s="12"/>
+      <c r="AQ66" s="12"/>
+      <c r="AR66" s="12"/>
+      <c r="AS66" s="12"/>
+      <c r="AT66" s="12"/>
+      <c r="AU66" s="12"/>
       <c r="AV66" s="12"/>
       <c r="AW66" s="12"/>
       <c r="AX66" s="12"/>
@@ -9819,35 +9666,35 @@
         <v>17</v>
       </c>
       <c r="Q67" s="8"/>
-      <c r="S67" s="36"/>
-      <c r="T67" s="36"/>
-      <c r="U67" s="38"/>
-      <c r="V67" s="38"/>
-      <c r="W67" s="38"/>
-      <c r="X67" s="38"/>
-      <c r="Y67" s="38"/>
-      <c r="Z67" s="38"/>
-      <c r="AA67" s="38"/>
-      <c r="AB67" s="38"/>
-      <c r="AC67" s="38"/>
-      <c r="AD67" s="38"/>
-      <c r="AE67" s="38"/>
-      <c r="AF67" s="38"/>
-      <c r="AG67" s="38"/>
-      <c r="AH67" s="38"/>
-      <c r="AI67" s="38"/>
-      <c r="AJ67" s="38"/>
-      <c r="AK67" s="38"/>
-      <c r="AL67" s="38"/>
-      <c r="AM67" s="38"/>
-      <c r="AN67" s="38"/>
-      <c r="AO67" s="38"/>
-      <c r="AP67" s="38"/>
-      <c r="AQ67" s="38"/>
-      <c r="AR67" s="38"/>
-      <c r="AS67" s="38"/>
-      <c r="AT67" s="38"/>
-      <c r="AU67" s="38"/>
+      <c r="S67" s="15"/>
+      <c r="T67" s="15"/>
+      <c r="U67" s="11"/>
+      <c r="V67" s="11"/>
+      <c r="W67" s="11"/>
+      <c r="X67" s="11"/>
+      <c r="Y67" s="11"/>
+      <c r="Z67" s="11"/>
+      <c r="AA67" s="11"/>
+      <c r="AB67" s="11"/>
+      <c r="AC67" s="11"/>
+      <c r="AD67" s="11"/>
+      <c r="AE67" s="11"/>
+      <c r="AF67" s="11"/>
+      <c r="AG67" s="11"/>
+      <c r="AH67" s="11"/>
+      <c r="AI67" s="11"/>
+      <c r="AJ67" s="11"/>
+      <c r="AK67" s="11"/>
+      <c r="AL67" s="11"/>
+      <c r="AM67" s="11"/>
+      <c r="AN67" s="11"/>
+      <c r="AO67" s="11"/>
+      <c r="AP67" s="11"/>
+      <c r="AQ67" s="11"/>
+      <c r="AR67" s="11"/>
+      <c r="AS67" s="11"/>
+      <c r="AT67" s="11"/>
+      <c r="AU67" s="11"/>
       <c r="AV67" s="11"/>
       <c r="AW67" s="11"/>
       <c r="AX67" s="11"/>
@@ -9953,35 +9800,35 @@
       <c r="O68" s="7"/>
       <c r="P68" s="8"/>
       <c r="Q68" s="8"/>
-      <c r="S68" s="37"/>
-      <c r="T68" s="37"/>
-      <c r="U68" s="35"/>
-      <c r="V68" s="35"/>
-      <c r="W68" s="35"/>
-      <c r="X68" s="35"/>
-      <c r="Y68" s="35"/>
-      <c r="Z68" s="35"/>
-      <c r="AA68" s="35"/>
-      <c r="AB68" s="35"/>
-      <c r="AC68" s="35"/>
-      <c r="AD68" s="35"/>
-      <c r="AE68" s="35"/>
-      <c r="AF68" s="35"/>
-      <c r="AG68" s="35"/>
-      <c r="AH68" s="35"/>
-      <c r="AI68" s="35"/>
-      <c r="AJ68" s="35"/>
-      <c r="AK68" s="35"/>
-      <c r="AL68" s="35"/>
-      <c r="AM68" s="35"/>
-      <c r="AN68" s="35"/>
-      <c r="AO68" s="35"/>
-      <c r="AP68" s="35"/>
-      <c r="AQ68" s="35"/>
-      <c r="AR68" s="35"/>
-      <c r="AS68" s="35"/>
-      <c r="AT68" s="35"/>
-      <c r="AU68" s="35"/>
+      <c r="S68" s="16"/>
+      <c r="T68" s="16"/>
+      <c r="U68" s="12"/>
+      <c r="V68" s="12"/>
+      <c r="W68" s="12"/>
+      <c r="X68" s="12"/>
+      <c r="Y68" s="12"/>
+      <c r="Z68" s="12"/>
+      <c r="AA68" s="12"/>
+      <c r="AB68" s="12"/>
+      <c r="AC68" s="12"/>
+      <c r="AD68" s="12"/>
+      <c r="AE68" s="12"/>
+      <c r="AF68" s="12"/>
+      <c r="AG68" s="12"/>
+      <c r="AH68" s="12"/>
+      <c r="AI68" s="12"/>
+      <c r="AJ68" s="12"/>
+      <c r="AK68" s="12"/>
+      <c r="AL68" s="12"/>
+      <c r="AM68" s="12"/>
+      <c r="AN68" s="12"/>
+      <c r="AO68" s="12"/>
+      <c r="AP68" s="12"/>
+      <c r="AQ68" s="12"/>
+      <c r="AR68" s="12"/>
+      <c r="AS68" s="12"/>
+      <c r="AT68" s="12"/>
+      <c r="AU68" s="12"/>
       <c r="AV68" s="12"/>
       <c r="AW68" s="12"/>
       <c r="AX68" s="12"/>
@@ -10093,35 +9940,35 @@
         <v>17</v>
       </c>
       <c r="Q69" s="8"/>
-      <c r="S69" s="36"/>
-      <c r="T69" s="36"/>
-      <c r="U69" s="38"/>
-      <c r="V69" s="38"/>
-      <c r="W69" s="38"/>
-      <c r="X69" s="38"/>
-      <c r="Y69" s="38"/>
-      <c r="Z69" s="38"/>
-      <c r="AA69" s="38"/>
-      <c r="AB69" s="38"/>
-      <c r="AC69" s="38"/>
-      <c r="AD69" s="38"/>
-      <c r="AE69" s="38"/>
-      <c r="AF69" s="38"/>
-      <c r="AG69" s="38"/>
-      <c r="AH69" s="38"/>
-      <c r="AI69" s="38"/>
-      <c r="AJ69" s="38"/>
-      <c r="AK69" s="38"/>
-      <c r="AL69" s="38"/>
-      <c r="AM69" s="38"/>
-      <c r="AN69" s="38"/>
-      <c r="AO69" s="38"/>
-      <c r="AP69" s="38"/>
-      <c r="AQ69" s="38"/>
-      <c r="AR69" s="38"/>
-      <c r="AS69" s="38"/>
-      <c r="AT69" s="38"/>
-      <c r="AU69" s="38"/>
+      <c r="S69" s="15"/>
+      <c r="T69" s="15"/>
+      <c r="U69" s="11"/>
+      <c r="V69" s="11"/>
+      <c r="W69" s="11"/>
+      <c r="X69" s="11"/>
+      <c r="Y69" s="11"/>
+      <c r="Z69" s="11"/>
+      <c r="AA69" s="11"/>
+      <c r="AB69" s="11"/>
+      <c r="AC69" s="11"/>
+      <c r="AD69" s="11"/>
+      <c r="AE69" s="11"/>
+      <c r="AF69" s="11"/>
+      <c r="AG69" s="11"/>
+      <c r="AH69" s="11"/>
+      <c r="AI69" s="11"/>
+      <c r="AJ69" s="11"/>
+      <c r="AK69" s="11"/>
+      <c r="AL69" s="11"/>
+      <c r="AM69" s="11"/>
+      <c r="AN69" s="11"/>
+      <c r="AO69" s="11"/>
+      <c r="AP69" s="11"/>
+      <c r="AQ69" s="11"/>
+      <c r="AR69" s="11"/>
+      <c r="AS69" s="11"/>
+      <c r="AT69" s="11"/>
+      <c r="AU69" s="11"/>
       <c r="AV69" s="11"/>
       <c r="AW69" s="11"/>
       <c r="AX69" s="11"/>
@@ -10227,35 +10074,35 @@
       <c r="O70" s="7"/>
       <c r="P70" s="8"/>
       <c r="Q70" s="8"/>
-      <c r="S70" s="37"/>
-      <c r="T70" s="37"/>
-      <c r="U70" s="35"/>
-      <c r="V70" s="35"/>
-      <c r="W70" s="35"/>
-      <c r="X70" s="35"/>
-      <c r="Y70" s="35"/>
-      <c r="Z70" s="35"/>
-      <c r="AA70" s="35"/>
-      <c r="AB70" s="35"/>
-      <c r="AC70" s="35"/>
-      <c r="AD70" s="35"/>
-      <c r="AE70" s="35"/>
-      <c r="AF70" s="35"/>
-      <c r="AG70" s="35"/>
-      <c r="AH70" s="35"/>
-      <c r="AI70" s="35"/>
-      <c r="AJ70" s="35"/>
-      <c r="AK70" s="35"/>
-      <c r="AL70" s="35"/>
-      <c r="AM70" s="35"/>
-      <c r="AN70" s="35"/>
-      <c r="AO70" s="35"/>
-      <c r="AP70" s="35"/>
-      <c r="AQ70" s="35"/>
-      <c r="AR70" s="35"/>
-      <c r="AS70" s="35"/>
-      <c r="AT70" s="35"/>
-      <c r="AU70" s="35"/>
+      <c r="S70" s="16"/>
+      <c r="T70" s="16"/>
+      <c r="U70" s="12"/>
+      <c r="V70" s="12"/>
+      <c r="W70" s="12"/>
+      <c r="X70" s="12"/>
+      <c r="Y70" s="12"/>
+      <c r="Z70" s="12"/>
+      <c r="AA70" s="12"/>
+      <c r="AB70" s="12"/>
+      <c r="AC70" s="12"/>
+      <c r="AD70" s="12"/>
+      <c r="AE70" s="12"/>
+      <c r="AF70" s="12"/>
+      <c r="AG70" s="12"/>
+      <c r="AH70" s="12"/>
+      <c r="AI70" s="12"/>
+      <c r="AJ70" s="12"/>
+      <c r="AK70" s="12"/>
+      <c r="AL70" s="12"/>
+      <c r="AM70" s="12"/>
+      <c r="AN70" s="12"/>
+      <c r="AO70" s="12"/>
+      <c r="AP70" s="12"/>
+      <c r="AQ70" s="12"/>
+      <c r="AR70" s="12"/>
+      <c r="AS70" s="12"/>
+      <c r="AT70" s="12"/>
+      <c r="AU70" s="12"/>
       <c r="AV70" s="12"/>
       <c r="AW70" s="12"/>
       <c r="AX70" s="12"/>
@@ -10367,21 +10214,21 @@
         <v>17</v>
       </c>
       <c r="Q71" s="8"/>
-      <c r="S71" s="13"/>
-      <c r="T71" s="13"/>
-      <c r="U71" s="13"/>
-      <c r="V71" s="13"/>
-      <c r="W71" s="13"/>
-      <c r="X71" s="13"/>
-      <c r="Y71" s="13"/>
-      <c r="Z71" s="13"/>
-      <c r="AA71" s="13"/>
-      <c r="AB71" s="13"/>
-      <c r="AC71" s="13"/>
-      <c r="AD71" s="13"/>
-      <c r="AE71" s="13"/>
-      <c r="AF71" s="13"/>
-      <c r="AG71" s="13"/>
+      <c r="S71" s="15"/>
+      <c r="T71" s="15"/>
+      <c r="U71" s="15"/>
+      <c r="V71" s="15"/>
+      <c r="W71" s="15"/>
+      <c r="X71" s="15"/>
+      <c r="Y71" s="15"/>
+      <c r="Z71" s="15"/>
+      <c r="AA71" s="15"/>
+      <c r="AB71" s="15"/>
+      <c r="AC71" s="15"/>
+      <c r="AD71" s="15"/>
+      <c r="AE71" s="15"/>
+      <c r="AF71" s="15"/>
+      <c r="AG71" s="15"/>
       <c r="AH71" s="11"/>
       <c r="AI71" s="11"/>
       <c r="AJ71" s="11"/>
@@ -10660,8 +10507,8 @@
         <v>17</v>
       </c>
       <c r="Q74" s="8"/>
-      <c r="S74" s="13"/>
-      <c r="T74" s="13"/>
+      <c r="S74" s="15"/>
+      <c r="T74" s="15"/>
       <c r="U74" s="11"/>
       <c r="V74" s="11"/>
       <c r="W74" s="11"/>
@@ -10934,8 +10781,8 @@
         <v>17</v>
       </c>
       <c r="Q76" s="8"/>
-      <c r="S76" s="13"/>
-      <c r="T76" s="13"/>
+      <c r="S76" s="15"/>
+      <c r="T76" s="15"/>
       <c r="U76" s="11"/>
       <c r="V76" s="11"/>
       <c r="W76" s="11"/>
@@ -11208,21 +11055,21 @@
         <v>17</v>
       </c>
       <c r="Q78" s="8"/>
-      <c r="S78" s="13"/>
-      <c r="T78" s="13"/>
-      <c r="U78" s="13"/>
-      <c r="V78" s="13"/>
-      <c r="W78" s="13"/>
-      <c r="X78" s="13"/>
-      <c r="Y78" s="13"/>
-      <c r="Z78" s="13"/>
-      <c r="AA78" s="13"/>
-      <c r="AB78" s="13"/>
-      <c r="AC78" s="13"/>
-      <c r="AD78" s="13"/>
-      <c r="AE78" s="13"/>
-      <c r="AF78" s="13"/>
-      <c r="AG78" s="13"/>
+      <c r="S78" s="15"/>
+      <c r="T78" s="15"/>
+      <c r="U78" s="15"/>
+      <c r="V78" s="15"/>
+      <c r="W78" s="15"/>
+      <c r="X78" s="15"/>
+      <c r="Y78" s="15"/>
+      <c r="Z78" s="15"/>
+      <c r="AA78" s="15"/>
+      <c r="AB78" s="15"/>
+      <c r="AC78" s="15"/>
+      <c r="AD78" s="15"/>
+      <c r="AE78" s="15"/>
+      <c r="AF78" s="15"/>
+      <c r="AG78" s="15"/>
       <c r="AH78" s="11"/>
       <c r="AI78" s="11"/>
       <c r="AJ78" s="11"/>
@@ -11482,6 +11329,16 @@
     <mergeCell ref="DW78:DW79"/>
     <mergeCell ref="DX78:DX79"/>
     <mergeCell ref="DY78:DY79"/>
+    <mergeCell ref="DX76:DX77"/>
+    <mergeCell ref="DY76:DY77"/>
+    <mergeCell ref="DZ76:DZ77"/>
+    <mergeCell ref="EA76:EA77"/>
+    <mergeCell ref="EB76:EB77"/>
+    <mergeCell ref="EC76:EC77"/>
+    <mergeCell ref="DO76:DO77"/>
+    <mergeCell ref="DP76:DP77"/>
+    <mergeCell ref="DQ76:DQ77"/>
+    <mergeCell ref="DR76:DR77"/>
     <mergeCell ref="CR78:CR79"/>
     <mergeCell ref="CS78:CS79"/>
     <mergeCell ref="CT78:CT79"/>
@@ -11550,12 +11407,6 @@
     <mergeCell ref="BG78:BG79"/>
     <mergeCell ref="BH78:BH79"/>
     <mergeCell ref="BI78:BI79"/>
-    <mergeCell ref="DX76:DX77"/>
-    <mergeCell ref="DY76:DY77"/>
-    <mergeCell ref="DZ76:DZ77"/>
-    <mergeCell ref="EA76:EA77"/>
-    <mergeCell ref="EB76:EB77"/>
-    <mergeCell ref="EC76:EC77"/>
     <mergeCell ref="S78:S79"/>
     <mergeCell ref="T78:T79"/>
     <mergeCell ref="U78:U79"/>
@@ -11590,10 +11441,21 @@
     <mergeCell ref="DL76:DL77"/>
     <mergeCell ref="DM76:DM77"/>
     <mergeCell ref="DN76:DN77"/>
-    <mergeCell ref="DO76:DO77"/>
-    <mergeCell ref="DP76:DP77"/>
-    <mergeCell ref="DQ76:DQ77"/>
-    <mergeCell ref="DR76:DR77"/>
+    <mergeCell ref="BY76:BY77"/>
+    <mergeCell ref="BZ76:BZ77"/>
+    <mergeCell ref="CA76:CA77"/>
+    <mergeCell ref="CB76:CB77"/>
+    <mergeCell ref="CC76:CC77"/>
+    <mergeCell ref="CD76:CD77"/>
+    <mergeCell ref="CE76:CE77"/>
+    <mergeCell ref="CF76:CF77"/>
+    <mergeCell ref="CG76:CG77"/>
+    <mergeCell ref="CH76:CH77"/>
+    <mergeCell ref="CI76:CI77"/>
+    <mergeCell ref="CJ76:CJ77"/>
+    <mergeCell ref="CK76:CK77"/>
+    <mergeCell ref="CL76:CL77"/>
+    <mergeCell ref="CM76:CM77"/>
     <mergeCell ref="DS76:DS77"/>
     <mergeCell ref="DT76:DT77"/>
     <mergeCell ref="DU76:DU77"/>
@@ -11616,21 +11478,6 @@
     <mergeCell ref="DD76:DD77"/>
     <mergeCell ref="DE76:DE77"/>
     <mergeCell ref="DF76:DF77"/>
-    <mergeCell ref="BY76:BY77"/>
-    <mergeCell ref="BZ76:BZ77"/>
-    <mergeCell ref="CA76:CA77"/>
-    <mergeCell ref="CB76:CB77"/>
-    <mergeCell ref="CC76:CC77"/>
-    <mergeCell ref="CD76:CD77"/>
-    <mergeCell ref="CE76:CE77"/>
-    <mergeCell ref="CF76:CF77"/>
-    <mergeCell ref="CG76:CG77"/>
-    <mergeCell ref="CH76:CH77"/>
-    <mergeCell ref="CI76:CI77"/>
-    <mergeCell ref="CJ76:CJ77"/>
-    <mergeCell ref="CK76:CK77"/>
-    <mergeCell ref="CL76:CL77"/>
-    <mergeCell ref="CM76:CM77"/>
     <mergeCell ref="CN76:CN77"/>
     <mergeCell ref="CO76:CO77"/>
     <mergeCell ref="BH76:BH77"/>
@@ -11782,23 +11629,6 @@
     <mergeCell ref="AJ71:AJ72"/>
     <mergeCell ref="AK71:AK72"/>
     <mergeCell ref="AL71:AL72"/>
-    <mergeCell ref="CJ69:CJ70"/>
-    <mergeCell ref="CK69:CK70"/>
-    <mergeCell ref="CL69:CL70"/>
-    <mergeCell ref="CM69:CM70"/>
-    <mergeCell ref="CN69:CN70"/>
-    <mergeCell ref="CO69:CO70"/>
-    <mergeCell ref="CP69:CP70"/>
-    <mergeCell ref="CQ69:CQ70"/>
-    <mergeCell ref="CR69:CR70"/>
-    <mergeCell ref="CS69:CS70"/>
-    <mergeCell ref="CT69:CT70"/>
-    <mergeCell ref="CU69:CU70"/>
-    <mergeCell ref="CV69:CV70"/>
-    <mergeCell ref="CW69:CW70"/>
-    <mergeCell ref="CX69:CX70"/>
-    <mergeCell ref="CY69:CY70"/>
-    <mergeCell ref="CZ69:CZ70"/>
     <mergeCell ref="BC69:BC70"/>
     <mergeCell ref="BD69:BD70"/>
     <mergeCell ref="BE69:BE70"/>
@@ -11950,6 +11780,21 @@
     <mergeCell ref="DO63:DO64"/>
     <mergeCell ref="DP63:DP64"/>
     <mergeCell ref="DQ63:DQ64"/>
+    <mergeCell ref="AU63:AU64"/>
+    <mergeCell ref="AV63:AV64"/>
+    <mergeCell ref="AW63:AW64"/>
+    <mergeCell ref="AX63:AX64"/>
+    <mergeCell ref="AY63:AY64"/>
+    <mergeCell ref="AZ63:AZ64"/>
+    <mergeCell ref="BA63:BA64"/>
+    <mergeCell ref="BB63:BB64"/>
+    <mergeCell ref="BC63:BC64"/>
+    <mergeCell ref="BD63:BD64"/>
+    <mergeCell ref="BE63:BE64"/>
+    <mergeCell ref="BF63:BF64"/>
+    <mergeCell ref="BG63:BG64"/>
+    <mergeCell ref="BH63:BH64"/>
+    <mergeCell ref="BI63:BI64"/>
     <mergeCell ref="DR63:DR64"/>
     <mergeCell ref="DS63:DS64"/>
     <mergeCell ref="DT63:DT64"/>
@@ -11977,21 +11822,11 @@
     <mergeCell ref="CQ63:CQ64"/>
     <mergeCell ref="CR63:CR64"/>
     <mergeCell ref="CS63:CS64"/>
-    <mergeCell ref="AU63:AU64"/>
-    <mergeCell ref="AV63:AV64"/>
-    <mergeCell ref="AW63:AW64"/>
-    <mergeCell ref="AX63:AX64"/>
-    <mergeCell ref="AY63:AY64"/>
-    <mergeCell ref="AZ63:AZ64"/>
-    <mergeCell ref="BA63:BA64"/>
-    <mergeCell ref="BB63:BB64"/>
-    <mergeCell ref="BC63:BC64"/>
-    <mergeCell ref="BD63:BD64"/>
-    <mergeCell ref="BE63:BE64"/>
-    <mergeCell ref="BF63:BF64"/>
-    <mergeCell ref="BG63:BG64"/>
-    <mergeCell ref="BH63:BH64"/>
-    <mergeCell ref="BI63:BI64"/>
+    <mergeCell ref="CX63:CX64"/>
+    <mergeCell ref="CY63:CY64"/>
+    <mergeCell ref="CZ63:CZ64"/>
+    <mergeCell ref="DA63:DA64"/>
+    <mergeCell ref="DB63:DB64"/>
     <mergeCell ref="BJ63:BJ64"/>
     <mergeCell ref="BK63:BK64"/>
     <mergeCell ref="DZ61:DZ62"/>
@@ -12105,6 +11940,21 @@
     <mergeCell ref="DS74:DS75"/>
     <mergeCell ref="DT74:DT75"/>
     <mergeCell ref="DU74:DU75"/>
+    <mergeCell ref="BY74:BY75"/>
+    <mergeCell ref="BZ74:BZ75"/>
+    <mergeCell ref="CA74:CA75"/>
+    <mergeCell ref="CB74:CB75"/>
+    <mergeCell ref="CC74:CC75"/>
+    <mergeCell ref="CD74:CD75"/>
+    <mergeCell ref="CE74:CE75"/>
+    <mergeCell ref="CF74:CF75"/>
+    <mergeCell ref="CG74:CG75"/>
+    <mergeCell ref="CH74:CH75"/>
+    <mergeCell ref="CI74:CI75"/>
+    <mergeCell ref="CJ74:CJ75"/>
+    <mergeCell ref="CK74:CK75"/>
+    <mergeCell ref="CL74:CL75"/>
+    <mergeCell ref="CM74:CM75"/>
     <mergeCell ref="DV74:DV75"/>
     <mergeCell ref="DW74:DW75"/>
     <mergeCell ref="CP74:CP75"/>
@@ -12124,21 +11974,6 @@
     <mergeCell ref="DD74:DD75"/>
     <mergeCell ref="DE74:DE75"/>
     <mergeCell ref="DF74:DF75"/>
-    <mergeCell ref="BY74:BY75"/>
-    <mergeCell ref="BZ74:BZ75"/>
-    <mergeCell ref="CA74:CA75"/>
-    <mergeCell ref="CB74:CB75"/>
-    <mergeCell ref="CC74:CC75"/>
-    <mergeCell ref="CD74:CD75"/>
-    <mergeCell ref="CE74:CE75"/>
-    <mergeCell ref="CF74:CF75"/>
-    <mergeCell ref="CG74:CG75"/>
-    <mergeCell ref="CH74:CH75"/>
-    <mergeCell ref="CI74:CI75"/>
-    <mergeCell ref="CJ74:CJ75"/>
-    <mergeCell ref="CK74:CK75"/>
-    <mergeCell ref="CL74:CL75"/>
-    <mergeCell ref="CM74:CM75"/>
     <mergeCell ref="CN74:CN75"/>
     <mergeCell ref="CO74:CO75"/>
     <mergeCell ref="BH74:BH75"/>
@@ -12241,6 +12076,21 @@
     <mergeCell ref="DF69:DF70"/>
     <mergeCell ref="DG69:DG70"/>
     <mergeCell ref="DH69:DH70"/>
+    <mergeCell ref="BT69:BT70"/>
+    <mergeCell ref="CJ69:CJ70"/>
+    <mergeCell ref="CK69:CK70"/>
+    <mergeCell ref="CL69:CL70"/>
+    <mergeCell ref="CM69:CM70"/>
+    <mergeCell ref="CN69:CN70"/>
+    <mergeCell ref="CO69:CO70"/>
+    <mergeCell ref="CP69:CP70"/>
+    <mergeCell ref="CQ69:CQ70"/>
+    <mergeCell ref="CR69:CR70"/>
+    <mergeCell ref="CS69:CS70"/>
+    <mergeCell ref="CT69:CT70"/>
+    <mergeCell ref="CU69:CU70"/>
+    <mergeCell ref="CV69:CV70"/>
+    <mergeCell ref="CW69:CW70"/>
     <mergeCell ref="DI69:DI70"/>
     <mergeCell ref="DJ69:DJ70"/>
     <mergeCell ref="DK69:DK70"/>
@@ -12267,7 +12117,9 @@
     <mergeCell ref="CG69:CG70"/>
     <mergeCell ref="CH69:CH70"/>
     <mergeCell ref="CI69:CI70"/>
-    <mergeCell ref="BT69:BT70"/>
+    <mergeCell ref="CX69:CX70"/>
+    <mergeCell ref="CY69:CY70"/>
+    <mergeCell ref="CZ69:CZ70"/>
     <mergeCell ref="AM69:AM70"/>
     <mergeCell ref="AN69:AN70"/>
     <mergeCell ref="AO69:AO70"/>
@@ -12285,6 +12137,21 @@
     <mergeCell ref="BA69:BA70"/>
     <mergeCell ref="DA59:DA60"/>
     <mergeCell ref="DB59:DB60"/>
+    <mergeCell ref="BS59:BS60"/>
+    <mergeCell ref="BT59:BT60"/>
+    <mergeCell ref="BU59:BU60"/>
+    <mergeCell ref="BV59:BV60"/>
+    <mergeCell ref="BW59:BW60"/>
+    <mergeCell ref="BX59:BX60"/>
+    <mergeCell ref="BY59:BY60"/>
+    <mergeCell ref="BZ59:BZ60"/>
+    <mergeCell ref="CA59:CA60"/>
+    <mergeCell ref="CB59:CB60"/>
+    <mergeCell ref="CC59:CC60"/>
+    <mergeCell ref="CD59:CD60"/>
+    <mergeCell ref="CE59:CE60"/>
+    <mergeCell ref="CF59:CF60"/>
+    <mergeCell ref="CG59:CG60"/>
     <mergeCell ref="DC59:DC60"/>
     <mergeCell ref="DD59:DD60"/>
     <mergeCell ref="DE59:DE60"/>
@@ -12313,21 +12180,6 @@
     <mergeCell ref="CV59:CV60"/>
     <mergeCell ref="CW59:CW60"/>
     <mergeCell ref="CX59:CX60"/>
-    <mergeCell ref="BS59:BS60"/>
-    <mergeCell ref="BT59:BT60"/>
-    <mergeCell ref="BU59:BU60"/>
-    <mergeCell ref="BV59:BV60"/>
-    <mergeCell ref="BW59:BW60"/>
-    <mergeCell ref="BX59:BX60"/>
-    <mergeCell ref="BY59:BY60"/>
-    <mergeCell ref="BZ59:BZ60"/>
-    <mergeCell ref="CA59:CA60"/>
-    <mergeCell ref="CB59:CB60"/>
-    <mergeCell ref="CC59:CC60"/>
-    <mergeCell ref="CD59:CD60"/>
-    <mergeCell ref="CE59:CE60"/>
-    <mergeCell ref="CF59:CF60"/>
-    <mergeCell ref="CG59:CG60"/>
     <mergeCell ref="BB59:BB60"/>
     <mergeCell ref="BC59:BC60"/>
     <mergeCell ref="BD59:BD60"/>
@@ -12345,6 +12197,21 @@
     <mergeCell ref="BP59:BP60"/>
     <mergeCell ref="DR52:DR53"/>
     <mergeCell ref="DS52:DS53"/>
+    <mergeCell ref="BB52:BB53"/>
+    <mergeCell ref="BC52:BC53"/>
+    <mergeCell ref="BD52:BD53"/>
+    <mergeCell ref="BE52:BE53"/>
+    <mergeCell ref="BF52:BF53"/>
+    <mergeCell ref="BG52:BG53"/>
+    <mergeCell ref="BH52:BH53"/>
+    <mergeCell ref="BI52:BI53"/>
+    <mergeCell ref="BJ52:BJ53"/>
+    <mergeCell ref="BK52:BK53"/>
+    <mergeCell ref="BL52:BL53"/>
+    <mergeCell ref="BM52:BM53"/>
+    <mergeCell ref="BN52:BN53"/>
+    <mergeCell ref="BO52:BO53"/>
+    <mergeCell ref="BP52:BP53"/>
     <mergeCell ref="DT52:DT53"/>
     <mergeCell ref="DU52:DU53"/>
     <mergeCell ref="DV52:DV53"/>
@@ -12372,21 +12239,9 @@
     <mergeCell ref="CX52:CX53"/>
     <mergeCell ref="CY52:CY53"/>
     <mergeCell ref="CZ52:CZ53"/>
-    <mergeCell ref="BB52:BB53"/>
-    <mergeCell ref="BC52:BC53"/>
-    <mergeCell ref="BD52:BD53"/>
-    <mergeCell ref="BE52:BE53"/>
-    <mergeCell ref="BF52:BF53"/>
-    <mergeCell ref="BG52:BG53"/>
-    <mergeCell ref="BH52:BH53"/>
-    <mergeCell ref="BI52:BI53"/>
-    <mergeCell ref="BJ52:BJ53"/>
-    <mergeCell ref="BK52:BK53"/>
-    <mergeCell ref="BL52:BL53"/>
-    <mergeCell ref="BM52:BM53"/>
-    <mergeCell ref="BN52:BN53"/>
-    <mergeCell ref="BO52:BO53"/>
-    <mergeCell ref="BP52:BP53"/>
+    <mergeCell ref="DO52:DO53"/>
+    <mergeCell ref="DP52:DP53"/>
+    <mergeCell ref="DQ52:DQ53"/>
     <mergeCell ref="BQ52:BQ53"/>
     <mergeCell ref="BR52:BR53"/>
     <mergeCell ref="DR50:DR51"/>
@@ -12436,6 +12291,21 @@
     <mergeCell ref="DK50:DK51"/>
     <mergeCell ref="DL50:DL51"/>
     <mergeCell ref="DM50:DM51"/>
+    <mergeCell ref="CH52:CH53"/>
+    <mergeCell ref="CI52:CI53"/>
+    <mergeCell ref="BS52:BS53"/>
+    <mergeCell ref="BT52:BT53"/>
+    <mergeCell ref="AM52:AM53"/>
+    <mergeCell ref="AN52:AN53"/>
+    <mergeCell ref="AO52:AO53"/>
+    <mergeCell ref="AP52:AP53"/>
+    <mergeCell ref="AQ52:AQ53"/>
+    <mergeCell ref="AR52:AR53"/>
+    <mergeCell ref="AS52:AS53"/>
+    <mergeCell ref="AT52:AT53"/>
+    <mergeCell ref="AU52:AU53"/>
+    <mergeCell ref="AV52:AV53"/>
+    <mergeCell ref="AW52:AW53"/>
     <mergeCell ref="DN50:DN51"/>
     <mergeCell ref="DO50:DO51"/>
     <mergeCell ref="BQ50:BQ51"/>
@@ -12504,23 +12374,6 @@
     <mergeCell ref="AF50:AF51"/>
     <mergeCell ref="AG50:AG51"/>
     <mergeCell ref="AH50:AH51"/>
-    <mergeCell ref="CF48:CF49"/>
-    <mergeCell ref="CG48:CG49"/>
-    <mergeCell ref="CH48:CH49"/>
-    <mergeCell ref="CI48:CI49"/>
-    <mergeCell ref="CJ48:CJ49"/>
-    <mergeCell ref="CK48:CK49"/>
-    <mergeCell ref="CL48:CL49"/>
-    <mergeCell ref="CM48:CM49"/>
-    <mergeCell ref="CN48:CN49"/>
-    <mergeCell ref="CO48:CO49"/>
-    <mergeCell ref="CP48:CP49"/>
-    <mergeCell ref="CQ48:CQ49"/>
-    <mergeCell ref="CR48:CR49"/>
-    <mergeCell ref="CS48:CS49"/>
-    <mergeCell ref="CT48:CT49"/>
-    <mergeCell ref="CU48:CU49"/>
-    <mergeCell ref="CV48:CV49"/>
     <mergeCell ref="AX48:AX49"/>
     <mergeCell ref="AY48:AY49"/>
     <mergeCell ref="AZ48:AZ49"/>
@@ -12587,26 +12440,23 @@
     <mergeCell ref="DI46:DI47"/>
     <mergeCell ref="DJ46:DJ47"/>
     <mergeCell ref="DK46:DK47"/>
+    <mergeCell ref="AJ46:AJ47"/>
+    <mergeCell ref="AK46:AK47"/>
+    <mergeCell ref="AL46:AL47"/>
+    <mergeCell ref="AM46:AM47"/>
+    <mergeCell ref="AN46:AN47"/>
+    <mergeCell ref="AO46:AO47"/>
+    <mergeCell ref="AP46:AP47"/>
+    <mergeCell ref="AQ46:AQ47"/>
+    <mergeCell ref="AR46:AR47"/>
+    <mergeCell ref="AS46:AS47"/>
+    <mergeCell ref="AT46:AT47"/>
+    <mergeCell ref="AU46:AU47"/>
     <mergeCell ref="BM46:BM47"/>
     <mergeCell ref="BN46:BN47"/>
     <mergeCell ref="BO46:BO47"/>
     <mergeCell ref="BP46:BP47"/>
     <mergeCell ref="BQ46:BQ47"/>
-    <mergeCell ref="BR46:BR47"/>
-    <mergeCell ref="BS46:BS47"/>
-    <mergeCell ref="BT46:BT47"/>
-    <mergeCell ref="BU46:BU47"/>
-    <mergeCell ref="BV46:BV47"/>
-    <mergeCell ref="BW46:BW47"/>
-    <mergeCell ref="BX46:BX47"/>
-    <mergeCell ref="BY46:BY47"/>
-    <mergeCell ref="BZ46:BZ47"/>
-    <mergeCell ref="CA46:CA47"/>
-    <mergeCell ref="CB46:CB47"/>
-    <mergeCell ref="CC46:CC47"/>
-    <mergeCell ref="EA44:EA45"/>
-    <mergeCell ref="EB44:EB45"/>
-    <mergeCell ref="EC44:EC45"/>
     <mergeCell ref="S46:S47"/>
     <mergeCell ref="T46:T47"/>
     <mergeCell ref="U46:U47"/>
@@ -12624,21 +12474,6 @@
     <mergeCell ref="AG46:AG47"/>
     <mergeCell ref="AH46:AH47"/>
     <mergeCell ref="AI46:AI47"/>
-    <mergeCell ref="AJ46:AJ47"/>
-    <mergeCell ref="AK46:AK47"/>
-    <mergeCell ref="AL46:AL47"/>
-    <mergeCell ref="AM46:AM47"/>
-    <mergeCell ref="AN46:AN47"/>
-    <mergeCell ref="AO46:AO47"/>
-    <mergeCell ref="AP46:AP47"/>
-    <mergeCell ref="AQ46:AQ47"/>
-    <mergeCell ref="AR46:AR47"/>
-    <mergeCell ref="AS46:AS47"/>
-    <mergeCell ref="AT46:AT47"/>
-    <mergeCell ref="AU46:AU47"/>
-    <mergeCell ref="AR44:AR45"/>
-    <mergeCell ref="AS44:AS45"/>
-    <mergeCell ref="AT44:AT45"/>
     <mergeCell ref="AU44:AU45"/>
     <mergeCell ref="AV44:AV45"/>
     <mergeCell ref="AW44:AW45"/>
@@ -12653,9 +12488,9 @@
     <mergeCell ref="BF44:BF45"/>
     <mergeCell ref="BG44:BG45"/>
     <mergeCell ref="BH44:BH45"/>
-    <mergeCell ref="DW39:DW40"/>
-    <mergeCell ref="DX39:DX40"/>
-    <mergeCell ref="DY39:DY40"/>
+    <mergeCell ref="EA44:EA45"/>
+    <mergeCell ref="EB44:EB45"/>
+    <mergeCell ref="EC44:EC45"/>
     <mergeCell ref="DZ39:DZ40"/>
     <mergeCell ref="EA39:EA40"/>
     <mergeCell ref="EB39:EB40"/>
@@ -12685,9 +12520,9 @@
     <mergeCell ref="AO44:AO45"/>
     <mergeCell ref="AP44:AP45"/>
     <mergeCell ref="AQ44:AQ45"/>
-    <mergeCell ref="DF39:DF40"/>
-    <mergeCell ref="DG39:DG40"/>
-    <mergeCell ref="DH39:DH40"/>
+    <mergeCell ref="AR44:AR45"/>
+    <mergeCell ref="AS44:AS45"/>
+    <mergeCell ref="AT44:AT45"/>
     <mergeCell ref="DI39:DI40"/>
     <mergeCell ref="DJ39:DJ40"/>
     <mergeCell ref="DK39:DK40"/>
@@ -12702,9 +12537,9 @@
     <mergeCell ref="DT39:DT40"/>
     <mergeCell ref="DU39:DU40"/>
     <mergeCell ref="DV39:DV40"/>
-    <mergeCell ref="CK39:CK40"/>
-    <mergeCell ref="CL39:CL40"/>
-    <mergeCell ref="CM39:CM40"/>
+    <mergeCell ref="DW39:DW40"/>
+    <mergeCell ref="DX39:DX40"/>
+    <mergeCell ref="DY39:DY40"/>
     <mergeCell ref="CN39:CN40"/>
     <mergeCell ref="CO39:CO40"/>
     <mergeCell ref="CP39:CP40"/>
@@ -12719,6 +12554,9 @@
     <mergeCell ref="CY39:CY40"/>
     <mergeCell ref="CZ39:CZ40"/>
     <mergeCell ref="DA39:DA40"/>
+    <mergeCell ref="DF39:DF40"/>
+    <mergeCell ref="DG39:DG40"/>
+    <mergeCell ref="DH39:DH40"/>
     <mergeCell ref="BT39:BT40"/>
     <mergeCell ref="BU39:BU40"/>
     <mergeCell ref="BV39:BV40"/>
@@ -12785,6 +12623,8 @@
     <mergeCell ref="AM39:AM40"/>
     <mergeCell ref="AN39:AN40"/>
     <mergeCell ref="AO39:AO40"/>
+    <mergeCell ref="BT37:BT38"/>
+    <mergeCell ref="BU37:BU38"/>
     <mergeCell ref="CM37:CM38"/>
     <mergeCell ref="CN37:CN38"/>
     <mergeCell ref="CO37:CO38"/>
@@ -12800,8 +12640,8 @@
     <mergeCell ref="CY37:CY38"/>
     <mergeCell ref="CZ37:CZ38"/>
     <mergeCell ref="DA37:DA38"/>
-    <mergeCell ref="DB37:DB38"/>
-    <mergeCell ref="DC37:DC38"/>
+    <mergeCell ref="AN37:AN38"/>
+    <mergeCell ref="AO37:AO38"/>
     <mergeCell ref="BE37:BE38"/>
     <mergeCell ref="BF37:BF38"/>
     <mergeCell ref="BG37:BG38"/>
@@ -12817,8 +12657,8 @@
     <mergeCell ref="BQ37:BQ38"/>
     <mergeCell ref="BR37:BR38"/>
     <mergeCell ref="BS37:BS38"/>
-    <mergeCell ref="BT37:BT38"/>
-    <mergeCell ref="BU37:BU38"/>
+    <mergeCell ref="DQ35:DQ36"/>
+    <mergeCell ref="DR35:DR36"/>
     <mergeCell ref="DU35:DU36"/>
     <mergeCell ref="DV35:DV36"/>
     <mergeCell ref="DW35:DW36"/>
@@ -12849,8 +12689,8 @@
     <mergeCell ref="AK37:AK38"/>
     <mergeCell ref="AL37:AL38"/>
     <mergeCell ref="AM37:AM38"/>
-    <mergeCell ref="AN37:AN38"/>
-    <mergeCell ref="AO37:AO38"/>
+    <mergeCell ref="CI35:CI36"/>
+    <mergeCell ref="CJ35:CJ36"/>
     <mergeCell ref="DB35:DB36"/>
     <mergeCell ref="DC35:DC36"/>
     <mergeCell ref="DD35:DD36"/>
@@ -12866,25 +12706,6 @@
     <mergeCell ref="DN35:DN36"/>
     <mergeCell ref="DO35:DO36"/>
     <mergeCell ref="DP35:DP36"/>
-    <mergeCell ref="DQ35:DQ36"/>
-    <mergeCell ref="DR35:DR36"/>
-    <mergeCell ref="BT35:BT36"/>
-    <mergeCell ref="BU35:BU36"/>
-    <mergeCell ref="BV35:BV36"/>
-    <mergeCell ref="BW35:BW36"/>
-    <mergeCell ref="BX35:BX36"/>
-    <mergeCell ref="BY35:BY36"/>
-    <mergeCell ref="BZ35:BZ36"/>
-    <mergeCell ref="CA35:CA36"/>
-    <mergeCell ref="CB35:CB36"/>
-    <mergeCell ref="CC35:CC36"/>
-    <mergeCell ref="CD35:CD36"/>
-    <mergeCell ref="CE35:CE36"/>
-    <mergeCell ref="CF35:CF36"/>
-    <mergeCell ref="CG35:CG36"/>
-    <mergeCell ref="CH35:CH36"/>
-    <mergeCell ref="CI35:CI36"/>
-    <mergeCell ref="CJ35:CJ36"/>
     <mergeCell ref="AL35:AL36"/>
     <mergeCell ref="AM35:AM36"/>
     <mergeCell ref="AN35:AN36"/>
@@ -13081,11 +12902,6 @@
     <mergeCell ref="EC65:EC66"/>
     <mergeCell ref="CV63:CV64"/>
     <mergeCell ref="CW63:CW64"/>
-    <mergeCell ref="CX63:CX64"/>
-    <mergeCell ref="CY63:CY64"/>
-    <mergeCell ref="CZ63:CZ64"/>
-    <mergeCell ref="DA63:DA64"/>
-    <mergeCell ref="DB63:DB64"/>
     <mergeCell ref="DC63:DC64"/>
     <mergeCell ref="DD63:DD64"/>
     <mergeCell ref="DE63:DE64"/>
@@ -13111,18 +12927,6 @@
     <mergeCell ref="BZ63:BZ64"/>
     <mergeCell ref="CA63:CA64"/>
     <mergeCell ref="CB63:CB64"/>
-    <mergeCell ref="BL63:BL64"/>
-    <mergeCell ref="BM63:BM64"/>
-    <mergeCell ref="DK61:DK62"/>
-    <mergeCell ref="DL61:DL62"/>
-    <mergeCell ref="DM61:DM62"/>
-    <mergeCell ref="DN61:DN62"/>
-    <mergeCell ref="DO61:DO62"/>
-    <mergeCell ref="DP61:DP62"/>
-    <mergeCell ref="DQ61:DQ62"/>
-    <mergeCell ref="DR61:DR62"/>
-    <mergeCell ref="DS61:DS62"/>
-    <mergeCell ref="DT61:DT62"/>
     <mergeCell ref="DU61:DU62"/>
     <mergeCell ref="DV61:DV62"/>
     <mergeCell ref="DW61:DW62"/>
@@ -13143,21 +12947,6 @@
     <mergeCell ref="DF61:DF62"/>
     <mergeCell ref="DG61:DG62"/>
     <mergeCell ref="DH61:DH62"/>
-    <mergeCell ref="CC61:CC62"/>
-    <mergeCell ref="CD61:CD62"/>
-    <mergeCell ref="CE61:CE62"/>
-    <mergeCell ref="CF61:CF62"/>
-    <mergeCell ref="CG61:CG62"/>
-    <mergeCell ref="CH61:CH62"/>
-    <mergeCell ref="CI61:CI62"/>
-    <mergeCell ref="CJ61:CJ62"/>
-    <mergeCell ref="CK61:CK62"/>
-    <mergeCell ref="CL61:CL62"/>
-    <mergeCell ref="CM61:CM62"/>
-    <mergeCell ref="CN61:CN62"/>
-    <mergeCell ref="CO61:CO62"/>
-    <mergeCell ref="CP61:CP62"/>
-    <mergeCell ref="CQ61:CQ62"/>
     <mergeCell ref="BL61:BL62"/>
     <mergeCell ref="BM61:BM62"/>
     <mergeCell ref="BN61:BN62"/>
@@ -13173,6 +12962,8 @@
     <mergeCell ref="BX61:BX62"/>
     <mergeCell ref="BY61:BY62"/>
     <mergeCell ref="BZ61:BZ62"/>
+    <mergeCell ref="BL63:BL64"/>
+    <mergeCell ref="BM63:BM64"/>
     <mergeCell ref="AU61:AU62"/>
     <mergeCell ref="AV61:AV62"/>
     <mergeCell ref="AW61:AW62"/>
@@ -13190,6 +12981,21 @@
     <mergeCell ref="BI61:BI62"/>
     <mergeCell ref="DP59:DP60"/>
     <mergeCell ref="DQ59:DQ60"/>
+    <mergeCell ref="BQ59:BQ60"/>
+    <mergeCell ref="BR59:BR60"/>
+    <mergeCell ref="BJ61:BJ62"/>
+    <mergeCell ref="BK61:BK62"/>
+    <mergeCell ref="CC61:CC62"/>
+    <mergeCell ref="CD61:CD62"/>
+    <mergeCell ref="CE61:CE62"/>
+    <mergeCell ref="CF61:CF62"/>
+    <mergeCell ref="CG61:CG62"/>
+    <mergeCell ref="CH61:CH62"/>
+    <mergeCell ref="CI61:CI62"/>
+    <mergeCell ref="CJ61:CJ62"/>
+    <mergeCell ref="CK61:CK62"/>
+    <mergeCell ref="CL61:CL62"/>
+    <mergeCell ref="CM61:CM62"/>
     <mergeCell ref="DR59:DR60"/>
     <mergeCell ref="DS59:DS60"/>
     <mergeCell ref="DT59:DT60"/>
@@ -13208,10 +13014,20 @@
     <mergeCell ref="CI59:CI60"/>
     <mergeCell ref="CA61:CA62"/>
     <mergeCell ref="CB61:CB62"/>
-    <mergeCell ref="BQ59:BQ60"/>
-    <mergeCell ref="BR59:BR60"/>
-    <mergeCell ref="BJ61:BJ62"/>
-    <mergeCell ref="BK61:BK62"/>
+    <mergeCell ref="CN61:CN62"/>
+    <mergeCell ref="CO61:CO62"/>
+    <mergeCell ref="CP61:CP62"/>
+    <mergeCell ref="CQ61:CQ62"/>
+    <mergeCell ref="DK61:DK62"/>
+    <mergeCell ref="DL61:DL62"/>
+    <mergeCell ref="DM61:DM62"/>
+    <mergeCell ref="DN61:DN62"/>
+    <mergeCell ref="DO61:DO62"/>
+    <mergeCell ref="DP61:DP62"/>
+    <mergeCell ref="DQ61:DQ62"/>
+    <mergeCell ref="DR61:DR62"/>
+    <mergeCell ref="DS61:DS62"/>
+    <mergeCell ref="DT61:DT62"/>
     <mergeCell ref="AS59:AS60"/>
     <mergeCell ref="AT59:AT60"/>
     <mergeCell ref="AU59:AU60"/>
@@ -13463,9 +13279,6 @@
     <mergeCell ref="DL52:DL53"/>
     <mergeCell ref="DM52:DM53"/>
     <mergeCell ref="DN52:DN53"/>
-    <mergeCell ref="DO52:DO53"/>
-    <mergeCell ref="DP52:DP53"/>
-    <mergeCell ref="DQ52:DQ53"/>
     <mergeCell ref="DA52:DA53"/>
     <mergeCell ref="DB52:DB53"/>
     <mergeCell ref="BU52:BU53"/>
@@ -13481,21 +13294,6 @@
     <mergeCell ref="CE52:CE53"/>
     <mergeCell ref="CF52:CF53"/>
     <mergeCell ref="CG52:CG53"/>
-    <mergeCell ref="CH52:CH53"/>
-    <mergeCell ref="CI52:CI53"/>
-    <mergeCell ref="BS52:BS53"/>
-    <mergeCell ref="BT52:BT53"/>
-    <mergeCell ref="AM52:AM53"/>
-    <mergeCell ref="AN52:AN53"/>
-    <mergeCell ref="AO52:AO53"/>
-    <mergeCell ref="AP52:AP53"/>
-    <mergeCell ref="AQ52:AQ53"/>
-    <mergeCell ref="AR52:AR53"/>
-    <mergeCell ref="AS52:AS53"/>
-    <mergeCell ref="AT52:AT53"/>
-    <mergeCell ref="AU52:AU53"/>
-    <mergeCell ref="AV52:AV53"/>
-    <mergeCell ref="AW52:AW53"/>
     <mergeCell ref="AX52:AX53"/>
     <mergeCell ref="AY52:AY53"/>
     <mergeCell ref="AZ52:AZ53"/>
@@ -13545,6 +13343,21 @@
     <mergeCell ref="DE48:DE49"/>
     <mergeCell ref="DF48:DF49"/>
     <mergeCell ref="DG48:DG49"/>
+    <mergeCell ref="BO48:BO49"/>
+    <mergeCell ref="BP48:BP49"/>
+    <mergeCell ref="CF48:CF49"/>
+    <mergeCell ref="CG48:CG49"/>
+    <mergeCell ref="CH48:CH49"/>
+    <mergeCell ref="CI48:CI49"/>
+    <mergeCell ref="CJ48:CJ49"/>
+    <mergeCell ref="CK48:CK49"/>
+    <mergeCell ref="CL48:CL49"/>
+    <mergeCell ref="CM48:CM49"/>
+    <mergeCell ref="CN48:CN49"/>
+    <mergeCell ref="CO48:CO49"/>
+    <mergeCell ref="CP48:CP49"/>
+    <mergeCell ref="CQ48:CQ49"/>
+    <mergeCell ref="CR48:CR49"/>
     <mergeCell ref="DH48:DH49"/>
     <mergeCell ref="DI48:DI49"/>
     <mergeCell ref="DJ48:DJ49"/>
@@ -13568,8 +13381,10 @@
     <mergeCell ref="CC48:CC49"/>
     <mergeCell ref="CD48:CD49"/>
     <mergeCell ref="CE48:CE49"/>
-    <mergeCell ref="BO48:BO49"/>
-    <mergeCell ref="BP48:BP49"/>
+    <mergeCell ref="CS48:CS49"/>
+    <mergeCell ref="CT48:CT49"/>
+    <mergeCell ref="CU48:CU49"/>
+    <mergeCell ref="CV48:CV49"/>
     <mergeCell ref="AI48:AI49"/>
     <mergeCell ref="AJ48:AJ49"/>
     <mergeCell ref="AK48:AK49"/>
@@ -13619,6 +13434,18 @@
     <mergeCell ref="BJ46:BJ47"/>
     <mergeCell ref="BK46:BK47"/>
     <mergeCell ref="BL46:BL47"/>
+    <mergeCell ref="BR46:BR47"/>
+    <mergeCell ref="BS46:BS47"/>
+    <mergeCell ref="BT46:BT47"/>
+    <mergeCell ref="BU46:BU47"/>
+    <mergeCell ref="BV46:BV47"/>
+    <mergeCell ref="BW46:BW47"/>
+    <mergeCell ref="BX46:BX47"/>
+    <mergeCell ref="BY46:BY47"/>
+    <mergeCell ref="BZ46:BZ47"/>
+    <mergeCell ref="CA46:CA47"/>
+    <mergeCell ref="CB46:CB47"/>
+    <mergeCell ref="CC46:CC47"/>
     <mergeCell ref="DL44:DL45"/>
     <mergeCell ref="DM44:DM45"/>
     <mergeCell ref="DN44:DN45"/>
@@ -13815,6 +13642,21 @@
     <mergeCell ref="DL37:DL38"/>
     <mergeCell ref="DM37:DM38"/>
     <mergeCell ref="DN37:DN38"/>
+    <mergeCell ref="BV37:BV38"/>
+    <mergeCell ref="BW37:BW38"/>
+    <mergeCell ref="BG39:BG40"/>
+    <mergeCell ref="BH39:BH40"/>
+    <mergeCell ref="BI39:BI40"/>
+    <mergeCell ref="BJ39:BJ40"/>
+    <mergeCell ref="BK39:BK40"/>
+    <mergeCell ref="BL39:BL40"/>
+    <mergeCell ref="BM39:BM40"/>
+    <mergeCell ref="BN39:BN40"/>
+    <mergeCell ref="BO39:BO40"/>
+    <mergeCell ref="BP39:BP40"/>
+    <mergeCell ref="BQ39:BQ40"/>
+    <mergeCell ref="BR39:BR40"/>
+    <mergeCell ref="BS39:BS40"/>
     <mergeCell ref="DO37:DO38"/>
     <mergeCell ref="DP37:DP38"/>
     <mergeCell ref="DQ37:DQ38"/>
@@ -13842,21 +13684,11 @@
     <mergeCell ref="CJ37:CJ38"/>
     <mergeCell ref="CK37:CK38"/>
     <mergeCell ref="CL37:CL38"/>
-    <mergeCell ref="BV37:BV38"/>
-    <mergeCell ref="BW37:BW38"/>
-    <mergeCell ref="BG39:BG40"/>
-    <mergeCell ref="BH39:BH40"/>
-    <mergeCell ref="BI39:BI40"/>
-    <mergeCell ref="BJ39:BJ40"/>
-    <mergeCell ref="BK39:BK40"/>
-    <mergeCell ref="BL39:BL40"/>
-    <mergeCell ref="BM39:BM40"/>
-    <mergeCell ref="BN39:BN40"/>
-    <mergeCell ref="BO39:BO40"/>
-    <mergeCell ref="BP39:BP40"/>
-    <mergeCell ref="BQ39:BQ40"/>
-    <mergeCell ref="BR39:BR40"/>
-    <mergeCell ref="BS39:BS40"/>
+    <mergeCell ref="DB37:DB38"/>
+    <mergeCell ref="DC37:DC38"/>
+    <mergeCell ref="CK39:CK40"/>
+    <mergeCell ref="CL39:CL40"/>
+    <mergeCell ref="CM39:CM40"/>
     <mergeCell ref="AP37:AP38"/>
     <mergeCell ref="AQ37:AQ38"/>
     <mergeCell ref="AR37:AR38"/>
@@ -13906,6 +13738,21 @@
     <mergeCell ref="BQ35:BQ36"/>
     <mergeCell ref="BR35:BR36"/>
     <mergeCell ref="BS35:BS36"/>
+    <mergeCell ref="BT35:BT36"/>
+    <mergeCell ref="BU35:BU36"/>
+    <mergeCell ref="BV35:BV36"/>
+    <mergeCell ref="BW35:BW36"/>
+    <mergeCell ref="BX35:BX36"/>
+    <mergeCell ref="BY35:BY36"/>
+    <mergeCell ref="BZ35:BZ36"/>
+    <mergeCell ref="CA35:CA36"/>
+    <mergeCell ref="CB35:CB36"/>
+    <mergeCell ref="CC35:CC36"/>
+    <mergeCell ref="CD35:CD36"/>
+    <mergeCell ref="CE35:CE36"/>
+    <mergeCell ref="CF35:CF36"/>
+    <mergeCell ref="CG35:CG36"/>
+    <mergeCell ref="CH35:CH36"/>
     <mergeCell ref="BC35:BC36"/>
     <mergeCell ref="BD35:BD36"/>
     <mergeCell ref="DB33:DB34"/>
@@ -13938,15 +13785,6 @@
     <mergeCell ref="CW33:CW34"/>
     <mergeCell ref="CX33:CX34"/>
     <mergeCell ref="CY33:CY34"/>
-    <mergeCell ref="BT33:BT34"/>
-    <mergeCell ref="BU33:BU34"/>
-    <mergeCell ref="BV33:BV34"/>
-    <mergeCell ref="BW33:BW34"/>
-    <mergeCell ref="BX33:BX34"/>
-    <mergeCell ref="BY33:BY34"/>
-    <mergeCell ref="BZ33:BZ34"/>
-    <mergeCell ref="CA33:CA34"/>
-    <mergeCell ref="CB33:CB34"/>
     <mergeCell ref="CC33:CC34"/>
     <mergeCell ref="CD33:CD34"/>
     <mergeCell ref="CE33:CE34"/>
@@ -13991,6 +13829,15 @@
     <mergeCell ref="BS33:BS34"/>
     <mergeCell ref="BA33:BA34"/>
     <mergeCell ref="BB33:BB34"/>
+    <mergeCell ref="BT33:BT34"/>
+    <mergeCell ref="BU33:BU34"/>
+    <mergeCell ref="BV33:BV34"/>
+    <mergeCell ref="BW33:BW34"/>
+    <mergeCell ref="BX33:BX34"/>
+    <mergeCell ref="BY33:BY34"/>
+    <mergeCell ref="BZ33:BZ34"/>
+    <mergeCell ref="CA33:CA34"/>
+    <mergeCell ref="CB33:CB34"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -15632,101 +15479,96 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="P1:Q3 P4 N9:O14 P11 P13 P15">
-    <cfRule type="cellIs" dxfId="35" priority="56" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="56" operator="equal">
       <formula>"À faire"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1:Q3 P4 P9:Q10 N9:O14 P11 P13 P15 P18 P20 P22 P24 P26 P28 P30 P33 P35 P37 P39 P41 P44 P46 P48 P50 P52 P55 P57 P59 P61 P63 P65 P67 P69 P71 P74 P76 P78 P80:Q1048576">
-    <cfRule type="cellIs" dxfId="34" priority="57" operator="equal">
-      <formula>"En cours"</formula>
+    <cfRule type="cellIs" dxfId="22" priority="60" operator="equal">
+      <formula>"Terminé"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="59" operator="equal">
+      <formula>"En attente"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="58" operator="equal">
       <formula>"En test"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="59" operator="equal">
-      <formula>"En attente"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="60" operator="equal">
-      <formula>"Terminé"</formula>
+    <cfRule type="cellIs" dxfId="19" priority="57" operator="equal">
+      <formula>"En cours"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1:Q7 P9:Q16 P18 P20 P22 P24 P26 P28 P30 P33 P35 P37 P39 P41 P44 P46 P48 P50 P52 P55 P57 P59 P61 P63 P65 P67 P69 P71 P74 P76 P78 P80:Q1048576">
-    <cfRule type="cellIs" dxfId="30" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="46" operator="equal">
       <formula>"À faire   ▾"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="47" operator="equal">
       <formula>"A faire"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:Q10">
-    <cfRule type="cellIs" dxfId="28" priority="61" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="61" operator="equal">
       <formula>"Terminé"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:Q16 P18 P20 P22 P24 P26 P28 P30 P33 P35 P37 P39 P41 P44 P46 P48 P50 P52 P55 P57 P59 P61 P63 P65 P67 P69 P71 P74 P76 P78 P80:Q1048576">
-    <cfRule type="cellIs" dxfId="27" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="50" operator="equal">
+      <formula>"En Test   ▾"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="48" operator="equal">
       <formula>"À faire"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="49" operator="equal">
       <formula>"À faire  ▾"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="50" operator="equal">
-      <formula>"En Test   ▾"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="51" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="51" operator="equal">
       <formula>"Terminé   ▾"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="52" operator="equal">
       <formula>"Terminé    ▾"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="53" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="53" operator="equal">
       <formula>"En cours    ▾"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="54" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="54" operator="equal">
       <formula>"En cours   ▾"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="55" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="55" operator="equal">
       <formula>"En cours   ▾"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="S18:AD19 AH18:EC19 S33:AD34 AH33:EC34 S35:EC42">
+    <cfRule type="expression" dxfId="7" priority="36">
+      <formula>AND($Q18="Terminé   ▾", S18&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S44:AD45 AH44:EC45 S46:EC53">
+    <cfRule type="expression" dxfId="6" priority="6">
+      <formula>AND($Q44="Terminé   ▾", S44&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S55:AD56 AH55:EC56">
+    <cfRule type="expression" dxfId="5" priority="5">
+      <formula>AND($Q55="Terminé   ▾", S55&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="S9:EC16">
-    <cfRule type="expression" dxfId="18" priority="45">
+    <cfRule type="expression" dxfId="4" priority="45">
       <formula>AND($Q9="Terminé   ▾", S9&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S20:EC27 S18:AD19 AH18:EC19 S35:EC42 S33:AD34 AH33:EC34 T28:EC31">
-    <cfRule type="expression" dxfId="19" priority="36">
-      <formula>AND($Q18="Terminé   ▾", S18&lt;&gt;"")</formula>
+  <conditionalFormatting sqref="S20:EC31">
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>AND($Q20="Terminé   ▾", S20&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S28:S29">
-    <cfRule type="expression" dxfId="17" priority="7">
-      <formula>AND($Q28="Terminé   ▾", S28&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S46:EC53 S44:AD45 AH44:EC45">
-    <cfRule type="expression" dxfId="11" priority="6">
-      <formula>AND($Q44="Terminé   ▾", S44&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S57:EC64 S55:AD56 AH55:EC56">
-    <cfRule type="expression" dxfId="7" priority="5">
-      <formula>AND($Q55="Terminé   ▾", S55&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S65:EC72">
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>AND($Q65="Terminé   ▾", S65&lt;&gt;"")</formula>
+  <conditionalFormatting sqref="S57:EC72">
+    <cfRule type="expression" dxfId="2" priority="4">
+      <formula>AND($Q57="Terminé   ▾", S57&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S74:EC79">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>AND($Q74="Terminé   ▾", S74&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S30:S31">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>AND($Q30="Terminé   ▾", S30&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ED31:ED32">
